--- a/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/3.2-beef-enteric/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{660E7225-7D1D-D746-832C-34021BECDE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{86816E00-529F-2545-9C86-ECEE4131780F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.2.1 methane" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="299">
   <si>
     <t>EFPRP</t>
   </si>
@@ -759,9 +759,6 @@
     <t>Njkl</t>
   </si>
   <si>
-    <t>LCjk=4,5</t>
-  </si>
-  <si>
     <t>FAjk=4,5</t>
   </si>
   <si>
@@ -909,12 +906,6 @@
     <t>Extended region</t>
   </si>
   <si>
-    <t>LC effective</t>
-  </si>
-  <si>
-    <t>Curent or previous season LC</t>
-  </si>
-  <si>
     <t>spring</t>
   </si>
   <si>
@@ -979,6 +970,18 @@
   </si>
   <si>
     <t>Remember this needs to calculated allowing for herd movements</t>
+  </si>
+  <si>
+    <t>LCk=5 (this)</t>
+  </si>
+  <si>
+    <t>LCk=5 (prev)</t>
+  </si>
+  <si>
+    <t>FA (this season)</t>
+  </si>
+  <si>
+    <t>FA (previous season)</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1207,7 +1210,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -23357,51 +23359,51 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" t="s">
         <v>243</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>244</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>245</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>246</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>247</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>248</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>249</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>250</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>251</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>252</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>253</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>254</v>
-      </c>
-      <c r="M1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" t="s">
@@ -25679,6 +25681,12 @@
       <c r="V4" t="s">
         <v>47</v>
       </c>
+      <c r="AC4" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD4">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
@@ -25711,6 +25719,12 @@
       <c r="V5" t="s">
         <v>203</v>
       </c>
+      <c r="AC5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD5">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="H8" t="s">
@@ -25754,9 +25768,6 @@
       <c r="J9" t="s">
         <v>214</v>
       </c>
-      <c r="K9" t="s">
-        <v>275</v>
-      </c>
       <c r="L9" t="s">
         <v>215</v>
       </c>
@@ -25784,16 +25795,16 @@
         <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>222</v>
@@ -25802,46 +25813,46 @@
         <v>223</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="L10" t="s">
         <v>224</v>
       </c>
-      <c r="K10" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N10" t="s">
         <v>225</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="O10" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="P10" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>227</v>
+      </c>
+      <c r="R10" t="s">
         <v>270</v>
       </c>
-      <c r="N10" t="s">
-        <v>226</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="P10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="S10" t="s">
         <v>228</v>
       </c>
-      <c r="R10" t="s">
-        <v>271</v>
-      </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>229</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>230</v>
       </c>
-      <c r="U10" t="s">
-        <v>231</v>
-      </c>
       <c r="V10" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AC10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AD10" t="s">
         <v>126</v>
@@ -25852,7 +25863,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" t="s">
         <v>135</v>
@@ -25887,7 +25898,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="Q11">
-        <f>(K11 * L11) + (1 - J11 )</f>
+        <f>(J11 * $AD$4 + K11*$AD$5) + (1 - J11 )</f>
         <v>1</v>
       </c>
       <c r="S11">
@@ -25904,7 +25915,7 @@
       </c>
       <c r="V11">
         <f>SUM(U11:U50)/1000</f>
-        <v>53.861310054946088</v>
+        <v>50.285648291275933</v>
       </c>
       <c r="AC11" t="s">
         <v>127</v>
@@ -25942,7 +25953,7 @@
         <v>0.33</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q12:Q50" si="0">(K12 * L12) + (1 - J12 )</f>
+        <f t="shared" ref="Q12:Q50" si="0">(J12 * $AD$4 + K12*$AD$5) + (1 - J12 )</f>
         <v>1</v>
       </c>
       <c r="S12">
@@ -25954,11 +25965,11 @@
         <v>0.11493047409327001</v>
       </c>
       <c r="U12">
-        <f t="shared" ref="U12:U50" si="3">H12*T12*I12</f>
+        <f>H12*T12*I12</f>
         <v>1048.7405761010889</v>
       </c>
       <c r="AA12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AB12" t="s">
         <v>117</v>
@@ -26008,7 +26019,7 @@
         <v>6.4887674174999993E-2</v>
       </c>
       <c r="U13">
-        <f t="shared" si="3"/>
+        <f>H13*T13*I13</f>
         <v>473.68002147749996</v>
       </c>
       <c r="AB13" t="s">
@@ -26059,7 +26070,7 @@
         <v>8.1213770643750002E-2</v>
       </c>
       <c r="U14">
-        <f t="shared" si="3"/>
+        <f>H14*T14*I14</f>
         <v>518.7529599869531</v>
       </c>
       <c r="AB14" t="s">
@@ -26113,7 +26124,7 @@
         <v>0.25445385417851996</v>
       </c>
       <c r="U15">
-        <f t="shared" si="3"/>
+        <f>H15*T15*I15</f>
         <v>464.3782838757989</v>
       </c>
       <c r="AB15" t="s">
@@ -26167,11 +26178,11 @@
         <v>0.22126857836175012</v>
       </c>
       <c r="U16">
-        <f t="shared" si="3"/>
+        <f>H16*T16*I16</f>
         <v>1615.2606220407758</v>
       </c>
       <c r="AA16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB16" t="s">
         <v>117</v>
@@ -26221,7 +26232,7 @@
         <v>0.20565665279999992</v>
       </c>
       <c r="U17">
-        <f t="shared" si="3"/>
+        <f>H17*T17*I17</f>
         <v>1313.6318697599995</v>
       </c>
       <c r="AB17" t="s">
@@ -26272,7 +26283,7 @@
         <v>0.20870311459931989</v>
       </c>
       <c r="U18">
-        <f t="shared" si="3"/>
+        <f>H18*T18*I18</f>
         <v>1142.6495524312766</v>
       </c>
       <c r="AB18" t="s">
@@ -26326,7 +26337,7 @@
         <v>0.17664036603327005</v>
       </c>
       <c r="U19">
-        <f t="shared" si="3"/>
+        <f>H19*T19*I19</f>
         <v>1611.8433400535891</v>
       </c>
       <c r="AB19" t="s">
@@ -26380,7 +26391,7 @@
         <v>0.16034523412527002</v>
       </c>
       <c r="U20">
-        <f t="shared" si="3"/>
+        <f>H20*T20*I20</f>
         <v>2633.6704705075599</v>
       </c>
     </row>
@@ -26422,7 +26433,7 @@
         <v>0.12441409099199996</v>
       </c>
       <c r="U21">
-        <f t="shared" si="3"/>
+        <f>H21*T21*I21</f>
         <v>1929.9735865133994</v>
       </c>
     </row>
@@ -26464,11 +26475,11 @@
         <v>0.12332640906971998</v>
       </c>
       <c r="U22">
-        <f t="shared" si="3"/>
+        <f>H22*T22*I22</f>
         <v>1800.5655724179114</v>
       </c>
       <c r="X22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s">
         <v>184</v>
@@ -26488,15 +26499,13 @@
         <v>150</v>
       </c>
       <c r="J23">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <f>J23+J26</f>
-        <v>0.79999999999999993</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <f>$AC$12</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <v>560</v>
@@ -26506,25 +26515,25 @@
       </c>
       <c r="Q23">
         <f t="shared" si="0"/>
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="S23">
         <f t="shared" si="1"/>
-        <v>13.927245421014002</v>
+        <v>10.3934667321</v>
       </c>
       <c r="T23">
         <f t="shared" si="2"/>
-        <v>0.28829398021498981</v>
+        <v>0.21514476135447</v>
       </c>
       <c r="U23">
-        <f t="shared" si="3"/>
-        <v>3946.0238541926733</v>
+        <f>H23*T23*I23</f>
+        <v>2944.7939210393079</v>
       </c>
       <c r="X23" t="s">
         <v>130</v>
       </c>
       <c r="Y23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s">
         <v>113</v>
@@ -26539,37 +26548,37 @@
         <v>135</v>
       </c>
       <c r="AD23" t="s">
+        <v>255</v>
+      </c>
+      <c r="AE23" t="s">
         <v>256</v>
       </c>
-      <c r="AE23" t="s">
+      <c r="AF23" t="s">
         <v>257</v>
       </c>
-      <c r="AF23" t="s">
+      <c r="AG23" t="s">
         <v>258</v>
       </c>
-      <c r="AG23" t="s">
+      <c r="AH23" t="s">
         <v>259</v>
       </c>
-      <c r="AH23" t="s">
+      <c r="AI23" t="s">
         <v>260</v>
       </c>
-      <c r="AI23" t="s">
+      <c r="AJ23" t="s">
         <v>261</v>
       </c>
-      <c r="AJ23" t="s">
+      <c r="AK23" t="s">
         <v>262</v>
       </c>
-      <c r="AK23" t="s">
+      <c r="AL23" t="s">
         <v>263</v>
       </c>
-      <c r="AL23" t="s">
+      <c r="AM23" t="s">
         <v>264</v>
       </c>
-      <c r="AM23" t="s">
-        <v>265</v>
-      </c>
       <c r="AN23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AP23" s="10"/>
       <c r="AQ23" s="11"/>
@@ -26602,12 +26611,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <f>J24+J23</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <f>$AC$13</f>
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N24">
         <v>550</v>
@@ -26617,19 +26624,19 @@
       </c>
       <c r="Q24">
         <f t="shared" si="0"/>
-        <v>1.77</v>
+        <v>1</v>
       </c>
       <c r="S24">
         <f t="shared" si="1"/>
-        <v>14.518417920000003</v>
+        <v>8.2024960000000018</v>
       </c>
       <c r="T24">
         <f t="shared" si="2"/>
-        <v>0.30053125094400002</v>
+        <v>0.16979166720000005</v>
       </c>
       <c r="U24">
-        <f t="shared" si="3"/>
-        <v>6855.8691621600001</v>
+        <f>H24*T24*I24</f>
+        <v>3873.3724080000011</v>
       </c>
       <c r="X24" s="9" t="s">
         <v>117</v>
@@ -26684,40 +26691,40 @@
       </c>
       <c r="AP24" s="14"/>
       <c r="AQ24" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR24" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="AR24" s="27" t="s">
+      <c r="AS24" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="AS24" s="28" t="s">
+      <c r="AT24" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="AT24" s="28" t="s">
+      <c r="AU24" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU24" s="28" t="s">
+      <c r="AV24" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AV24" s="29" t="s">
+      <c r="AW24" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AW24" s="28" t="s">
+      <c r="AX24" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="AX24" s="28" t="s">
+      <c r="AY24" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="AY24" s="28" t="s">
+      <c r="AZ24" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="AZ24" s="28" t="s">
+      <c r="BA24" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="BA24" s="28" t="s">
+      <c r="BB24" s="28" t="s">
         <v>253</v>
-      </c>
-      <c r="BB24" s="28" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="25" spans="5:54" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -26734,7 +26741,6 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <f>J25+J24</f>
         <v>0</v>
       </c>
       <c r="L25">
@@ -26760,7 +26766,7 @@
         <v>0.158198927175</v>
       </c>
       <c r="U25">
-        <f t="shared" si="3"/>
+        <f>H25*T25*I25</f>
         <v>3464.5565051325002</v>
       </c>
       <c r="X25" s="9" t="s">
@@ -26816,7 +26822,7 @@
       </c>
       <c r="AP25" s="18"/>
       <c r="AQ25" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR25" s="15" t="s">
         <v>130</v>
@@ -26863,11 +26869,10 @@
         <v>200</v>
       </c>
       <c r="J26">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <f>J26+K25</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <f>$AC$14</f>
@@ -26881,19 +26886,19 @@
       </c>
       <c r="Q26">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="S26">
         <f t="shared" si="1"/>
-        <v>7.1255208038400015</v>
+        <v>7.9172453376000016</v>
       </c>
       <c r="T26">
         <f t="shared" si="2"/>
-        <v>0.14749828063948803</v>
+        <v>0.16388697848832004</v>
       </c>
       <c r="U26">
-        <f t="shared" si="3"/>
-        <v>2691.8436216706564</v>
+        <f>H26*T26*I26</f>
+        <v>2990.9373574118408</v>
       </c>
       <c r="X26" s="9" t="s">
         <v>120</v>
@@ -27001,8 +27006,7 @@
         <v>0.8</v>
       </c>
       <c r="K27">
-        <f>J27+J30</f>
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="L27">
         <f>$AC$12</f>
@@ -27016,19 +27020,19 @@
       </c>
       <c r="Q27">
         <f t="shared" si="0"/>
-        <v>1.37</v>
+        <v>1.2949999999999999</v>
       </c>
       <c r="S27">
         <f t="shared" si="1"/>
-        <v>8.3673043119719992</v>
+        <v>7.9092402073019974</v>
       </c>
       <c r="T27">
         <f t="shared" si="2"/>
-        <v>0.17320319925782038</v>
+        <v>0.16372127229115133</v>
       </c>
       <c r="U27">
-        <f t="shared" si="3"/>
-        <v>1580.4791932276109</v>
+        <f>H27*T27*I27</f>
+        <v>1493.9566096567557</v>
       </c>
       <c r="X27" s="9" t="s">
         <v>121</v>
@@ -27119,7 +27123,7 @@
     </row>
     <row r="28" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F28" t="s">
         <v>119</v>
@@ -27134,8 +27138,7 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <f>J28+J27</f>
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="L28">
         <f>$AC$13</f>
@@ -27149,19 +27152,19 @@
       </c>
       <c r="Q28">
         <f t="shared" si="0"/>
-        <v>1.8800000000000001</v>
+        <v>1.8580000000000001</v>
       </c>
       <c r="S28">
         <f t="shared" si="1"/>
-        <v>9.5932826563680038</v>
+        <v>9.4810208380488028</v>
       </c>
       <c r="T28">
         <f t="shared" si="2"/>
-        <v>0.19858095098681766</v>
+        <v>0.19625713134761019</v>
       </c>
       <c r="U28">
-        <f t="shared" si="3"/>
-        <v>3442.897237733951</v>
+        <f>H28*T28*I28</f>
+        <v>3402.6080147391917</v>
       </c>
       <c r="X28" s="9" t="s">
         <v>117</v>
@@ -27264,7 +27267,6 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <f>J29+J28</f>
         <v>0</v>
       </c>
       <c r="L29">
@@ -27290,7 +27292,7 @@
         <v>6.4564463903557495E-2</v>
       </c>
       <c r="U29">
-        <f t="shared" si="3"/>
+        <f>H29*T29*I29</f>
         <v>1148.8439295839262</v>
       </c>
       <c r="X29" s="9" t="s">
@@ -27394,8 +27396,7 @@
         <v>0.1</v>
       </c>
       <c r="K30">
-        <f>J30+K29</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <f>$AC$14</f>
@@ -27409,19 +27410,19 @@
       </c>
       <c r="Q30">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="S30">
         <f t="shared" si="1"/>
-        <v>3.3315637680899997</v>
+        <v>3.8127896457029995</v>
       </c>
       <c r="T30">
         <f t="shared" si="2"/>
-        <v>6.8963369999462981E-2</v>
+        <v>7.8924745666052093E-2</v>
       </c>
       <c r="U30">
-        <f t="shared" si="3"/>
-        <v>1258.5815024901995</v>
+        <f>H30*T30*I30</f>
+        <v>1440.3766084054507</v>
       </c>
       <c r="X30" s="9" t="s">
         <v>120</v>
@@ -27529,8 +27530,7 @@
         <v>0.9</v>
       </c>
       <c r="K31">
-        <f>J31+J34</f>
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="L31">
         <f>$AC$12</f>
@@ -27544,19 +27544,19 @@
       </c>
       <c r="Q31">
         <f t="shared" si="0"/>
-        <v>1.27</v>
+        <v>1.3250000000000002</v>
       </c>
       <c r="S31">
         <f t="shared" si="1"/>
-        <v>13.199702749767001</v>
+        <v>13.771343420032503</v>
       </c>
       <c r="T31">
         <f t="shared" si="2"/>
-        <v>0.27323384692017694</v>
+        <v>0.28506680879467278</v>
       </c>
       <c r="U31">
-        <f t="shared" si="3"/>
-        <v>1246.6294265733072</v>
+        <f>H31*T31*I31</f>
+        <v>1300.6173151256944</v>
       </c>
       <c r="X31" s="9" t="s">
         <v>121</v>
@@ -27647,7 +27647,7 @@
     </row>
     <row r="32" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F32" t="s">
         <v>119</v>
@@ -27662,7 +27662,6 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <f>J32+J31</f>
         <v>0.9</v>
       </c>
       <c r="L32">
@@ -27688,7 +27687,7 @@
         <v>0.33788541772800013</v>
       </c>
       <c r="U32">
-        <f t="shared" si="3"/>
+        <f>H32*T32*I32</f>
         <v>3083.2044367680014</v>
       </c>
       <c r="X32" s="9" t="s">
@@ -27792,7 +27791,6 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <f>J33+J32</f>
         <v>0</v>
       </c>
       <c r="L33">
@@ -27818,7 +27816,7 @@
         <v>0.158198927175</v>
       </c>
       <c r="U33">
-        <f t="shared" si="3"/>
+        <f>H33*T33*I33</f>
         <v>1299.2086894246875</v>
       </c>
       <c r="X33" s="9" t="s">
@@ -27922,7 +27920,6 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <f>J34+K33</f>
         <v>0</v>
       </c>
       <c r="L34">
@@ -27948,7 +27945,7 @@
         <v>0.16388697848832004</v>
       </c>
       <c r="U34">
-        <f t="shared" si="3"/>
+        <f>H34*T34*I34</f>
         <v>1196.3749429647364</v>
       </c>
       <c r="X34" s="9" t="s">
@@ -28069,7 +28066,7 @@
         <v>0.77</v>
       </c>
       <c r="Q35">
-        <f>(K35 * L35) + (1 - J35 )</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S35">
@@ -28081,7 +28078,7 @@
         <v>0.19467496241126997</v>
       </c>
       <c r="U35">
-        <f t="shared" si="3"/>
+        <f>H35*T35*I35</f>
         <v>532.92270960085148</v>
       </c>
       <c r="X35" s="9" t="s">
@@ -28212,7 +28209,7 @@
         <v>0.17138540797766999</v>
       </c>
       <c r="U36">
-        <f t="shared" si="3"/>
+        <f>H36*T36*I36</f>
         <v>1094.7242934573671</v>
       </c>
       <c r="X36" s="9" t="s">
@@ -28340,7 +28337,7 @@
         <v>0.14782700226492007</v>
       </c>
       <c r="U37">
-        <f t="shared" si="3"/>
+        <f>H37*T37*I37</f>
         <v>539.56855826695823</v>
       </c>
       <c r="X37" s="9" t="s">
@@ -28468,7 +28465,7 @@
         <v>0.16034523412527002</v>
       </c>
       <c r="U38">
-        <f t="shared" si="3"/>
+        <f>H38*T38*I38</f>
         <v>292.63005227861777</v>
       </c>
       <c r="X38" s="9" t="s">
@@ -28601,7 +28598,7 @@
         <v>0.19467496241126997</v>
       </c>
       <c r="U39">
-        <f t="shared" si="3"/>
+        <f>H39*T39*I39</f>
         <v>532.92270960085148</v>
       </c>
       <c r="X39" s="9" t="s">
@@ -28693,7 +28690,7 @@
     </row>
     <row r="40" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F40" t="s">
         <v>119</v>
@@ -28732,7 +28729,7 @@
         <v>0.17138540797766999</v>
       </c>
       <c r="U40">
-        <f t="shared" si="3"/>
+        <f>H40*T40*I40</f>
         <v>1563.8918477962386</v>
       </c>
       <c r="X40" s="9" t="s">
@@ -28860,7 +28857,7 @@
         <v>0.14782700226492007</v>
       </c>
       <c r="U41">
-        <f t="shared" si="3"/>
+        <f>H41*T41*I41</f>
         <v>539.56855826695823</v>
       </c>
       <c r="X41" s="9" t="s">
@@ -28988,7 +28985,7 @@
         <v>0.16034523412527002</v>
       </c>
       <c r="U42">
-        <f t="shared" si="3"/>
+        <f>H42*T42*I42</f>
         <v>0</v>
       </c>
       <c r="X42" s="9" t="s">
@@ -29044,7 +29041,7 @@
       </c>
       <c r="AP42" s="20"/>
       <c r="AQ42" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR42" s="19" t="s">
         <v>117</v>
@@ -29121,7 +29118,7 @@
         <v>0.12642569288891994</v>
       </c>
       <c r="U43">
-        <f t="shared" si="3"/>
+        <f>H43*T43*I43</f>
         <v>230.7268895222789</v>
       </c>
       <c r="X43" s="9" t="s">
@@ -29213,7 +29210,7 @@
     </row>
     <row r="44" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F44" t="s">
         <v>119</v>
@@ -29252,7 +29249,7 @@
         <v>0.11191665196287003</v>
       </c>
       <c r="U44">
-        <f t="shared" si="3"/>
+        <f>H44*T44*I44</f>
         <v>408.49577966447561</v>
       </c>
       <c r="X44" s="9" t="s">
@@ -29380,7 +29377,7 @@
         <v>6.4564463903557495E-2</v>
       </c>
       <c r="U45">
-        <f t="shared" si="3"/>
+        <f>H45*T45*I45</f>
         <v>206.20275659198674</v>
       </c>
       <c r="X45" s="9" t="s">
@@ -29508,7 +29505,7 @@
         <v>7.6625966666069981E-2</v>
       </c>
       <c r="U46">
-        <f t="shared" si="3"/>
+        <f>H46*T46*I46</f>
         <v>209.76358374836656</v>
       </c>
       <c r="X46" s="9" t="s">
@@ -29564,7 +29561,7 @@
       </c>
       <c r="AP46" s="20"/>
       <c r="AQ46" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AR46" s="19" t="s">
         <v>117</v>
@@ -29641,7 +29638,7 @@
         <v>0.19467496241126997</v>
       </c>
       <c r="U47">
-        <f t="shared" si="3"/>
+        <f>H47*T47*I47</f>
         <v>532.92270960085148</v>
       </c>
       <c r="X47" s="9" t="s">
@@ -29733,7 +29730,7 @@
     </row>
     <row r="48" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E48" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F48" t="s">
         <v>119</v>
@@ -29772,7 +29769,7 @@
         <v>0.17138540797766999</v>
       </c>
       <c r="U48">
-        <f t="shared" si="3"/>
+        <f>H48*T48*I48</f>
         <v>547.36214672868357</v>
       </c>
       <c r="X48" s="9" t="s">
@@ -29900,7 +29897,7 @@
         <v>0.14782700226492007</v>
       </c>
       <c r="U49">
-        <f t="shared" si="3"/>
+        <f>H49*T49*I49</f>
         <v>269.78427913347912</v>
       </c>
       <c r="X49" s="9" t="s">
@@ -30028,7 +30025,7 @@
         <v>0.16034523412527002</v>
       </c>
       <c r="U50">
-        <f t="shared" si="3"/>
+        <f>H50*T50*I50</f>
         <v>0</v>
       </c>
       <c r="X50" s="9" t="s">
@@ -30084,7 +30081,7 @@
       </c>
       <c r="AP50" s="20"/>
       <c r="AQ50" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR50" s="19" t="s">
         <v>117</v>
@@ -30429,7 +30426,7 @@
       </c>
       <c r="AP54" s="20"/>
       <c r="AQ54" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AR54" s="19" t="s">
         <v>117</v>
@@ -30780,7 +30777,7 @@
       </c>
       <c r="AP58" s="20"/>
       <c r="AQ58" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AR58" s="19" t="s">
         <v>117</v>
@@ -30991,7 +30988,7 @@
         <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C61" t="s">
         <v>113</v>
@@ -31014,36 +31011,39 @@
       <c r="J61">
         <v>0</v>
       </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
       <c r="L61">
         <v>0</v>
       </c>
-      <c r="N61" t="e" cm="1">
-        <f t="array" ref="N61">_xlfn.DROP(_xlfn.XLOOKUP($C61,#REF!,#REF!),1)</f>
-        <v>#REF!</v>
+      <c r="N61" s="32" cm="1">
+        <f t="array" ref="N61:N100">_xlfn.DROP(_xlfn.XLOOKUP($C61,TableW[[#Headers],[ACT/NSW]:[QLD - Low]],TableW[[#All],[ACT/NSW]:[QLD - Low]]),1)</f>
+        <v>80</v>
       </c>
       <c r="P61" cm="1">
         <f t="array" ref="P61:P100">_xlfn.DROP(_xlfn.XLOOKUP($C61,TableLWG[[#Headers],[ACT/NSW]:[QLD - Low]],TableLWG[[#All],[ACT/NSW]:[QLD - Low]]),1)</f>
         <v>0.5</v>
       </c>
       <c r="Q61">
-        <f>(J61 * L61) + (1 - J61 )</f>
-        <v>1</v>
-      </c>
-      <c r="S61" t="e">
+        <f>(J61 * $AD$4 + K61*$AD$5) + (1 - J61 )</f>
+        <v>1</v>
+      </c>
+      <c r="S61">
         <f>(1.185 + 0.00454 * N61- 0.0000026 * N61^2 + 0.315 * P61 )^2 * Q61</f>
-        <v>#REF!</v>
-      </c>
-      <c r="T61" t="e">
+        <v>2.8529236835999998</v>
+      </c>
+      <c r="T61">
         <f>20.7 * S61 * 10^-3</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U61" t="e">
+        <v>5.9055520250520001E-2</v>
+      </c>
+      <c r="U61">
         <f>H61*T61*I61</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V61" t="e">
+        <v>269.44081114299752</v>
+      </c>
+      <c r="V61">
         <f>SUM(U61:U100)/1000</f>
-        <v>#REF!</v>
+        <v>49.157894155502696</v>
       </c>
       <c r="X61" s="9" t="s">
         <v>119</v>
@@ -31142,27 +31142,33 @@
       <c r="J62">
         <v>0</v>
       </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
       <c r="L62">
         <v>0</v>
       </c>
+      <c r="N62">
+        <v>170</v>
+      </c>
       <c r="P62">
         <v>1</v>
       </c>
       <c r="Q62">
-        <f t="shared" ref="Q62:Q100" si="4">(J62 * L62) + (1 - J62 )</f>
+        <f t="shared" ref="Q62:Q100" si="3">(J62 * $AD$4 + K62*$AD$5) + (1 - J62 )</f>
         <v>1</v>
       </c>
       <c r="S62">
-        <f t="shared" ref="S62:S100" si="5">(1.185 + 0.00454 * N62- 0.0000026 * N62^2 + 0.315 * P62 )^2 * Q62</f>
-        <v>2.25</v>
+        <f t="shared" ref="S62:S100" si="4">(1.185 + 0.00454 * N62- 0.0000026 * N62^2 + 0.315 * P62 )^2 * Q62</f>
+        <v>4.8253151556000002</v>
       </c>
       <c r="T62">
-        <f t="shared" ref="T62:T100" si="6">20.7 * S62 * 10^-3</f>
-        <v>4.6574999999999998E-2</v>
+        <f t="shared" ref="T62:T100" si="5">20.7 * S62 * 10^-3</f>
+        <v>9.9884023720920007E-2</v>
       </c>
       <c r="U62">
-        <f t="shared" ref="U62:U100" si="7">H62*T62*I62</f>
-        <v>424.99687499999999</v>
+        <f>H62*T62*I62</f>
+        <v>911.44171645339509</v>
       </c>
       <c r="X62" s="9" t="s">
         <v>120</v>
@@ -31211,7 +31217,7 @@
       </c>
       <c r="AP62" s="20"/>
       <c r="AQ62" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AR62" s="19" t="s">
         <v>117</v>
@@ -31260,27 +31266,33 @@
       <c r="J63">
         <v>0</v>
       </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
       <c r="L63">
         <v>0</v>
+      </c>
+      <c r="N63">
+        <v>240</v>
       </c>
       <c r="P63">
         <v>0.8</v>
       </c>
       <c r="Q63">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S63">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S63">
+        <v>5.6493683855999981</v>
+      </c>
+      <c r="T63">
         <f t="shared" si="5"/>
-        <v>2.0649690000000001</v>
-      </c>
-      <c r="T63">
-        <f t="shared" si="6"/>
-        <v>4.2744858300000001E-2</v>
+        <v>0.11694192558191996</v>
       </c>
       <c r="U63">
-        <f t="shared" si="7"/>
-        <v>312.03746559000001</v>
+        <f>H63*T63*I63</f>
+        <v>853.67605674801564</v>
       </c>
       <c r="X63" s="9" t="s">
         <v>121</v>
@@ -31376,27 +31388,33 @@
       <c r="J64">
         <v>0</v>
       </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
       <c r="L64">
         <v>0</v>
+      </c>
+      <c r="N64">
+        <v>280</v>
       </c>
       <c r="P64">
         <v>0.4</v>
       </c>
       <c r="Q64">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S64">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S64">
+        <v>5.6565962895999995</v>
+      </c>
+      <c r="T64">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T64">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.11709154319472</v>
       </c>
       <c r="U64">
-        <f t="shared" si="7"/>
-        <v>227.25143902125001</v>
+        <f>H64*T64*I64</f>
+        <v>747.92223215627394</v>
       </c>
       <c r="AP64" s="20"/>
       <c r="AQ64" s="18"/>
@@ -31450,27 +31468,33 @@
       <c r="J65">
         <v>0</v>
       </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
       <c r="L65">
         <v>0</v>
+      </c>
+      <c r="N65">
+        <v>480</v>
       </c>
       <c r="P65">
         <v>0.2</v>
       </c>
       <c r="Q65">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S65">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S65">
+        <v>7.9984889855999999</v>
+      </c>
+      <c r="T65">
         <f t="shared" si="5"/>
-        <v>1.557504</v>
-      </c>
-      <c r="T65">
-        <f t="shared" si="6"/>
-        <v>3.22403328E-2</v>
+        <v>0.16556872200191999</v>
       </c>
       <c r="U65">
-        <f t="shared" si="7"/>
-        <v>58.838607359999997</v>
+        <f>H65*T65*I65</f>
+        <v>302.162917653504</v>
       </c>
       <c r="AP65" s="18"/>
       <c r="AQ65" s="20"/>
@@ -31524,31 +31548,37 @@
       <c r="J66">
         <v>0</v>
       </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
       <c r="L66">
         <v>0</v>
+      </c>
+      <c r="N66">
+        <v>520</v>
       </c>
       <c r="P66">
         <v>0.4</v>
       </c>
       <c r="Q66">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S66">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S66">
+        <v>8.8135359375999975</v>
+      </c>
+      <c r="T66">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T66">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.18244019390831995</v>
       </c>
       <c r="U66">
-        <f t="shared" si="7"/>
-        <v>259.71593031000003</v>
+        <f>H66*T66*I66</f>
+        <v>1331.8134155307357</v>
       </c>
       <c r="AP66" s="20"/>
       <c r="AQ66" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AR66" s="19" t="s">
         <v>117</v>
@@ -31597,27 +31627,33 @@
       <c r="J67">
         <v>0</v>
       </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
       <c r="L67">
         <v>0</v>
+      </c>
+      <c r="N67">
+        <v>550</v>
       </c>
       <c r="P67">
         <v>0.3</v>
       </c>
       <c r="Q67">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S67">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S67">
+        <v>8.940100000000001</v>
+      </c>
+      <c r="T67">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T67">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.18506007000000002</v>
       </c>
       <c r="U67">
-        <f t="shared" si="7"/>
-        <v>216.46208585531249</v>
+        <f>H67*T67*I67</f>
+        <v>1182.0711971250003</v>
       </c>
       <c r="AP67" s="18"/>
       <c r="AQ67" s="20"/>
@@ -31668,27 +31704,33 @@
       <c r="J68">
         <v>0</v>
       </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
       <c r="L68">
         <v>0</v>
+      </c>
+      <c r="N68">
+        <v>560</v>
       </c>
       <c r="P68">
         <v>0.1</v>
       </c>
       <c r="Q68">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S68">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S68">
+        <v>8.6644277315999982</v>
+      </c>
+      <c r="T68">
         <f t="shared" si="5"/>
-        <v>1.4798722500000003</v>
-      </c>
-      <c r="T68">
-        <f t="shared" si="6"/>
-        <v>3.0633355575000007E-2</v>
+        <v>0.17935365404411996</v>
       </c>
       <c r="U68">
-        <f t="shared" si="7"/>
-        <v>167.71762177312505</v>
+        <f>H68*T68*I68</f>
+        <v>981.96125589155668</v>
       </c>
       <c r="AP68" s="20"/>
       <c r="AQ68" s="18"/>
@@ -31742,27 +31784,33 @@
       <c r="J69">
         <v>0</v>
       </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
       <c r="L69">
         <v>0</v>
+      </c>
+      <c r="N69">
+        <v>300</v>
       </c>
       <c r="P69">
         <v>0.4</v>
       </c>
       <c r="Q69">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S69">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S69">
+        <v>5.9487209999999981</v>
+      </c>
+      <c r="T69">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T69">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.12313852469999996</v>
       </c>
       <c r="U69">
-        <f t="shared" si="7"/>
-        <v>324.64491288750003</v>
+        <f>H69*T69*I69</f>
+        <v>1123.6390378874996</v>
       </c>
       <c r="AP69" s="18"/>
       <c r="AQ69" s="20"/>
@@ -31816,31 +31864,37 @@
       <c r="J70">
         <v>0</v>
       </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
       <c r="L70">
         <v>0</v>
+      </c>
+      <c r="N70">
+        <v>360</v>
       </c>
       <c r="P70">
         <v>0.7</v>
       </c>
       <c r="Q70">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S70">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S70">
+        <v>7.3058846435999998</v>
+      </c>
+      <c r="T70">
         <f t="shared" si="5"/>
-        <v>1.9754302499999998</v>
-      </c>
-      <c r="T70">
-        <f t="shared" si="6"/>
-        <v>4.0891406174999992E-2</v>
+        <v>0.15123181212251999</v>
       </c>
       <c r="U70">
-        <f t="shared" si="7"/>
-        <v>671.64134642437489</v>
+        <f>H70*T70*I70</f>
+        <v>2483.9825141123911</v>
       </c>
       <c r="AP70" s="20"/>
       <c r="AQ70" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AR70" s="19" t="s">
         <v>117</v>
@@ -31889,27 +31943,33 @@
       <c r="J71">
         <v>0</v>
       </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
       <c r="L71">
         <v>0</v>
+      </c>
+      <c r="N71">
+        <v>390</v>
       </c>
       <c r="P71">
         <v>0.3</v>
       </c>
       <c r="Q71">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S71">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S71">
+        <v>7.0471135296000007</v>
+      </c>
+      <c r="T71">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T71">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.14587525006272001</v>
       </c>
       <c r="U71">
-        <f t="shared" si="7"/>
-        <v>525.69363707718742</v>
+        <f>H71*T71*I71</f>
+        <v>2262.889816597944</v>
       </c>
       <c r="AP71" s="18"/>
       <c r="AQ71" s="20"/>
@@ -31960,27 +32020,33 @@
       <c r="J72">
         <v>0</v>
       </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
       <c r="L72">
         <v>0</v>
+      </c>
+      <c r="N72">
+        <v>410</v>
       </c>
       <c r="P72">
         <v>0.2</v>
       </c>
       <c r="Q72">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S72">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S72">
+        <v>7.1414010756000028</v>
+      </c>
+      <c r="T72">
         <f t="shared" si="5"/>
-        <v>1.557504</v>
-      </c>
-      <c r="T72">
-        <f t="shared" si="6"/>
-        <v>3.22403328E-2</v>
+        <v>0.14782700226492007</v>
       </c>
       <c r="U72">
-        <f t="shared" si="7"/>
-        <v>470.70885887999998</v>
+        <f>H72*T72*I72</f>
+        <v>2158.2742330678329</v>
       </c>
       <c r="AP72" s="20"/>
       <c r="AQ72" s="18"/>
@@ -32034,28 +32100,34 @@
       <c r="J73">
         <v>0.7</v>
       </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
       <c r="L73">
         <f>$AC$12</f>
         <v>1.3</v>
       </c>
+      <c r="N73">
+        <v>440</v>
+      </c>
       <c r="P73">
         <v>0.3</v>
       </c>
       <c r="Q73">
+        <f t="shared" si="3"/>
+        <v>1.21</v>
+      </c>
+      <c r="S73">
         <f t="shared" si="4"/>
-        <v>1.21</v>
-      </c>
-      <c r="S73">
+        <v>9.309296640996001</v>
+      </c>
+      <c r="T73">
         <f t="shared" si="5"/>
-        <v>1.9809155025</v>
-      </c>
-      <c r="T73">
-        <f t="shared" si="6"/>
-        <v>4.1004950901749999E-2</v>
+        <v>0.19270244046861723</v>
       </c>
       <c r="U73">
-        <f t="shared" si="7"/>
-        <v>561.25526546770311</v>
+        <f>H73*T73*I73</f>
+        <v>2637.6146539141982</v>
       </c>
       <c r="AP73" s="18"/>
       <c r="AQ73" s="20"/>
@@ -32109,32 +32181,38 @@
       <c r="J74">
         <v>0</v>
       </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
       <c r="L74">
         <f>$AC$13</f>
         <v>1.1000000000000001</v>
       </c>
+      <c r="N74">
+        <v>470</v>
+      </c>
       <c r="P74">
         <v>0.3</v>
       </c>
       <c r="Q74">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S74">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S74">
+        <v>8.0596938816000012</v>
+      </c>
+      <c r="T74">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T74">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.16683566334912001</v>
       </c>
       <c r="U74">
-        <f t="shared" si="7"/>
-        <v>773.07887805468749</v>
+        <f>H74*T74*I74</f>
+        <v>3805.9385701518004</v>
       </c>
       <c r="AP74" s="20"/>
       <c r="AQ74" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AR74" s="19" t="s">
         <v>117</v>
@@ -32183,28 +32261,34 @@
       <c r="J75">
         <v>0</v>
       </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
       <c r="L75">
         <f>$AC$14</f>
         <v>0</v>
       </c>
+      <c r="N75">
+        <v>490</v>
+      </c>
       <c r="P75">
         <v>0.2</v>
       </c>
       <c r="Q75">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S75">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S75">
+        <v>8.1130407556000002</v>
+      </c>
+      <c r="T75">
         <f t="shared" si="5"/>
-        <v>1.557504</v>
-      </c>
-      <c r="T75">
-        <f t="shared" si="6"/>
-        <v>3.22403328E-2</v>
+        <v>0.16793994364092002</v>
       </c>
       <c r="U75">
-        <f t="shared" si="7"/>
-        <v>706.06328831999997</v>
+        <f>H75*T75*I75</f>
+        <v>3677.8847657361484</v>
       </c>
       <c r="AP75" s="18"/>
       <c r="AQ75" s="20"/>
@@ -32255,28 +32339,34 @@
       <c r="J76">
         <v>0.1</v>
       </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
       <c r="L76">
         <f>$AC$14</f>
         <v>0</v>
       </c>
+      <c r="N76">
+        <v>500</v>
+      </c>
       <c r="P76">
         <v>0.1</v>
       </c>
       <c r="Q76">
+        <f t="shared" si="3"/>
+        <v>1.03</v>
+      </c>
+      <c r="S76">
         <f t="shared" si="4"/>
-        <v>0.9</v>
-      </c>
-      <c r="S76">
+        <v>8.2871042175000014</v>
+      </c>
+      <c r="T76">
         <f t="shared" si="5"/>
-        <v>1.3318850250000003</v>
-      </c>
-      <c r="T76">
-        <f t="shared" si="6"/>
-        <v>2.7570020017500006E-2</v>
+        <v>0.17154305730225003</v>
       </c>
       <c r="U76">
-        <f t="shared" si="7"/>
-        <v>503.15286531937511</v>
+        <f>H76*T76*I76</f>
+        <v>3130.6607957660631</v>
       </c>
       <c r="AP76" s="20"/>
       <c r="AQ76" s="18"/>
@@ -32330,28 +32420,34 @@
       <c r="J77">
         <v>0.8</v>
       </c>
+      <c r="K77">
+        <v>0.05</v>
+      </c>
       <c r="L77">
         <f>$AC$12</f>
         <v>1.3</v>
       </c>
+      <c r="N77">
+        <v>75</v>
+      </c>
       <c r="P77">
         <v>0.5</v>
       </c>
       <c r="Q77">
+        <f t="shared" si="3"/>
+        <v>1.2949999999999999</v>
+      </c>
+      <c r="S77">
         <f t="shared" si="4"/>
-        <v>1.24</v>
-      </c>
-      <c r="S77">
+        <v>3.6046003071093744</v>
+      </c>
+      <c r="T77">
         <f t="shared" si="5"/>
-        <v>2.23485975</v>
-      </c>
-      <c r="T77">
-        <f t="shared" si="6"/>
-        <v>4.6261596825000001E-2</v>
+        <v>7.4615226357164055E-2</v>
       </c>
       <c r="U77">
-        <f t="shared" si="7"/>
-        <v>422.13707102812504</v>
+        <f>H77*T77*I77</f>
+        <v>680.86394050912202</v>
       </c>
       <c r="AP77" s="18"/>
       <c r="AQ77" s="20"/>
@@ -32391,7 +32487,7 @@
     </row>
     <row r="78" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E78" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F78" t="s">
         <v>119</v>
@@ -32404,33 +32500,39 @@
       </c>
       <c r="J78">
         <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0.78</v>
       </c>
       <c r="L78">
         <f>$AC$13</f>
         <v>1.1000000000000001</v>
       </c>
+      <c r="N78">
+        <v>160</v>
+      </c>
       <c r="P78">
         <v>0.9</v>
       </c>
       <c r="Q78">
+        <f t="shared" si="3"/>
+        <v>1.8580000000000001</v>
+      </c>
+      <c r="S78">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S78">
+        <v>8.4164262871047999</v>
+      </c>
+      <c r="T78">
         <f t="shared" si="5"/>
-        <v>2.1564922500000003</v>
-      </c>
-      <c r="T78">
-        <f t="shared" si="6"/>
-        <v>4.4639389575000001E-2</v>
+        <v>0.17422002414306934</v>
       </c>
       <c r="U78">
-        <f t="shared" si="7"/>
-        <v>773.93541675656252</v>
+        <f>H78*T78*I78</f>
+        <v>3020.5396685804644</v>
       </c>
       <c r="AP78" s="20"/>
       <c r="AQ78" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AR78" s="19" t="s">
         <v>117</v>
@@ -32479,28 +32581,34 @@
       <c r="J79">
         <v>0</v>
       </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
       <c r="L79">
         <f>$AC$14</f>
         <v>0</v>
       </c>
+      <c r="N79">
+        <v>220</v>
+      </c>
       <c r="P79">
         <v>0.7</v>
       </c>
       <c r="Q79">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S79">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S79">
+        <v>5.1913799715999973</v>
+      </c>
+      <c r="T79">
         <f t="shared" si="5"/>
-        <v>1.9754302499999998</v>
-      </c>
-      <c r="T79">
-        <f t="shared" si="6"/>
-        <v>4.0891406174999992E-2</v>
+        <v>0.10746156541211994</v>
       </c>
       <c r="U79">
-        <f t="shared" si="7"/>
-        <v>727.61145862640603</v>
+        <f>H79*T79*I79</f>
+        <v>1912.1442295519091</v>
       </c>
       <c r="AP79" s="18"/>
       <c r="AQ79" s="20"/>
@@ -32551,28 +32659,34 @@
       <c r="J80">
         <v>0.1</v>
       </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
       <c r="L80">
         <f>$AC$14</f>
         <v>0</v>
       </c>
+      <c r="N80">
+        <v>260</v>
+      </c>
       <c r="P80">
         <v>0.4</v>
       </c>
       <c r="Q80">
+        <f t="shared" si="3"/>
+        <v>1.03</v>
+      </c>
+      <c r="S80">
         <f t="shared" si="4"/>
-        <v>0.9</v>
-      </c>
-      <c r="S80">
+        <v>5.5230542678880008</v>
+      </c>
+      <c r="T80">
         <f t="shared" si="5"/>
-        <v>1.5468489000000001</v>
-      </c>
-      <c r="T80">
-        <f t="shared" si="6"/>
-        <v>3.201977223E-2</v>
+        <v>0.11432722334528161</v>
       </c>
       <c r="U80">
-        <f t="shared" si="7"/>
-        <v>584.3608431975</v>
+        <f>H80*T80*I80</f>
+        <v>2086.4718260513891</v>
       </c>
       <c r="AP80" s="20"/>
       <c r="AQ80" s="18"/>
@@ -32626,28 +32740,34 @@
       <c r="J81">
         <v>0.9</v>
       </c>
+      <c r="K81">
+        <v>0.05</v>
+      </c>
       <c r="L81">
         <f>$AC$12</f>
         <v>1.3</v>
       </c>
+      <c r="N81">
+        <v>440</v>
+      </c>
       <c r="P81">
         <v>0.3</v>
       </c>
       <c r="Q81">
+        <f t="shared" si="3"/>
+        <v>1.3250000000000002</v>
+      </c>
+      <c r="S81">
         <f t="shared" si="4"/>
-        <v>1.27</v>
-      </c>
-      <c r="S81">
+        <v>10.194064503570003</v>
+      </c>
+      <c r="T81">
         <f t="shared" si="5"/>
-        <v>2.0791427175000003</v>
-      </c>
-      <c r="T81">
-        <f t="shared" si="6"/>
-        <v>4.3038254252250004E-2</v>
+        <v>0.21101713522389906</v>
       </c>
       <c r="U81">
-        <f t="shared" si="7"/>
-        <v>196.36203502589063</v>
+        <f>H81*T81*I81</f>
+        <v>962.76567945903957</v>
       </c>
       <c r="AQ81" s="20"/>
       <c r="AR81" s="8" t="s">
@@ -32686,7 +32806,7 @@
     </row>
     <row r="82" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E82" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F82" t="s">
         <v>119</v>
@@ -32699,29 +32819,35 @@
       </c>
       <c r="J82">
         <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0.9</v>
       </c>
       <c r="L82">
         <f>$AC$13</f>
         <v>1.1000000000000001</v>
       </c>
+      <c r="N82">
+        <v>470</v>
+      </c>
       <c r="P82">
         <v>0.3</v>
       </c>
       <c r="Q82">
+        <f t="shared" si="3"/>
+        <v>1.9900000000000002</v>
+      </c>
+      <c r="S82">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S82">
+        <v>16.038790824384005</v>
+      </c>
+      <c r="T82">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T82">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.33200297006474894</v>
       </c>
       <c r="U82">
-        <f t="shared" si="7"/>
-        <v>309.23155122187495</v>
+        <f>H82*T82*I82</f>
+        <v>3029.5271018408339</v>
       </c>
     </row>
     <row r="83" spans="5:54" x14ac:dyDescent="0.2">
@@ -32737,28 +32863,34 @@
       <c r="J83">
         <v>0</v>
       </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
       <c r="L83">
         <f>$AC$14</f>
         <v>0</v>
       </c>
+      <c r="N83">
+        <v>490</v>
+      </c>
       <c r="P83">
         <v>0.2</v>
       </c>
       <c r="Q83">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S83">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S83">
+        <v>8.1130407556000002</v>
+      </c>
+      <c r="T83">
         <f t="shared" si="5"/>
-        <v>1.557504</v>
-      </c>
-      <c r="T83">
-        <f t="shared" si="6"/>
-        <v>3.22403328E-2</v>
+        <v>0.16793994364092002</v>
       </c>
       <c r="U83">
-        <f t="shared" si="7"/>
-        <v>264.77373311999997</v>
+        <f>H83*T83*I83</f>
+        <v>1379.2067871510558</v>
       </c>
     </row>
     <row r="84" spans="5:54" x14ac:dyDescent="0.2">
@@ -32774,28 +32906,34 @@
       <c r="J84">
         <v>0</v>
       </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
       <c r="L84">
         <f>$AC$14</f>
         <v>0</v>
       </c>
+      <c r="N84">
+        <v>500</v>
+      </c>
       <c r="P84">
         <v>0.1</v>
       </c>
       <c r="Q84">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S84">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S84">
+        <v>8.0457322500000004</v>
+      </c>
+      <c r="T84">
         <f t="shared" si="5"/>
-        <v>1.4798722500000003</v>
-      </c>
-      <c r="T84">
-        <f t="shared" si="6"/>
-        <v>3.0633355575000007E-2</v>
+        <v>0.16654665757500001</v>
       </c>
       <c r="U84">
-        <f t="shared" si="7"/>
-        <v>223.62349569750006</v>
+        <f>H84*T84*I84</f>
+        <v>1215.7906002975001</v>
       </c>
     </row>
     <row r="85" spans="5:54" x14ac:dyDescent="0.2">
@@ -32814,27 +32952,33 @@
       <c r="J85">
         <v>0</v>
       </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
       <c r="L85">
         <v>0</v>
+      </c>
+      <c r="N85">
+        <v>380</v>
       </c>
       <c r="P85">
         <v>0.4</v>
       </c>
       <c r="Q85">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S85">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S85">
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="T85">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T85">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.14654862619631992</v>
       </c>
       <c r="U85">
-        <f t="shared" si="7"/>
-        <v>97.393473866250005</v>
+        <f>H85*T85*I85</f>
+        <v>401.17686421242576</v>
       </c>
     </row>
     <row r="86" spans="5:54" x14ac:dyDescent="0.2">
@@ -32853,27 +32997,33 @@
       <c r="J86">
         <v>0</v>
       </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
       <c r="L86">
         <v>0</v>
+      </c>
+      <c r="N86">
+        <v>420</v>
       </c>
       <c r="P86">
         <v>0.4</v>
       </c>
       <c r="Q86">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S86">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S86">
+        <v>7.6129639056</v>
+      </c>
+      <c r="T86">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T86">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.15758835284591999</v>
       </c>
       <c r="U86">
-        <f t="shared" si="7"/>
-        <v>227.25143902125001</v>
+        <f>H86*T86*I86</f>
+        <v>1006.5956038033139</v>
       </c>
     </row>
     <row r="87" spans="5:54" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -32889,27 +33039,33 @@
       <c r="J87">
         <v>0</v>
       </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
       <c r="L87">
         <v>0</v>
+      </c>
+      <c r="N87">
+        <v>450</v>
       </c>
       <c r="P87">
         <v>0.3</v>
       </c>
       <c r="Q87">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S87">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S87">
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="T87">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T87">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.16182465119999997</v>
       </c>
       <c r="U87">
-        <f t="shared" si="7"/>
-        <v>123.69262048874999</v>
+        <f>H87*T87*I87</f>
+        <v>590.65997687999993</v>
       </c>
       <c r="AS87" s="2" t="s">
         <v>173</v>
@@ -32955,63 +33111,69 @@
       <c r="J88">
         <v>0</v>
       </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
       <c r="L88">
         <v>0</v>
+      </c>
+      <c r="N88">
+        <v>460</v>
       </c>
       <c r="P88">
         <v>0.1</v>
       </c>
       <c r="Q88">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S88">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S88">
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="T88">
         <f t="shared" si="5"/>
-        <v>1.4798722500000003</v>
-      </c>
-      <c r="T88">
-        <f t="shared" si="6"/>
-        <v>3.0633355575000007E-2</v>
+        <v>0.15708386407931998</v>
       </c>
       <c r="U88">
-        <f t="shared" si="7"/>
-        <v>55.905873924375015</v>
+        <f>H88*T88*I88</f>
+        <v>286.67805194475898</v>
       </c>
       <c r="AQ88" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR88" t="s">
         <v>243</v>
       </c>
-      <c r="AR88" t="s">
+      <c r="AS88" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="AS88" s="2" t="s">
+      <c r="AT88" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="AT88" s="2" t="s">
+      <c r="AU88" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="AU88" s="2" t="s">
+      <c r="AV88" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="AV88" s="3" t="s">
+      <c r="AW88" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="AW88" s="2" t="s">
+      <c r="AX88" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="AX88" s="2" t="s">
+      <c r="AY88" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="AY88" s="2" t="s">
+      <c r="AZ88" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="AZ88" s="2" t="s">
+      <c r="BA88" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="BA88" s="2" t="s">
+      <c r="BB88" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="BB88" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="89" spans="5:54" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -33030,33 +33192,39 @@
       <c r="J89">
         <v>0</v>
       </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
       <c r="L89">
         <v>0</v>
+      </c>
+      <c r="N89">
+        <v>380</v>
       </c>
       <c r="P89">
         <v>0.4</v>
       </c>
       <c r="Q89">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S89">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S89">
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="T89">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T89">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.14654862619631992</v>
       </c>
       <c r="U89">
-        <f t="shared" si="7"/>
-        <v>97.393473866250005</v>
+        <f>H89*T89*I89</f>
+        <v>401.17686421242576</v>
       </c>
       <c r="X89" t="s">
         <v>130</v>
       </c>
       <c r="Y89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Z89" t="s">
         <v>113</v>
@@ -33071,43 +33239,43 @@
         <v>135</v>
       </c>
       <c r="AD89" t="s">
+        <v>255</v>
+      </c>
+      <c r="AE89" t="s">
         <v>256</v>
       </c>
-      <c r="AE89" t="s">
+      <c r="AF89" t="s">
         <v>257</v>
       </c>
-      <c r="AF89" t="s">
+      <c r="AG89" t="s">
         <v>258</v>
       </c>
-      <c r="AG89" t="s">
+      <c r="AH89" t="s">
         <v>259</v>
       </c>
-      <c r="AH89" t="s">
+      <c r="AI89" t="s">
         <v>260</v>
       </c>
-      <c r="AI89" t="s">
+      <c r="AJ89" t="s">
         <v>261</v>
       </c>
-      <c r="AJ89" t="s">
+      <c r="AK89" t="s">
         <v>262</v>
       </c>
-      <c r="AK89" t="s">
+      <c r="AL89" t="s">
         <v>263</v>
       </c>
-      <c r="AL89" t="s">
+      <c r="AM89" t="s">
         <v>264</v>
       </c>
-      <c r="AM89" t="s">
-        <v>265</v>
-      </c>
       <c r="AN89" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AP89" t="s">
         <v>113</v>
       </c>
       <c r="AQ89" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR89" t="s">
         <v>130</v>
@@ -33145,7 +33313,7 @@
     </row>
     <row r="90" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E90" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
         <v>119</v>
@@ -33159,27 +33327,33 @@
       <c r="J90">
         <v>0</v>
       </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
       <c r="L90">
         <v>0</v>
+      </c>
+      <c r="N90">
+        <v>420</v>
       </c>
       <c r="P90">
         <v>0.4</v>
       </c>
       <c r="Q90">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S90">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S90">
+        <v>7.6129639056</v>
+      </c>
+      <c r="T90">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T90">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.15758835284591999</v>
       </c>
       <c r="U90">
-        <f t="shared" si="7"/>
-        <v>324.64491288750003</v>
+        <f>H90*T90*I90</f>
+        <v>1437.9937197190197</v>
       </c>
       <c r="X90" s="9" t="s">
         <v>117</v>
@@ -33282,27 +33456,33 @@
       <c r="J91">
         <v>0</v>
       </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
       <c r="L91">
         <v>0</v>
+      </c>
+      <c r="N91">
+        <v>450</v>
       </c>
       <c r="P91">
         <v>0.3</v>
       </c>
       <c r="Q91">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S91">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S91">
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="T91">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T91">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.16182465119999997</v>
       </c>
       <c r="U91">
-        <f t="shared" si="7"/>
-        <v>123.69262048874999</v>
+        <f>H91*T91*I91</f>
+        <v>590.65997687999993</v>
       </c>
       <c r="X91" s="9" t="s">
         <v>119</v>
@@ -33403,26 +33583,32 @@
       <c r="J92">
         <v>0</v>
       </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
       <c r="L92">
         <v>0</v>
+      </c>
+      <c r="N92">
+        <v>460</v>
       </c>
       <c r="P92">
         <v>0.1</v>
       </c>
       <c r="Q92">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S92">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S92">
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="T92">
         <f t="shared" si="5"/>
-        <v>1.4798722500000003</v>
-      </c>
-      <c r="T92">
-        <f t="shared" si="6"/>
-        <v>3.0633355575000007E-2</v>
+        <v>0.15708386407931998</v>
       </c>
       <c r="U92">
-        <f t="shared" si="7"/>
+        <f>H92*T92*I92</f>
         <v>0</v>
       </c>
       <c r="X92" s="9" t="s">
@@ -33527,27 +33713,33 @@
       <c r="J93">
         <v>0</v>
       </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
       <c r="L93">
         <v>0</v>
+      </c>
+      <c r="N93">
+        <v>75</v>
       </c>
       <c r="P93">
         <v>0.5</v>
       </c>
       <c r="Q93">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S93">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S93">
+        <v>2.7834751406249998</v>
+      </c>
+      <c r="T93">
         <f t="shared" si="5"/>
-        <v>1.80230625</v>
-      </c>
-      <c r="T93">
-        <f t="shared" si="6"/>
-        <v>3.7307739374999996E-2</v>
+        <v>5.7617935410937494E-2</v>
       </c>
       <c r="U93">
-        <f t="shared" si="7"/>
-        <v>68.086624359374994</v>
+        <f>H93*T93*I93</f>
+        <v>105.15273212496092</v>
       </c>
       <c r="X93" s="9" t="s">
         <v>121</v>
@@ -33640,7 +33832,7 @@
     </row>
     <row r="94" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E94" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F94" t="s">
         <v>119</v>
@@ -33654,27 +33846,33 @@
       <c r="J94">
         <v>0</v>
       </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
       <c r="L94">
         <v>0</v>
+      </c>
+      <c r="N94">
+        <v>160</v>
       </c>
       <c r="P94">
         <v>0.9</v>
       </c>
       <c r="Q94">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S94">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S94">
+        <v>4.5298311556000002</v>
+      </c>
+      <c r="T94">
         <f t="shared" si="5"/>
-        <v>2.1564922500000003</v>
-      </c>
-      <c r="T94">
-        <f t="shared" si="6"/>
-        <v>4.4639389575000001E-2</v>
+        <v>9.3767504920920008E-2</v>
       </c>
       <c r="U94">
-        <f t="shared" si="7"/>
-        <v>162.93377194875001</v>
+        <f>H94*T94*I94</f>
+        <v>342.25139296135802</v>
       </c>
       <c r="X94" s="9" t="s">
         <v>117</v>
@@ -33777,27 +33975,33 @@
       <c r="J95">
         <v>0</v>
       </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
       <c r="L95">
         <v>0</v>
+      </c>
+      <c r="N95">
+        <v>220</v>
       </c>
       <c r="P95">
         <v>0.7</v>
       </c>
       <c r="Q95">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S95">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S95">
+        <v>5.1913799715999973</v>
+      </c>
+      <c r="T95">
         <f t="shared" si="5"/>
-        <v>1.9754302499999998</v>
-      </c>
-      <c r="T95">
-        <f t="shared" si="6"/>
-        <v>4.0891406174999992E-2</v>
+        <v>0.10746156541211994</v>
       </c>
       <c r="U95">
-        <f t="shared" si="7"/>
-        <v>130.59692847140622</v>
+        <f>H95*T95*I95</f>
+        <v>343.20537453495803</v>
       </c>
       <c r="X95" s="9" t="s">
         <v>119</v>
@@ -33898,27 +34102,33 @@
       <c r="J96">
         <v>0</v>
       </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
       <c r="L96">
         <v>0</v>
+      </c>
+      <c r="N96">
+        <v>260</v>
       </c>
       <c r="P96">
         <v>0.4</v>
       </c>
       <c r="Q96">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S96">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S96">
+        <v>5.3621886096000004</v>
+      </c>
+      <c r="T96">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T96">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.11099730421872001</v>
       </c>
       <c r="U96">
-        <f t="shared" si="7"/>
-        <v>97.393473866250005</v>
+        <f>H96*T96*I96</f>
+        <v>303.85512029874604</v>
       </c>
       <c r="X96" s="9" t="s">
         <v>120</v>
@@ -34022,27 +34232,33 @@
       <c r="J97">
         <v>0</v>
       </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
       <c r="L97">
         <v>0</v>
+      </c>
+      <c r="N97">
+        <v>380</v>
       </c>
       <c r="P97">
         <v>0.4</v>
       </c>
       <c r="Q97">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S97">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S97">
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="T97">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T97">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.14654862619631992</v>
       </c>
       <c r="U97">
-        <f t="shared" si="7"/>
-        <v>97.393473866250005</v>
+        <f>H97*T97*I97</f>
+        <v>401.17686421242576</v>
       </c>
       <c r="X97" s="9" t="s">
         <v>121</v>
@@ -34135,7 +34351,7 @@
     </row>
     <row r="98" spans="5:54" x14ac:dyDescent="0.2">
       <c r="E98" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F98" t="s">
         <v>119</v>
@@ -34149,27 +34365,33 @@
       <c r="J98">
         <v>0</v>
       </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
       <c r="L98">
         <v>0</v>
+      </c>
+      <c r="N98">
+        <v>420</v>
       </c>
       <c r="P98">
         <v>0.4</v>
       </c>
       <c r="Q98">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S98">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S98">
+        <v>7.6129639056</v>
+      </c>
+      <c r="T98">
         <f t="shared" si="5"/>
-        <v>1.7187209999999999</v>
-      </c>
-      <c r="T98">
-        <f t="shared" si="6"/>
-        <v>3.5577524700000002E-2</v>
+        <v>0.15758835284591999</v>
       </c>
       <c r="U98">
-        <f t="shared" si="7"/>
-        <v>113.625719510625</v>
+        <f>H98*T98*I98</f>
+        <v>503.29780190165695</v>
       </c>
       <c r="X98" s="9" t="s">
         <v>117</v>
@@ -34272,27 +34494,33 @@
       <c r="J99">
         <v>0</v>
       </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
       <c r="L99">
         <v>0</v>
+      </c>
+      <c r="N99">
+        <v>450</v>
       </c>
       <c r="P99">
         <v>0.3</v>
       </c>
       <c r="Q99">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S99">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S99">
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="T99">
         <f t="shared" si="5"/>
-        <v>1.6371202500000002</v>
-      </c>
-      <c r="T99">
-        <f t="shared" si="6"/>
-        <v>3.3888389174999999E-2</v>
+        <v>0.16182465119999997</v>
       </c>
       <c r="U99">
-        <f t="shared" si="7"/>
-        <v>61.846310244374997</v>
+        <f>H99*T99*I99</f>
+        <v>295.32998843999997</v>
       </c>
       <c r="X99" s="9" t="s">
         <v>119</v>
@@ -34393,26 +34621,32 @@
       <c r="J100">
         <v>0</v>
       </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
       <c r="L100">
         <v>0</v>
+      </c>
+      <c r="N100">
+        <v>460</v>
       </c>
       <c r="P100">
         <v>0.1</v>
       </c>
       <c r="Q100">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="S100">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="S100">
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="T100">
         <f t="shared" si="5"/>
-        <v>1.4798722500000003</v>
-      </c>
-      <c r="T100">
-        <f t="shared" si="6"/>
-        <v>3.0633355575000007E-2</v>
+        <v>0.15708386407931998</v>
       </c>
       <c r="U100">
-        <f t="shared" si="7"/>
+        <f>H100*T100*I100</f>
         <v>0</v>
       </c>
       <c r="X100" s="9" t="s">
@@ -34997,7 +35231,7 @@
         <v>1</v>
       </c>
       <c r="AQ106" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR106" s="4" t="s">
         <v>117</v>
@@ -35350,7 +35584,7 @@
         <v>1</v>
       </c>
       <c r="AQ110" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AR110" s="4" t="s">
         <v>117</v>
@@ -35703,7 +35937,7 @@
         <v>1</v>
       </c>
       <c r="AQ114" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR114" s="4" t="s">
         <v>117</v>
@@ -36053,7 +36287,7 @@
         <v>1</v>
       </c>
       <c r="AQ118" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AR118" s="4" t="s">
         <v>117</v>
@@ -36397,7 +36631,7 @@
         <v>1</v>
       </c>
       <c r="AQ122" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AR122" s="4" t="s">
         <v>117</v>
@@ -36744,7 +36978,7 @@
         <v>1</v>
       </c>
       <c r="AQ126" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AR126" s="4" t="s">
         <v>117</v>
@@ -37028,7 +37262,7 @@
     </row>
     <row r="130" spans="24:54" x14ac:dyDescent="0.2">
       <c r="AQ130" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AR130" s="4" t="s">
         <v>117</v>
@@ -37177,7 +37411,7 @@
     </row>
     <row r="134" spans="24:54" x14ac:dyDescent="0.2">
       <c r="AQ134" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AR134" s="4" t="s">
         <v>117</v>
@@ -37326,7 +37560,7 @@
     </row>
     <row r="138" spans="24:54" x14ac:dyDescent="0.2">
       <c r="AQ138" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AR138" s="4" t="s">
         <v>117</v>
@@ -37475,7 +37709,7 @@
     </row>
     <row r="142" spans="24:54" x14ac:dyDescent="0.2">
       <c r="AQ142" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AR142" s="4" t="s">
         <v>117</v>
@@ -37622,7 +37856,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="V2:V10 T11 S2:T10 N2:N10 L2:L10 P2:Q10 H2:J10" numberStoredAsText="1"/>
+    <ignoredError sqref="V2:V10 T11 S2:T10 N2:N10 L2:L10 P2:Q10 H2:J9 H10:I10" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="4">
     <tablePart r:id="rId1"/>
@@ -37647,21 +37881,21 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" ht="106" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F2" s="33" t="s">
         <v>294</v>
-      </c>
-      <c r="D1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E1" t="s">
-        <v>295</v>
-      </c>
-      <c r="F1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="2:6" ht="106" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F2" s="34" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
@@ -37669,7 +37903,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D3">
         <v>0.1</v>
@@ -37680,7 +37914,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D4">
         <v>0.7</v>
@@ -37694,10 +37928,10 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -37714,7 +37948,7 @@
         <v>2026</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -37731,7 +37965,7 @@
         <v>2026</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D7">
         <v>0.2</v>
@@ -37748,7 +37982,7 @@
         <v>2024</v>
       </c>
       <c r="C12" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D12">
         <v>0.05</v>
@@ -37763,7 +37997,7 @@
         <v>2024</v>
       </c>
       <c r="C13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D13">
         <v>0.05</v>
@@ -37778,7 +38012,7 @@
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D14">
         <v>0.3</v>
@@ -37793,7 +38027,7 @@
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D15">
         <v>0.25</v>
@@ -37808,7 +38042,7 @@
         <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D16">
         <v>0.15</v>
@@ -37823,7 +38057,7 @@
         <v>2024</v>
       </c>
       <c r="C17" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -37838,7 +38072,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -37857,7 +38091,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -37876,7 +38110,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -37895,7 +38129,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -37914,7 +38148,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -37933,7 +38167,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -37952,7 +38186,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -37971,7 +38205,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D25">
         <v>0.1</v>
@@ -37990,7 +38224,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D26">
         <v>0.2</v>
@@ -38009,7 +38243,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D27">
         <v>0.3</v>
@@ -38028,7 +38262,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D28">
         <v>0.2</v>
@@ -38047,7 +38281,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D29">
         <v>0</v>

--- a/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/3.2-beef-enteric/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1F9E8A58-2811-CC46-A109-87D78632EB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{A9CDA150-C7B8-344A-B152-B20469EC9742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51220" yWindow="14300" windowWidth="28800" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.2.1 methane" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="311">
   <si>
     <t>EFPRP</t>
   </si>
@@ -982,6 +982,42 @@
   </si>
   <si>
     <t>FA (previous season)</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>December</t>
   </si>
 </sst>
 </file>
@@ -25612,7 +25648,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:BB750"/>
+  <dimension ref="A2:BB890"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -25855,7 +25891,7 @@
       <c r="Q10" t="s">
         <v>227</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="1" t="s">
         <v>270</v>
       </c>
       <c r="S10" t="s">
@@ -31060,7 +31096,7 @@
       </c>
       <c r="V61">
         <f>SUM(U61:U100)/1000</f>
-        <v>46.421829506520886</v>
+        <v>46.216817336068232</v>
       </c>
       <c r="X61" s="9" t="s">
         <v>119</v>
@@ -31716,7 +31752,7 @@
         <v>91.25</v>
       </c>
       <c r="I68">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -31747,7 +31783,7 @@
       </c>
       <c r="U68">
         <f>H68*T68*I68</f>
-        <v>981.96125589155668</v>
+        <v>818.30104657629727</v>
       </c>
       <c r="AP68" s="21"/>
       <c r="AQ68" s="19"/>
@@ -32432,7 +32468,7 @@
         <v>91.25</v>
       </c>
       <c r="I77">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -32463,7 +32499,7 @@
       </c>
       <c r="U77">
         <f>H77*T77*I77</f>
-        <v>525.76366062480463</v>
+        <v>578.3400266872851</v>
       </c>
       <c r="AP77" s="19"/>
       <c r="AQ77" s="21"/>
@@ -32751,7 +32787,7 @@
         <v>50</v>
       </c>
       <c r="J81">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K81">
         <v>0.05</v>
@@ -32768,19 +32804,19 @@
       </c>
       <c r="Q81">
         <f t="shared" si="7"/>
-        <v>1.2750000000000001</v>
+        <v>1.2449999999999999</v>
       </c>
       <c r="S81">
         <f t="shared" si="5"/>
-        <v>9.8093828241900027</v>
+        <v>9.5785738165620007</v>
       </c>
       <c r="T81">
         <f t="shared" si="6"/>
-        <v>0.20305422446073307</v>
+        <v>0.19827647800283341</v>
       </c>
       <c r="U81">
         <f>H81*T81*I81</f>
-        <v>926.43489910209473</v>
+        <v>904.63643088792742</v>
       </c>
       <c r="AQ81" s="21"/>
       <c r="AR81" s="8" t="s">
@@ -33005,7 +33041,7 @@
         <v>91.25</v>
       </c>
       <c r="I86">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -33036,7 +33072,7 @@
       </c>
       <c r="U86">
         <f>H86*T86*I86</f>
-        <v>1006.5956038033139</v>
+        <v>862.79623183141189</v>
       </c>
     </row>
     <row r="87" spans="5:54" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33591,7 +33627,7 @@
         <v>91.25</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -33622,7 +33658,7 @@
       </c>
       <c r="U92">
         <f>H92*T92*I92</f>
-        <v>0</v>
+        <v>71.669512986189744</v>
       </c>
       <c r="X92" s="9" t="s">
         <v>120</v>
@@ -35693,7 +35729,7 @@
       </c>
       <c r="V111">
         <f>SUM(U111:U150)/1000</f>
-        <v>46.421829506520886</v>
+        <v>46.549475629774207</v>
       </c>
       <c r="X111" s="9" t="s">
         <v>119</v>
@@ -35810,7 +35846,7 @@
         <v>1</v>
       </c>
       <c r="Q112">
-        <f t="shared" ref="Q112:Q150" si="8">(J112 * $AD$4 + K112*$AD$5) + (1 - J112 )</f>
+        <f t="shared" ref="Q112:Q122" si="8">(J112 * $AD$4 + K112*$AD$5) + (1 - J112 )</f>
         <v>1</v>
       </c>
       <c r="S112">
@@ -37597,7 +37633,7 @@
         <v>91.25</v>
       </c>
       <c r="I126">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="J126">
         <v>0.1</v>
@@ -37629,7 +37665,7 @@
       </c>
       <c r="U126">
         <f>H126*T126*I126</f>
-        <v>3130.6607957660631</v>
+        <v>3287.1938355543662</v>
       </c>
       <c r="X126" s="9" t="s">
         <v>117</v>
@@ -37848,7 +37884,7 @@
         <v>91.25</v>
       </c>
       <c r="I128">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -37879,7 +37915,7 @@
       </c>
       <c r="U128">
         <f>H128*T128*I128</f>
-        <v>1625.6941165664505</v>
+        <v>1540.131268326111</v>
       </c>
       <c r="X128" s="9" t="s">
         <v>120</v>
@@ -38260,7 +38296,7 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L132">
         <f>$AC$13</f>
@@ -38274,19 +38310,19 @@
       </c>
       <c r="Q132">
         <f t="shared" si="11"/>
-        <v>1.0900000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="S132">
         <f t="shared" si="9"/>
-        <v>8.7850663309440016</v>
+        <v>8.7044693921280025</v>
       </c>
       <c r="T132">
         <f t="shared" si="10"/>
-        <v>0.18185087305054082</v>
+        <v>0.18018251641704963</v>
       </c>
       <c r="U132">
         <f>H132*T132*I132</f>
-        <v>1659.3892165861848</v>
+        <v>1644.1654623055779</v>
       </c>
       <c r="AQ132" s="6"/>
       <c r="AR132" s="4" t="s">
@@ -38572,7 +38608,7 @@
         <v>91.25</v>
       </c>
       <c r="I136">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -38603,7 +38639,7 @@
       </c>
       <c r="U136">
         <f>H136*T136*I136</f>
-        <v>1006.5956038033139</v>
+        <v>934.6959178173629</v>
       </c>
       <c r="AQ136" s="6"/>
       <c r="AR136" s="4" t="s">
@@ -38887,7 +38923,7 @@
         <v>91.25</v>
       </c>
       <c r="I140">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -38918,7 +38954,7 @@
       </c>
       <c r="U140">
         <f>H140*T140*I140</f>
-        <v>1437.9937197190197</v>
+        <v>1581.7930916909218</v>
       </c>
       <c r="AQ140" s="6"/>
       <c r="AR140" s="4" t="s">
@@ -39622,7 +39658,7 @@
       </c>
       <c r="V161">
         <f>SUM(U161:U200)/1000</f>
-        <v>44.791119269331546</v>
+        <v>44.850616431779741</v>
       </c>
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.2">
@@ -39654,7 +39690,7 @@
         <v>0.77</v>
       </c>
       <c r="Q162">
-        <f t="shared" ref="Q162:Q200" si="13">(J162 * $AD$4 + K162*$AD$5) + (1 - J162 )</f>
+        <f t="shared" ref="Q162:Q172" si="13">(J162 * $AD$4 + K162*$AD$5) + (1 - J162 )</f>
         <v>1</v>
       </c>
       <c r="S162">
@@ -39894,7 +39930,7 @@
         <v>91.25</v>
       </c>
       <c r="I168">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -39925,7 +39961,7 @@
       </c>
       <c r="U168">
         <f>H168*T168*I168</f>
-        <v>1081.4097617324996</v>
+        <v>1261.6447220212497</v>
       </c>
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.2">
@@ -40202,7 +40238,7 @@
         <v>91.25</v>
       </c>
       <c r="I175">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -40234,7 +40270,7 @@
       </c>
       <c r="U175">
         <f>H175*T175*I175</f>
-        <v>2897.7071481731246</v>
+        <v>2776.969350332578</v>
       </c>
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.2">
@@ -41388,7 +41424,7 @@
       </c>
       <c r="V211">
         <f>SUM(U211:U250)/1000</f>
-        <v>47.428222776174991</v>
+        <v>47.430666915396166</v>
       </c>
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.2">
@@ -41420,7 +41456,7 @@
         <v>0.82</v>
       </c>
       <c r="Q212">
-        <f t="shared" ref="Q212:Q250" si="18">(J212 * $AD$4 + K212*$AD$5) + (1 - J212 )</f>
+        <f t="shared" ref="Q212:Q222" si="18">(J212 * $AD$4 + K212*$AD$5) + (1 - J212 )</f>
         <v>1</v>
       </c>
       <c r="S212">
@@ -41931,7 +41967,7 @@
         <v>0</v>
       </c>
       <c r="K224">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="L224">
         <f>$AC$13</f>
@@ -41945,19 +41981,19 @@
       </c>
       <c r="Q224">
         <f t="shared" ref="Q224:Q236" si="21">(J224 * $AD$4 +K224* $AD$5) + (1 -J224 - K224 )</f>
-        <v>1.0710000000000002</v>
+        <v>1.0649999999999999</v>
       </c>
       <c r="S224">
         <f t="shared" si="19"/>
-        <v>10.780781044931102</v>
+        <v>10.720384512466499</v>
       </c>
       <c r="T224">
         <f t="shared" si="20"/>
-        <v>0.22316216763007382</v>
+        <v>0.2219119594080565</v>
       </c>
       <c r="U224">
         <f>H224*T224*I224</f>
-        <v>5090.8869490610596</v>
+        <v>5062.3665739962889</v>
       </c>
     </row>
     <row r="225" spans="5:21" x14ac:dyDescent="0.2">
@@ -42102,7 +42138,7 @@
         <v>91.25</v>
       </c>
       <c r="I228">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -42133,7 +42169,7 @@
       </c>
       <c r="U228">
         <f>H228*T228*I228</f>
-        <v>1480.6104621533159</v>
+        <v>1558.5373285824378</v>
       </c>
     </row>
     <row r="229" spans="5:21" x14ac:dyDescent="0.2">
@@ -42844,7 +42880,7 @@
         <v>91.25</v>
       </c>
       <c r="I245">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -42875,7 +42911,7 @@
       </c>
       <c r="U245">
         <f>H245*T245*I245</f>
-        <v>328.73646500221179</v>
+        <v>281.77411285903867</v>
       </c>
     </row>
     <row r="246" spans="5:21" x14ac:dyDescent="0.2">
@@ -43159,7 +43195,7 @@
       </c>
       <c r="V261">
         <f>SUM(U261:U300)/1000</f>
-        <v>47.331386886781324</v>
+        <v>47.31539830102588</v>
       </c>
     </row>
     <row r="262" spans="1:22" x14ac:dyDescent="0.2">
@@ -43191,7 +43227,7 @@
         <v>0.44</v>
       </c>
       <c r="Q262">
-        <f t="shared" ref="Q262:Q300" si="23">(J262 * $AD$4 + K262*$AD$5) + (1 - J262 )</f>
+        <f t="shared" ref="Q262:Q272" si="23">(J262 * $AD$4 + K262*$AD$5) + (1 - J262 )</f>
         <v>1</v>
       </c>
       <c r="S262">
@@ -43389,7 +43425,7 @@
         <v>91.25</v>
       </c>
       <c r="I267">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -43420,7 +43456,7 @@
       </c>
       <c r="U267">
         <f>H267*T267*I267</f>
-        <v>1246.1395857975538</v>
+        <v>1157.1296153834428</v>
       </c>
     </row>
     <row r="268" spans="1:22" x14ac:dyDescent="0.2">
@@ -43785,7 +43821,7 @@
         <v>200</v>
       </c>
       <c r="J276">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -43802,19 +43838,19 @@
       </c>
       <c r="Q276">
         <f t="shared" si="26"/>
-        <v>1.03</v>
+        <v>1.0449999999999999</v>
       </c>
       <c r="S276">
         <f t="shared" si="24"/>
-        <v>8.1909139081029991</v>
+        <v>8.3101990621044983</v>
       </c>
       <c r="T276">
         <f t="shared" si="25"/>
-        <v>0.16955191789773208</v>
+        <v>0.1720211205855631</v>
       </c>
       <c r="U276">
         <f>H276*T276*I276</f>
-        <v>3094.3225016336105</v>
+        <v>3139.3854506865264</v>
       </c>
     </row>
     <row r="277" spans="5:21" x14ac:dyDescent="0.2">
@@ -43915,7 +43951,7 @@
         <v>91.25</v>
       </c>
       <c r="I279">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J279">
         <v>0</v>
@@ -43946,7 +43982,7 @@
       </c>
       <c r="U279">
         <f>H279*T279*I279</f>
-        <v>1090.378988624484</v>
+        <v>1118.33742423024</v>
       </c>
     </row>
     <row r="280" spans="5:21" x14ac:dyDescent="0.2">
@@ -44930,7 +44966,7 @@
       </c>
       <c r="V311">
         <f>SUM(U311:U350)/1000</f>
-        <v>40.479903884629458</v>
+        <v>40.259432875035088</v>
       </c>
     </row>
     <row r="312" spans="1:22" x14ac:dyDescent="0.2">
@@ -44962,7 +44998,7 @@
         <v>0.77</v>
       </c>
       <c r="Q312">
-        <f t="shared" ref="Q312:Q350" si="28">(J312 * $AD$4 + K312*$AD$5) + (1 - J312 )</f>
+        <f t="shared" ref="Q312:Q322" si="28">(J312 * $AD$4 + K312*$AD$5) + (1 - J312 )</f>
         <v>1</v>
       </c>
       <c r="S312">
@@ -45028,7 +45064,7 @@
         <v>91.25</v>
       </c>
       <c r="I314">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J314">
         <v>0</v>
@@ -45059,7 +45095,7 @@
       </c>
       <c r="U314">
         <f>H314*T314*I314</f>
-        <v>655.63734639060033</v>
+        <v>702.46858541850031</v>
       </c>
     </row>
     <row r="315" spans="1:22" x14ac:dyDescent="0.2">
@@ -45202,7 +45238,7 @@
         <v>91.25</v>
       </c>
       <c r="I318">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J318">
         <v>0</v>
@@ -45233,7 +45269,7 @@
       </c>
       <c r="U318">
         <f>H318*T318*I318</f>
-        <v>784.95314199328141</v>
+        <v>719.54038016050799</v>
       </c>
     </row>
     <row r="319" spans="1:22" x14ac:dyDescent="0.2">
@@ -45376,7 +45412,7 @@
         <v>91.25</v>
       </c>
       <c r="I322">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J322">
         <v>0</v>
@@ -45407,7 +45443,7 @@
       </c>
       <c r="U322">
         <f>H322*T322*I322</f>
-        <v>1832.9165601501425</v>
+        <v>1775.6379176454504</v>
       </c>
     </row>
     <row r="323" spans="5:21" x14ac:dyDescent="0.2">
@@ -45825,7 +45861,7 @@
         <v>0</v>
       </c>
       <c r="K332">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L332">
         <f>$AC$13</f>
@@ -45839,19 +45875,19 @@
       </c>
       <c r="Q332">
         <f t="shared" si="31"/>
-        <v>1.0900000000000001</v>
+        <v>1.085</v>
       </c>
       <c r="S332">
         <f t="shared" si="29"/>
-        <v>7.6874314199489993</v>
+        <v>7.6521679730684991</v>
       </c>
       <c r="T332">
         <f t="shared" si="30"/>
-        <v>0.15912983039294429</v>
+        <v>0.15839987704251793</v>
       </c>
       <c r="U332">
         <f>H332*T332*I332</f>
-        <v>1452.0597023356165</v>
+        <v>1445.398878012976</v>
       </c>
     </row>
     <row r="333" spans="5:21" x14ac:dyDescent="0.2">
@@ -46038,7 +46074,7 @@
         <v>91.25</v>
       </c>
       <c r="I337">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -46069,7 +46105,7 @@
       </c>
       <c r="U337">
         <f>H337*T337*I337</f>
-        <v>551.80007984863801</v>
+        <v>413.85005988647856</v>
       </c>
     </row>
     <row r="338" spans="5:21" x14ac:dyDescent="0.2">
@@ -46701,7 +46737,7 @@
       </c>
       <c r="V361">
         <f>SUM(U361:U400)/1000</f>
-        <v>38.193353027275023</v>
+        <v>38.608465234425331</v>
       </c>
     </row>
     <row r="362" spans="1:22" x14ac:dyDescent="0.2">
@@ -46733,7 +46769,7 @@
         <v>0.8</v>
       </c>
       <c r="Q362">
-        <f t="shared" ref="Q362:Q400" si="33">(J362 * $AD$4 + K362*$AD$5) + (1 - J362 )</f>
+        <f t="shared" ref="Q362:Q372" si="33">(J362 * $AD$4 + K362*$AD$5) + (1 - J362 )</f>
         <v>1</v>
       </c>
       <c r="S362">
@@ -46844,7 +46880,7 @@
         <v>91.25</v>
       </c>
       <c r="I365">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J365">
         <v>0</v>
@@ -46875,7 +46911,7 @@
       </c>
       <c r="U365">
         <f>H365*T365*I365</f>
-        <v>261.65104733109382</v>
+        <v>392.4765709966407</v>
       </c>
     </row>
     <row r="366" spans="1:22" x14ac:dyDescent="0.2">
@@ -47147,7 +47183,7 @@
         <v>91.25</v>
       </c>
       <c r="I372">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J372">
         <v>0</v>
@@ -47178,7 +47214,7 @@
       </c>
       <c r="U372">
         <f>H372*T372*I372</f>
-        <v>1580.7359427530218</v>
+        <v>1679.5319391750857</v>
       </c>
     </row>
     <row r="373" spans="5:21" x14ac:dyDescent="0.2">
@@ -47809,7 +47845,7 @@
         <v>91.25</v>
       </c>
       <c r="I387">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J387">
         <v>0</v>
@@ -47840,7 +47876,7 @@
       </c>
       <c r="U387">
         <f>H387*T387*I387</f>
-        <v>604.98842987717558</v>
+        <v>680.61198361182255</v>
       </c>
     </row>
     <row r="388" spans="5:21" x14ac:dyDescent="0.2">
@@ -48373,7 +48409,7 @@
         <v>91.25</v>
       </c>
       <c r="I400">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J400">
         <v>0</v>
@@ -48404,7 +48440,7 @@
       </c>
       <c r="U400">
         <f>H400*T400*I400</f>
-        <v>0</v>
+        <v>109.86713332804686</v>
       </c>
     </row>
     <row r="403" spans="1:22" x14ac:dyDescent="0.2">
@@ -48504,7 +48540,7 @@
         <v>0.66</v>
       </c>
       <c r="Q412">
-        <f t="shared" ref="Q412:Q450" si="38">(J412 * $AD$4 + K412*$AD$5) + (1 - J412 )</f>
+        <f t="shared" ref="Q412:Q422" si="38">(J412 * $AD$4 + K412*$AD$5) + (1 - J412 )</f>
         <v>1</v>
       </c>
       <c r="S412">
@@ -50275,7 +50311,7 @@
         <v>0.66</v>
       </c>
       <c r="Q462">
-        <f t="shared" ref="Q462:Q500" si="43">(J462 * $AD$4 + K462*$AD$5) + (1 - J462 )</f>
+        <f t="shared" ref="Q462:Q472" si="43">(J462 * $AD$4 + K462*$AD$5) + (1 - J462 )</f>
         <v>1</v>
       </c>
       <c r="S462">
@@ -52014,7 +52050,7 @@
       </c>
       <c r="V511">
         <f>SUM(U511:U550)/1000</f>
-        <v>36.393442264202982</v>
+        <v>36.210795981942951</v>
       </c>
     </row>
     <row r="512" spans="1:22" x14ac:dyDescent="0.2">
@@ -52046,7 +52082,7 @@
         <v>0.66</v>
       </c>
       <c r="Q512">
-        <f t="shared" ref="Q512:Q550" si="48">(J512 * $AD$4 + K512*$AD$5) + (1 - J512 )</f>
+        <f t="shared" ref="Q512:Q522" si="48">(J512 * $AD$4 + K512*$AD$5) + (1 - J512 )</f>
         <v>1</v>
       </c>
       <c r="S512">
@@ -52286,7 +52322,7 @@
         <v>91.25</v>
       </c>
       <c r="I518">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J518">
         <v>0</v>
@@ -52317,7 +52353,7 @@
       </c>
       <c r="U518">
         <f>H518*T518*I518</f>
-        <v>995.51847855536357</v>
+        <v>829.59873212946957</v>
       </c>
     </row>
     <row r="519" spans="5:21" x14ac:dyDescent="0.2">
@@ -52557,7 +52593,7 @@
         <v>0</v>
       </c>
       <c r="K524">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="L524">
         <f>$AC$13</f>
@@ -52571,19 +52607,19 @@
       </c>
       <c r="Q524">
         <f t="shared" ref="Q524:Q536" si="51">(J524 * $AD$4 +K524* $AD$5) + (1 -J524 - K524 )</f>
-        <v>1.0710000000000002</v>
+        <v>1.0649999999999999</v>
       </c>
       <c r="S524">
         <f t="shared" si="49"/>
-        <v>6.3226770355770165</v>
+        <v>6.2872558757138393</v>
       </c>
       <c r="T524">
         <f t="shared" si="50"/>
-        <v>0.13087941463644423</v>
+        <v>0.13014619662727647</v>
       </c>
       <c r="U524">
         <f>H524*T524*I524</f>
-        <v>2985.6866463938841</v>
+        <v>2968.9601105597444</v>
       </c>
     </row>
     <row r="525" spans="5:21" x14ac:dyDescent="0.2">
@@ -53817,7 +53853,7 @@
         <v>0.16</v>
       </c>
       <c r="Q562">
-        <f t="shared" ref="Q562:Q600" si="53">(J562 * $AD$4 + K562*$AD$5) + (1 - J562 )</f>
+        <f t="shared" ref="Q562:Q572" si="53">(J562 * $AD$4 + K562*$AD$5) + (1 - J562 )</f>
         <v>1</v>
       </c>
       <c r="S562">
@@ -55588,7 +55624,7 @@
         <v>0.65</v>
       </c>
       <c r="Q612">
-        <f t="shared" ref="Q612:Q650" si="58">(J612 * $AD$4 + K612*$AD$5) + (1 - J612 )</f>
+        <f t="shared" ref="Q612:Q622" si="58">(J612 * $AD$4 + K612*$AD$5) + (1 - J612 )</f>
         <v>1</v>
       </c>
       <c r="S612">
@@ -57362,7 +57398,7 @@
         <v>0.05</v>
       </c>
       <c r="Q662">
-        <f t="shared" ref="Q662:Q700" si="63">(J662 * $AD$4 + K662*$AD$5) + (1 - J662 )</f>
+        <f t="shared" ref="Q662:Q672" si="63">(J662 * $AD$4 + K662*$AD$5) + (1 - J662 )</f>
         <v>1</v>
       </c>
       <c r="S662">
@@ -59128,7 +59164,7 @@
         <v>0.62</v>
       </c>
       <c r="Q712">
-        <f t="shared" ref="Q712:Q750" si="68">(J712 * $AD$4 + K712*$AD$5) + (1 - J712 )</f>
+        <f t="shared" ref="Q712:Q722" si="68">(J712 * $AD$4 + K712*$AD$5) + (1 - J712 )</f>
         <v>1</v>
       </c>
       <c r="S712">
@@ -59652,7 +59688,7 @@
         <v>0.47</v>
       </c>
       <c r="Q724">
-        <f t="shared" ref="Q724:Q736" si="71">(J724 * $AD$4 +K724* $AD$5) + (1 -J724 - K724 )</f>
+        <f t="shared" ref="Q724:Q787" si="71">(J724 * $AD$4 +K724* $AD$5) + (1 -J724 - K724 )</f>
         <v>1.0710000000000002</v>
       </c>
       <c r="S724">
@@ -60222,7 +60258,7 @@
         <v>0.24</v>
       </c>
       <c r="Q737">
-        <f t="shared" ref="Q737:Q750" si="72">(J737 * $AD$4 + K737*$AD$5) + (1 - J737 )</f>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S737">
@@ -60264,7 +60300,7 @@
         <v>0.16</v>
       </c>
       <c r="Q738">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S738">
@@ -60309,7 +60345,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="Q739">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S739">
@@ -60354,7 +60390,7 @@
         <v>0.26</v>
       </c>
       <c r="Q740">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S740">
@@ -60396,7 +60432,7 @@
         <v>0.15</v>
       </c>
       <c r="Q741">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S741">
@@ -60438,7 +60474,7 @@
         <v>0.4</v>
       </c>
       <c r="Q742">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S742">
@@ -60483,7 +60519,7 @@
         <v>0.34</v>
       </c>
       <c r="Q743">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S743">
@@ -60528,7 +60564,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="Q744">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S744">
@@ -60570,7 +60606,7 @@
         <v>0.13</v>
       </c>
       <c r="Q745">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S745">
@@ -60612,7 +60648,7 @@
         <v>0.13</v>
       </c>
       <c r="Q746">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S746">
@@ -60657,7 +60693,7 @@
         <v>0.52</v>
       </c>
       <c r="Q747">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S747">
@@ -60702,7 +60738,7 @@
         <v>0.43</v>
       </c>
       <c r="Q748">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S748">
@@ -60744,7 +60780,7 @@
         <v>0.21</v>
       </c>
       <c r="Q749">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S749">
@@ -60786,7 +60822,7 @@
         <v>0.33</v>
       </c>
       <c r="Q750">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="S750">
@@ -60802,7 +60838,5405 @@
         <v>0</v>
       </c>
     </row>
+    <row r="771" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A771" t="s">
+        <v>264</v>
+      </c>
+      <c r="B771" t="s">
+        <v>232</v>
+      </c>
+      <c r="C771" t="s">
+        <v>264</v>
+      </c>
+      <c r="D771" t="s">
+        <v>264</v>
+      </c>
+      <c r="E771" t="s">
+        <v>116</v>
+      </c>
+      <c r="F771" t="s">
+        <v>299</v>
+      </c>
+      <c r="H771">
+        <v>31</v>
+      </c>
+      <c r="I771">
+        <v>100</v>
+      </c>
+      <c r="J771">
+        <v>0</v>
+      </c>
+      <c r="K771">
+        <v>0</v>
+      </c>
+      <c r="L771">
+        <v>0</v>
+      </c>
+      <c r="N771">
+        <f>$AM$91</f>
+        <v>119</v>
+      </c>
+      <c r="P771">
+        <f>$AM$25</f>
+        <v>0.62</v>
+      </c>
+      <c r="Q771">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S771">
+        <f>(1.185 + 0.00454 * N771- 0.0000026 * N771^2 + 0.315 * P771 )^2 * Q771</f>
+        <v>3.5484816620739603</v>
+      </c>
+      <c r="T771">
+        <f>20.7 * S771 * 10^-3</f>
+        <v>7.3453570404930973E-2</v>
+      </c>
+      <c r="U771">
+        <f>H771*T771*I771</f>
+        <v>227.706068255286</v>
+      </c>
+      <c r="V771">
+        <f>SUM(U771:U890)/1000</f>
+        <v>36.741561800938577</v>
+      </c>
+    </row>
+    <row r="772" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="E772">
+        <v>1</v>
+      </c>
+      <c r="F772" t="s">
+        <v>300</v>
+      </c>
+      <c r="H772">
+        <v>28</v>
+      </c>
+      <c r="I772">
+        <v>90</v>
+      </c>
+      <c r="J772">
+        <v>0</v>
+      </c>
+      <c r="K772">
+        <v>0</v>
+      </c>
+      <c r="L772">
+        <v>0</v>
+      </c>
+      <c r="N772">
+        <f>$AM$91</f>
+        <v>119</v>
+      </c>
+      <c r="P772">
+        <f>$AM$25</f>
+        <v>0.62</v>
+      </c>
+      <c r="Q772">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S772">
+        <f t="shared" ref="S772:S810" si="72">(1.185 + 0.00454 * N772- 0.0000026 * N772^2 + 0.315 * P772 )^2 * Q772</f>
+        <v>3.5484816620739603</v>
+      </c>
+      <c r="T772">
+        <f t="shared" ref="T772:T835" si="73">20.7 * S772 * 10^-3</f>
+        <v>7.3453570404930973E-2</v>
+      </c>
+      <c r="U772">
+        <f t="shared" ref="U772:U835" si="74">H772*T772*I772</f>
+        <v>185.10299742042605</v>
+      </c>
+    </row>
+    <row r="773" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F773" t="s">
+        <v>301</v>
+      </c>
+      <c r="G773" s="1">
+        <v>25</v>
+      </c>
+      <c r="H773" s="1">
+        <v>25</v>
+      </c>
+      <c r="I773">
+        <v>80</v>
+      </c>
+      <c r="J773">
+        <v>0</v>
+      </c>
+      <c r="K773">
+        <v>0</v>
+      </c>
+      <c r="L773">
+        <v>0</v>
+      </c>
+      <c r="N773">
+        <f>$AM$92</f>
+        <v>175</v>
+      </c>
+      <c r="P773">
+        <f>$AM$26</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q773">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S773">
+        <f t="shared" si="72"/>
+        <v>4.1041695156250002</v>
+      </c>
+      <c r="T773">
+        <f t="shared" si="73"/>
+        <v>8.4956308973437505E-2</v>
+      </c>
+      <c r="U773">
+        <f t="shared" si="74"/>
+        <v>169.912617946875</v>
+      </c>
+    </row>
+    <row r="774" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F774" t="s">
+        <v>302</v>
+      </c>
+      <c r="H774">
+        <v>30</v>
+      </c>
+      <c r="I774">
+        <v>80</v>
+      </c>
+      <c r="J774">
+        <v>0</v>
+      </c>
+      <c r="K774">
+        <v>0</v>
+      </c>
+      <c r="L774">
+        <v>0</v>
+      </c>
+      <c r="N774">
+        <f t="shared" ref="N774:N775" si="75">$AM$92</f>
+        <v>175</v>
+      </c>
+      <c r="P774">
+        <f t="shared" ref="P774:P775" si="76">$AM$26</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q774">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S774">
+        <f t="shared" si="72"/>
+        <v>4.1041695156250002</v>
+      </c>
+      <c r="T774">
+        <f t="shared" si="73"/>
+        <v>8.4956308973437505E-2</v>
+      </c>
+      <c r="U774">
+        <f t="shared" si="74"/>
+        <v>203.89514153625001</v>
+      </c>
+    </row>
+    <row r="775" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F775" t="s">
+        <v>303</v>
+      </c>
+      <c r="H775">
+        <v>31</v>
+      </c>
+      <c r="I775">
+        <v>75</v>
+      </c>
+      <c r="J775">
+        <v>0</v>
+      </c>
+      <c r="K775">
+        <v>0</v>
+      </c>
+      <c r="L775">
+        <v>0</v>
+      </c>
+      <c r="N775">
+        <f t="shared" si="75"/>
+        <v>175</v>
+      </c>
+      <c r="P775">
+        <f t="shared" si="76"/>
+        <v>0.4</v>
+      </c>
+      <c r="Q775">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S775">
+        <f t="shared" si="72"/>
+        <v>4.1041695156250002</v>
+      </c>
+      <c r="T775">
+        <f t="shared" si="73"/>
+        <v>8.4956308973437505E-2</v>
+      </c>
+      <c r="U775">
+        <f t="shared" si="74"/>
+        <v>197.5234183632422</v>
+      </c>
+    </row>
+    <row r="776" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F776" t="s">
+        <v>304</v>
+      </c>
+      <c r="H776">
+        <v>30</v>
+      </c>
+      <c r="I776">
+        <v>70</v>
+      </c>
+      <c r="J776">
+        <v>0</v>
+      </c>
+      <c r="K776">
+        <v>0</v>
+      </c>
+      <c r="L776">
+        <v>0</v>
+      </c>
+      <c r="N776">
+        <f>$AM$93</f>
+        <v>192</v>
+      </c>
+      <c r="P776">
+        <f>$AM$27</f>
+        <v>0.08</v>
+      </c>
+      <c r="Q776">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S776">
+        <f t="shared" si="72"/>
+        <v>3.9443294603289596</v>
+      </c>
+      <c r="T776">
+        <f t="shared" si="73"/>
+        <v>8.1647619828809456E-2</v>
+      </c>
+      <c r="U776">
+        <f t="shared" si="74"/>
+        <v>171.46000164049985</v>
+      </c>
+    </row>
+    <row r="777" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F777" t="s">
+        <v>305</v>
+      </c>
+      <c r="H777">
+        <v>31</v>
+      </c>
+      <c r="I777">
+        <v>60</v>
+      </c>
+      <c r="J777">
+        <v>0</v>
+      </c>
+      <c r="K777">
+        <v>0</v>
+      </c>
+      <c r="L777">
+        <v>0</v>
+      </c>
+      <c r="N777">
+        <f t="shared" ref="N777:N778" si="77">$AM$93</f>
+        <v>192</v>
+      </c>
+      <c r="P777">
+        <f t="shared" ref="P777:P778" si="78">$AM$27</f>
+        <v>0.08</v>
+      </c>
+      <c r="Q777">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S777">
+        <f t="shared" si="72"/>
+        <v>3.9443294603289596</v>
+      </c>
+      <c r="T777">
+        <f t="shared" si="73"/>
+        <v>8.1647619828809456E-2</v>
+      </c>
+      <c r="U777">
+        <f t="shared" si="74"/>
+        <v>151.86457288158559</v>
+      </c>
+    </row>
+    <row r="778" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F778" t="s">
+        <v>306</v>
+      </c>
+      <c r="H778">
+        <v>31</v>
+      </c>
+      <c r="I778">
+        <v>50</v>
+      </c>
+      <c r="J778">
+        <v>0</v>
+      </c>
+      <c r="K778">
+        <v>0</v>
+      </c>
+      <c r="L778">
+        <v>0</v>
+      </c>
+      <c r="N778">
+        <f t="shared" si="77"/>
+        <v>192</v>
+      </c>
+      <c r="P778">
+        <f t="shared" si="78"/>
+        <v>0.08</v>
+      </c>
+      <c r="Q778">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S778">
+        <f t="shared" si="72"/>
+        <v>3.9443294603289596</v>
+      </c>
+      <c r="T778">
+        <f t="shared" si="73"/>
+        <v>8.1647619828809456E-2</v>
+      </c>
+      <c r="U778">
+        <f t="shared" si="74"/>
+        <v>126.55381073465466</v>
+      </c>
+    </row>
+    <row r="779" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F779" t="s">
+        <v>307</v>
+      </c>
+      <c r="H779">
+        <v>30</v>
+      </c>
+      <c r="I779">
+        <v>50</v>
+      </c>
+      <c r="J779">
+        <v>0</v>
+      </c>
+      <c r="K779">
+        <v>0</v>
+      </c>
+      <c r="L779">
+        <v>0</v>
+      </c>
+      <c r="N779">
+        <f>$AM$90</f>
+        <v>190</v>
+      </c>
+      <c r="P779">
+        <f>$AM$24</f>
+        <v>-0.2</v>
+      </c>
+      <c r="Q779">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S779">
+        <f t="shared" si="72"/>
+        <v>3.5748977476000001</v>
+      </c>
+      <c r="T779">
+        <f t="shared" si="73"/>
+        <v>7.400038337532E-2</v>
+      </c>
+      <c r="U779">
+        <f t="shared" si="74"/>
+        <v>111.00057506298</v>
+      </c>
+    </row>
+    <row r="780" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F780" t="s">
+        <v>308</v>
+      </c>
+      <c r="H780">
+        <v>31</v>
+      </c>
+      <c r="I780">
+        <v>70</v>
+      </c>
+      <c r="J780">
+        <v>0</v>
+      </c>
+      <c r="K780">
+        <v>0</v>
+      </c>
+      <c r="L780">
+        <v>0</v>
+      </c>
+      <c r="N780">
+        <f t="shared" ref="N780:N782" si="79">$AM$90</f>
+        <v>190</v>
+      </c>
+      <c r="P780">
+        <f t="shared" ref="P780:P782" si="80">$AM$24</f>
+        <v>-0.2</v>
+      </c>
+      <c r="Q780">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S780">
+        <f t="shared" si="72"/>
+        <v>3.5748977476000001</v>
+      </c>
+      <c r="T780">
+        <f t="shared" si="73"/>
+        <v>7.400038337532E-2</v>
+      </c>
+      <c r="U780">
+        <f t="shared" si="74"/>
+        <v>160.58083192444442</v>
+      </c>
+    </row>
+    <row r="781" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F781" t="s">
+        <v>309</v>
+      </c>
+      <c r="H781">
+        <v>30</v>
+      </c>
+      <c r="I781">
+        <v>90</v>
+      </c>
+      <c r="J781">
+        <v>0</v>
+      </c>
+      <c r="K781">
+        <v>0</v>
+      </c>
+      <c r="L781">
+        <v>0</v>
+      </c>
+      <c r="N781">
+        <f t="shared" si="79"/>
+        <v>190</v>
+      </c>
+      <c r="P781">
+        <f t="shared" si="80"/>
+        <v>-0.2</v>
+      </c>
+      <c r="Q781">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S781">
+        <f t="shared" si="72"/>
+        <v>3.5748977476000001</v>
+      </c>
+      <c r="T781">
+        <f t="shared" si="73"/>
+        <v>7.400038337532E-2</v>
+      </c>
+      <c r="U781">
+        <f t="shared" si="74"/>
+        <v>199.80103511336401</v>
+      </c>
+    </row>
+    <row r="782" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="F782" t="s">
+        <v>310</v>
+      </c>
+      <c r="H782">
+        <v>31</v>
+      </c>
+      <c r="I782">
+        <v>95</v>
+      </c>
+      <c r="J782">
+        <v>0</v>
+      </c>
+      <c r="K782">
+        <v>0</v>
+      </c>
+      <c r="L782">
+        <v>0</v>
+      </c>
+      <c r="N782">
+        <f>$AM$91</f>
+        <v>119</v>
+      </c>
+      <c r="P782">
+        <f>$AM$25</f>
+        <v>0.62</v>
+      </c>
+      <c r="Q782">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S782">
+        <f t="shared" si="72"/>
+        <v>3.5484816620739603</v>
+      </c>
+      <c r="T782">
+        <f t="shared" si="73"/>
+        <v>7.3453570404930973E-2</v>
+      </c>
+      <c r="U782">
+        <f t="shared" si="74"/>
+        <v>216.3207648425217</v>
+      </c>
+    </row>
+    <row r="783" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="E783" t="s">
+        <v>122</v>
+      </c>
+      <c r="F783" t="s">
+        <v>299</v>
+      </c>
+      <c r="H783">
+        <v>31</v>
+      </c>
+      <c r="I783">
+        <v>80</v>
+      </c>
+      <c r="J783">
+        <v>0</v>
+      </c>
+      <c r="K783">
+        <v>0</v>
+      </c>
+      <c r="L783">
+        <v>0</v>
+      </c>
+      <c r="N783">
+        <f>$AM$95</f>
+        <v>591</v>
+      </c>
+      <c r="P783">
+        <f>$AM$29</f>
+        <v>0.21</v>
+      </c>
+      <c r="Q783">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S783">
+        <f t="shared" si="72"/>
+        <v>9.1576407142083571</v>
+      </c>
+      <c r="T783">
+        <f t="shared" si="73"/>
+        <v>0.189563162784113</v>
+      </c>
+      <c r="U783">
+        <f t="shared" si="74"/>
+        <v>470.11664370460028</v>
+      </c>
+    </row>
+    <row r="784" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="E784">
+        <v>2</v>
+      </c>
+      <c r="F784" t="s">
+        <v>300</v>
+      </c>
+      <c r="H784">
+        <v>28</v>
+      </c>
+      <c r="I784">
+        <v>75</v>
+      </c>
+      <c r="J784">
+        <v>0</v>
+      </c>
+      <c r="K784">
+        <v>0</v>
+      </c>
+      <c r="L784">
+        <v>0</v>
+      </c>
+      <c r="N784">
+        <f>$AM$95</f>
+        <v>591</v>
+      </c>
+      <c r="P784">
+        <f>$AM$29</f>
+        <v>0.21</v>
+      </c>
+      <c r="Q784">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S784">
+        <f t="shared" si="72"/>
+        <v>9.1576407142083571</v>
+      </c>
+      <c r="T784">
+        <f t="shared" si="73"/>
+        <v>0.189563162784113</v>
+      </c>
+      <c r="U784">
+        <f t="shared" si="74"/>
+        <v>398.08264184663733</v>
+      </c>
+    </row>
+    <row r="785" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F785" t="s">
+        <v>301</v>
+      </c>
+      <c r="H785">
+        <v>31</v>
+      </c>
+      <c r="I785">
+        <v>70</v>
+      </c>
+      <c r="J785">
+        <v>0</v>
+      </c>
+      <c r="K785">
+        <v>0</v>
+      </c>
+      <c r="L785">
+        <v>0</v>
+      </c>
+      <c r="N785">
+        <f>$AM$96</f>
+        <v>610</v>
+      </c>
+      <c r="P785">
+        <f>$AM$30</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q785">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S785">
+        <f t="shared" si="72"/>
+        <v>9.1681178520999982</v>
+      </c>
+      <c r="T785">
+        <f t="shared" si="73"/>
+        <v>0.18978003953846997</v>
+      </c>
+      <c r="U785">
+        <f t="shared" si="74"/>
+        <v>411.82268579847982</v>
+      </c>
+    </row>
+    <row r="786" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F786" t="s">
+        <v>302</v>
+      </c>
+      <c r="H786">
+        <v>30</v>
+      </c>
+      <c r="I786">
+        <v>70</v>
+      </c>
+      <c r="J786">
+        <v>0</v>
+      </c>
+      <c r="K786">
+        <v>0</v>
+      </c>
+      <c r="L786">
+        <v>0</v>
+      </c>
+      <c r="N786">
+        <f t="shared" ref="N786:N787" si="81">$AM$96</f>
+        <v>610</v>
+      </c>
+      <c r="P786">
+        <f t="shared" ref="P786:P787" si="82">$AM$30</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q786">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S786">
+        <f t="shared" si="72"/>
+        <v>9.1681178520999982</v>
+      </c>
+      <c r="T786">
+        <f t="shared" si="73"/>
+        <v>0.18978003953846997</v>
+      </c>
+      <c r="U786">
+        <f t="shared" si="74"/>
+        <v>398.53808303078694</v>
+      </c>
+    </row>
+    <row r="787" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F787" t="s">
+        <v>303</v>
+      </c>
+      <c r="G787" s="1">
+        <v>30</v>
+      </c>
+      <c r="H787" s="1">
+        <v>30</v>
+      </c>
+      <c r="I787">
+        <v>65</v>
+      </c>
+      <c r="J787">
+        <v>0</v>
+      </c>
+      <c r="K787">
+        <v>0</v>
+      </c>
+      <c r="L787">
+        <v>0</v>
+      </c>
+      <c r="N787">
+        <f t="shared" si="81"/>
+        <v>610</v>
+      </c>
+      <c r="P787">
+        <f t="shared" si="82"/>
+        <v>0.13</v>
+      </c>
+      <c r="Q787">
+        <f t="shared" si="71"/>
+        <v>1</v>
+      </c>
+      <c r="S787">
+        <f t="shared" si="72"/>
+        <v>9.1681178520999982</v>
+      </c>
+      <c r="T787">
+        <f t="shared" si="73"/>
+        <v>0.18978003953846997</v>
+      </c>
+      <c r="U787">
+        <f t="shared" si="74"/>
+        <v>370.07107710001645</v>
+      </c>
+    </row>
+    <row r="788" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F788" t="s">
+        <v>304</v>
+      </c>
+      <c r="H788">
+        <v>30</v>
+      </c>
+      <c r="I788">
+        <v>65</v>
+      </c>
+      <c r="J788">
+        <v>0</v>
+      </c>
+      <c r="K788">
+        <v>0</v>
+      </c>
+      <c r="L788">
+        <v>0</v>
+      </c>
+      <c r="N788">
+        <f>$AM$97</f>
+        <v>615</v>
+      </c>
+      <c r="P788">
+        <f>$AM$31</f>
+        <v>0.04</v>
+      </c>
+      <c r="Q788">
+        <f t="shared" ref="Q788:Q851" si="83">(J788 * $AD$4 +K788* $AD$5) + (1 -J788 - K788 )</f>
+        <v>1</v>
+      </c>
+      <c r="S788">
+        <f t="shared" si="72"/>
+        <v>9.0379298792249987</v>
+      </c>
+      <c r="T788">
+        <f t="shared" si="73"/>
+        <v>0.18708514849995747</v>
+      </c>
+      <c r="U788">
+        <f t="shared" si="74"/>
+        <v>364.81603957491706</v>
+      </c>
+    </row>
+    <row r="789" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F789" t="s">
+        <v>305</v>
+      </c>
+      <c r="H789">
+        <v>31</v>
+      </c>
+      <c r="I789">
+        <v>40</v>
+      </c>
+      <c r="J789">
+        <v>0</v>
+      </c>
+      <c r="K789">
+        <v>0</v>
+      </c>
+      <c r="L789">
+        <v>0</v>
+      </c>
+      <c r="N789">
+        <f t="shared" ref="N789:N790" si="84">$AM$97</f>
+        <v>615</v>
+      </c>
+      <c r="P789">
+        <f t="shared" ref="P789:P790" si="85">$AM$31</f>
+        <v>0.04</v>
+      </c>
+      <c r="Q789">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S789">
+        <f t="shared" si="72"/>
+        <v>9.0379298792249987</v>
+      </c>
+      <c r="T789">
+        <f t="shared" si="73"/>
+        <v>0.18708514849995747</v>
+      </c>
+      <c r="U789">
+        <f t="shared" si="74"/>
+        <v>231.98558413994726</v>
+      </c>
+    </row>
+    <row r="790" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F790" t="s">
+        <v>306</v>
+      </c>
+      <c r="H790">
+        <v>31</v>
+      </c>
+      <c r="I790">
+        <v>30</v>
+      </c>
+      <c r="J790">
+        <v>0</v>
+      </c>
+      <c r="K790">
+        <v>0</v>
+      </c>
+      <c r="L790">
+        <v>0</v>
+      </c>
+      <c r="N790">
+        <f t="shared" si="84"/>
+        <v>615</v>
+      </c>
+      <c r="P790">
+        <f t="shared" si="85"/>
+        <v>0.04</v>
+      </c>
+      <c r="Q790">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S790">
+        <f t="shared" si="72"/>
+        <v>9.0379298792249987</v>
+      </c>
+      <c r="T790">
+        <f t="shared" si="73"/>
+        <v>0.18708514849995747</v>
+      </c>
+      <c r="U790">
+        <f t="shared" si="74"/>
+        <v>173.98918810496045</v>
+      </c>
+    </row>
+    <row r="791" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F791" t="s">
+        <v>307</v>
+      </c>
+      <c r="H791">
+        <v>30</v>
+      </c>
+      <c r="I791">
+        <v>20</v>
+      </c>
+      <c r="J791">
+        <v>0</v>
+      </c>
+      <c r="K791">
+        <v>0</v>
+      </c>
+      <c r="L791">
+        <v>0</v>
+      </c>
+      <c r="N791">
+        <f>$AM$94</f>
+        <v>617</v>
+      </c>
+      <c r="P791">
+        <f>$AM$28</f>
+        <v>0.02</v>
+      </c>
+      <c r="Q791">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S791">
+        <f t="shared" si="72"/>
+        <v>9.0161388285699591</v>
+      </c>
+      <c r="T791">
+        <f t="shared" si="73"/>
+        <v>0.18663407375139815</v>
+      </c>
+      <c r="U791">
+        <f t="shared" si="74"/>
+        <v>111.9804442508389</v>
+      </c>
+    </row>
+    <row r="792" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F792" t="s">
+        <v>308</v>
+      </c>
+      <c r="H792">
+        <v>31</v>
+      </c>
+      <c r="I792">
+        <v>40</v>
+      </c>
+      <c r="J792">
+        <v>0</v>
+      </c>
+      <c r="K792">
+        <v>0</v>
+      </c>
+      <c r="L792">
+        <v>0</v>
+      </c>
+      <c r="N792">
+        <f t="shared" ref="N792:N794" si="86">$AM$94</f>
+        <v>617</v>
+      </c>
+      <c r="P792">
+        <f t="shared" ref="P792:P794" si="87">$AM$28</f>
+        <v>0.02</v>
+      </c>
+      <c r="Q792">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S792">
+        <f t="shared" si="72"/>
+        <v>9.0161388285699591</v>
+      </c>
+      <c r="T792">
+        <f t="shared" si="73"/>
+        <v>0.18663407375139815</v>
+      </c>
+      <c r="U792">
+        <f t="shared" si="74"/>
+        <v>231.42625145173369</v>
+      </c>
+    </row>
+    <row r="793" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F793" t="s">
+        <v>309</v>
+      </c>
+      <c r="H793">
+        <v>30</v>
+      </c>
+      <c r="I793">
+        <v>60</v>
+      </c>
+      <c r="J793">
+        <v>0</v>
+      </c>
+      <c r="K793">
+        <v>0</v>
+      </c>
+      <c r="L793">
+        <v>0</v>
+      </c>
+      <c r="N793">
+        <f t="shared" si="86"/>
+        <v>617</v>
+      </c>
+      <c r="P793">
+        <f t="shared" si="87"/>
+        <v>0.02</v>
+      </c>
+      <c r="Q793">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S793">
+        <f t="shared" si="72"/>
+        <v>9.0161388285699591</v>
+      </c>
+      <c r="T793">
+        <f t="shared" si="73"/>
+        <v>0.18663407375139815</v>
+      </c>
+      <c r="U793">
+        <f t="shared" si="74"/>
+        <v>335.9413327525167</v>
+      </c>
+    </row>
+    <row r="794" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F794" t="s">
+        <v>310</v>
+      </c>
+      <c r="H794">
+        <v>31</v>
+      </c>
+      <c r="I794">
+        <v>75</v>
+      </c>
+      <c r="J794">
+        <v>0</v>
+      </c>
+      <c r="K794">
+        <v>0</v>
+      </c>
+      <c r="L794">
+        <v>0</v>
+      </c>
+      <c r="N794">
+        <f>$AM$95</f>
+        <v>591</v>
+      </c>
+      <c r="P794">
+        <f>$AM$29</f>
+        <v>0.21</v>
+      </c>
+      <c r="Q794">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S794">
+        <f t="shared" si="72"/>
+        <v>9.1576407142083571</v>
+      </c>
+      <c r="T794">
+        <f t="shared" si="73"/>
+        <v>0.189563162784113</v>
+      </c>
+      <c r="U794">
+        <f t="shared" si="74"/>
+        <v>440.73435347306275</v>
+      </c>
+    </row>
+    <row r="795" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E795" t="s">
+        <v>146</v>
+      </c>
+      <c r="F795" t="s">
+        <v>299</v>
+      </c>
+      <c r="H795">
+        <v>31</v>
+      </c>
+      <c r="I795">
+        <v>180</v>
+      </c>
+      <c r="J795">
+        <v>0</v>
+      </c>
+      <c r="K795">
+        <v>0</v>
+      </c>
+      <c r="L795">
+        <v>0</v>
+      </c>
+      <c r="M795" s="1">
+        <v>210</v>
+      </c>
+      <c r="N795" s="1">
+        <v>210</v>
+      </c>
+      <c r="O795" s="1">
+        <v>0</v>
+      </c>
+      <c r="P795" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q795">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S795">
+        <f t="shared" si="72"/>
+        <v>4.0955235875999989</v>
+      </c>
+      <c r="T795">
+        <f t="shared" si="73"/>
+        <v>8.4777338263319985E-2</v>
+      </c>
+      <c r="U795">
+        <f t="shared" si="74"/>
+        <v>473.0575475093255</v>
+      </c>
+    </row>
+    <row r="796" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E796">
+        <v>4</v>
+      </c>
+      <c r="F796" t="s">
+        <v>300</v>
+      </c>
+      <c r="H796">
+        <v>28</v>
+      </c>
+      <c r="I796">
+        <v>180</v>
+      </c>
+      <c r="J796">
+        <v>0</v>
+      </c>
+      <c r="K796">
+        <v>0</v>
+      </c>
+      <c r="L796">
+        <v>0</v>
+      </c>
+      <c r="M796" s="1">
+        <v>210</v>
+      </c>
+      <c r="N796" s="1">
+        <v>210</v>
+      </c>
+      <c r="O796" s="1">
+        <v>0</v>
+      </c>
+      <c r="P796" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q796">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S796">
+        <f t="shared" si="72"/>
+        <v>4.0955235875999989</v>
+      </c>
+      <c r="T796">
+        <f t="shared" si="73"/>
+        <v>8.4777338263319985E-2</v>
+      </c>
+      <c r="U796">
+        <f t="shared" si="74"/>
+        <v>427.27778484713269</v>
+      </c>
+    </row>
+    <row r="797" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F797" t="s">
+        <v>301</v>
+      </c>
+      <c r="H797">
+        <v>31</v>
+      </c>
+      <c r="I797">
+        <v>170</v>
+      </c>
+      <c r="J797">
+        <v>0</v>
+      </c>
+      <c r="K797">
+        <v>0</v>
+      </c>
+      <c r="L797">
+        <v>0</v>
+      </c>
+      <c r="M797" s="1">
+        <v>225</v>
+      </c>
+      <c r="N797" s="1">
+        <v>225</v>
+      </c>
+      <c r="O797" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="P797" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Q797">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S797">
+        <f t="shared" si="72"/>
+        <v>4.9834981406250014</v>
+      </c>
+      <c r="T797">
+        <f t="shared" si="73"/>
+        <v>0.10315841151093753</v>
+      </c>
+      <c r="U797">
+        <f t="shared" si="74"/>
+        <v>543.64482866264086</v>
+      </c>
+    </row>
+    <row r="798" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F798" t="s">
+        <v>302</v>
+      </c>
+      <c r="H798">
+        <v>30</v>
+      </c>
+      <c r="I798">
+        <v>170</v>
+      </c>
+      <c r="J798">
+        <v>0</v>
+      </c>
+      <c r="K798">
+        <v>0</v>
+      </c>
+      <c r="L798">
+        <v>0</v>
+      </c>
+      <c r="M798" s="1">
+        <v>230</v>
+      </c>
+      <c r="N798" s="1">
+        <v>230</v>
+      </c>
+      <c r="O798" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="P798" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Q798">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S798">
+        <f t="shared" si="72"/>
+        <v>4.441176908100001</v>
+      </c>
+      <c r="T798">
+        <f t="shared" si="73"/>
+        <v>9.193236199767002E-2</v>
+      </c>
+      <c r="U798">
+        <f t="shared" si="74"/>
+        <v>468.85504618811711</v>
+      </c>
+    </row>
+    <row r="799" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F799" t="s">
+        <v>303</v>
+      </c>
+      <c r="H799">
+        <v>31</v>
+      </c>
+      <c r="I799">
+        <v>168</v>
+      </c>
+      <c r="J799">
+        <v>0</v>
+      </c>
+      <c r="K799">
+        <v>0</v>
+      </c>
+      <c r="L799">
+        <v>0</v>
+      </c>
+      <c r="M799" s="1">
+        <v>235</v>
+      </c>
+      <c r="N799" s="1">
+        <v>235</v>
+      </c>
+      <c r="O799" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="P799" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="Q799">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S799">
+        <f t="shared" si="72"/>
+        <v>4.4849285952250018</v>
+      </c>
+      <c r="T799">
+        <f t="shared" si="73"/>
+        <v>9.2838021921157532E-2</v>
+      </c>
+      <c r="U799">
+        <f t="shared" si="74"/>
+        <v>483.5004181653884</v>
+      </c>
+    </row>
+    <row r="800" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F800" t="s">
+        <v>304</v>
+      </c>
+      <c r="H800">
+        <v>30</v>
+      </c>
+      <c r="I800">
+        <v>165</v>
+      </c>
+      <c r="J800">
+        <v>0</v>
+      </c>
+      <c r="K800">
+        <v>0</v>
+      </c>
+      <c r="L800">
+        <v>0</v>
+      </c>
+      <c r="M800" s="1">
+        <v>240</v>
+      </c>
+      <c r="N800" s="1">
+        <v>240</v>
+      </c>
+      <c r="O800" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="P800" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="Q800">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S800">
+        <f t="shared" si="72"/>
+        <v>4.5551938041</v>
+      </c>
+      <c r="T800">
+        <f t="shared" si="73"/>
+        <v>9.4292511744869995E-2</v>
+      </c>
+      <c r="U800">
+        <f t="shared" si="74"/>
+        <v>466.74793313710643</v>
+      </c>
+    </row>
+    <row r="801" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F801" t="s">
+        <v>305</v>
+      </c>
+      <c r="H801">
+        <v>31</v>
+      </c>
+      <c r="I801">
+        <v>130</v>
+      </c>
+      <c r="J801">
+        <v>0</v>
+      </c>
+      <c r="K801">
+        <v>0</v>
+      </c>
+      <c r="L801">
+        <v>0</v>
+      </c>
+      <c r="M801" s="1">
+        <v>245</v>
+      </c>
+      <c r="N801" s="1">
+        <v>245</v>
+      </c>
+      <c r="O801" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="P801" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q801">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S801">
+        <f t="shared" si="72"/>
+        <v>4.6186737920999992</v>
+      </c>
+      <c r="T801">
+        <f t="shared" si="73"/>
+        <v>9.560654749646999E-2</v>
+      </c>
+      <c r="U801">
+        <f t="shared" si="74"/>
+        <v>385.29438641077405</v>
+      </c>
+    </row>
+    <row r="802" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F802" t="s">
+        <v>306</v>
+      </c>
+      <c r="H802">
+        <v>31</v>
+      </c>
+      <c r="I802">
+        <v>120</v>
+      </c>
+      <c r="J802">
+        <v>0</v>
+      </c>
+      <c r="K802">
+        <v>0</v>
+      </c>
+      <c r="L802">
+        <v>0</v>
+      </c>
+      <c r="M802" s="1">
+        <v>260</v>
+      </c>
+      <c r="N802" s="1">
+        <v>260</v>
+      </c>
+      <c r="O802" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="P802" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="Q802">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S802">
+        <f t="shared" si="72"/>
+        <v>5.3621886096000004</v>
+      </c>
+      <c r="T802">
+        <f t="shared" si="73"/>
+        <v>0.11099730421872001</v>
+      </c>
+      <c r="U802">
+        <f t="shared" si="74"/>
+        <v>412.90997169363845</v>
+      </c>
+    </row>
+    <row r="803" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F803" t="s">
+        <v>307</v>
+      </c>
+      <c r="H803">
+        <v>30</v>
+      </c>
+      <c r="I803">
+        <v>90</v>
+      </c>
+      <c r="J803">
+        <v>0</v>
+      </c>
+      <c r="K803">
+        <v>0</v>
+      </c>
+      <c r="L803">
+        <v>0</v>
+      </c>
+      <c r="M803" s="1">
+        <v>260</v>
+      </c>
+      <c r="N803" s="1">
+        <v>260</v>
+      </c>
+      <c r="O803" s="1">
+        <v>0</v>
+      </c>
+      <c r="P803" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q803">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S803">
+        <f t="shared" si="72"/>
+        <v>4.7945233296000014</v>
+      </c>
+      <c r="T803">
+        <f t="shared" si="73"/>
+        <v>9.9246632922720027E-2</v>
+      </c>
+      <c r="U803">
+        <f t="shared" si="74"/>
+        <v>267.9659088913441</v>
+      </c>
+    </row>
+    <row r="804" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F804" t="s">
+        <v>308</v>
+      </c>
+      <c r="H804">
+        <v>31</v>
+      </c>
+      <c r="I804">
+        <v>120</v>
+      </c>
+      <c r="J804">
+        <v>0</v>
+      </c>
+      <c r="K804">
+        <v>0</v>
+      </c>
+      <c r="L804">
+        <v>0</v>
+      </c>
+      <c r="M804" s="1">
+        <v>265</v>
+      </c>
+      <c r="N804" s="1">
+        <v>265</v>
+      </c>
+      <c r="O804" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="P804" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="Q804">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S804">
+        <f t="shared" si="72"/>
+        <v>4.8921255942249982</v>
+      </c>
+      <c r="T804">
+        <f t="shared" si="73"/>
+        <v>0.10126699980045746</v>
+      </c>
+      <c r="U804">
+        <f t="shared" si="74"/>
+        <v>376.71323925770179</v>
+      </c>
+    </row>
+    <row r="805" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F805" t="s">
+        <v>309</v>
+      </c>
+      <c r="H805">
+        <v>30</v>
+      </c>
+      <c r="I805">
+        <v>150</v>
+      </c>
+      <c r="J805">
+        <v>0</v>
+      </c>
+      <c r="K805">
+        <v>0</v>
+      </c>
+      <c r="L805">
+        <v>0</v>
+      </c>
+      <c r="M805" s="1">
+        <v>250</v>
+      </c>
+      <c r="N805" s="1">
+        <v>250</v>
+      </c>
+      <c r="O805" s="1">
+        <v>-0.3</v>
+      </c>
+      <c r="P805" s="1">
+        <v>-0.3</v>
+      </c>
+      <c r="Q805">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S805">
+        <f t="shared" si="72"/>
+        <v>4.2559690000000003</v>
+      </c>
+      <c r="T805">
+        <f t="shared" si="73"/>
+        <v>8.8098558300000004E-2</v>
+      </c>
+      <c r="U805">
+        <f t="shared" si="74"/>
+        <v>396.44351234999999</v>
+      </c>
+    </row>
+    <row r="806" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F806" t="s">
+        <v>310</v>
+      </c>
+      <c r="H806">
+        <v>31</v>
+      </c>
+      <c r="I806">
+        <v>170</v>
+      </c>
+      <c r="J806">
+        <v>0</v>
+      </c>
+      <c r="K806">
+        <v>0</v>
+      </c>
+      <c r="L806">
+        <v>0</v>
+      </c>
+      <c r="M806" s="1">
+        <v>240</v>
+      </c>
+      <c r="N806" s="1">
+        <v>240</v>
+      </c>
+      <c r="O806" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="P806" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="Q806">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S806">
+        <f t="shared" si="72"/>
+        <v>4.2511841855999988</v>
+      </c>
+      <c r="T806">
+        <f t="shared" si="73"/>
+        <v>8.7999512641919977E-2</v>
+      </c>
+      <c r="U806">
+        <f t="shared" si="74"/>
+        <v>463.75743162291826</v>
+      </c>
+    </row>
+    <row r="807" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E807" t="s">
+        <v>152</v>
+      </c>
+      <c r="F807" t="s">
+        <v>299</v>
+      </c>
+      <c r="H807">
+        <v>31</v>
+      </c>
+      <c r="I807">
+        <v>250</v>
+      </c>
+      <c r="J807">
+        <v>0.05</v>
+      </c>
+      <c r="K807">
+        <v>0.5</v>
+      </c>
+      <c r="L807">
+        <f>$AC$12</f>
+        <v>1.3</v>
+      </c>
+      <c r="N807">
+        <f>$AM$103</f>
+        <v>310</v>
+      </c>
+      <c r="P807">
+        <f>$AM$37</f>
+        <v>0.47</v>
+      </c>
+      <c r="Q807">
+        <f t="shared" si="83"/>
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="S807">
+        <f>(1.185 + 0.00454 * N807- 0.0000026 * N807^2 + 0.315 * P807 )^2 * Q807</f>
+        <v>6.6062360537264997</v>
+      </c>
+      <c r="T807">
+        <f t="shared" si="73"/>
+        <v>0.13674908631213853</v>
+      </c>
+      <c r="U807">
+        <f t="shared" si="74"/>
+        <v>1059.8054189190736</v>
+      </c>
+    </row>
+    <row r="808" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E808" t="s">
+        <v>235</v>
+      </c>
+      <c r="F808" t="s">
+        <v>300</v>
+      </c>
+      <c r="H808">
+        <v>28</v>
+      </c>
+      <c r="I808">
+        <v>260</v>
+      </c>
+      <c r="J808">
+        <v>0</v>
+      </c>
+      <c r="K808">
+        <v>0.35</v>
+      </c>
+      <c r="L808">
+        <f>$AC$13</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N808">
+        <f t="shared" ref="N808:N809" si="88">$AM$103</f>
+        <v>310</v>
+      </c>
+      <c r="P808">
+        <f t="shared" ref="P808:P809" si="89">$AM$37</f>
+        <v>0.47</v>
+      </c>
+      <c r="Q808">
+        <f t="shared" si="83"/>
+        <v>1.0350000000000001</v>
+      </c>
+      <c r="S808">
+        <f t="shared" si="72"/>
+        <v>6.4201448972835014</v>
+      </c>
+      <c r="T808">
+        <f t="shared" si="73"/>
+        <v>0.13289699937376848</v>
+      </c>
+      <c r="U808">
+        <f t="shared" si="74"/>
+        <v>967.4901554410344</v>
+      </c>
+    </row>
+    <row r="809" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F809" t="s">
+        <v>301</v>
+      </c>
+      <c r="H809">
+        <v>31</v>
+      </c>
+      <c r="I809">
+        <v>240</v>
+      </c>
+      <c r="J809">
+        <v>0</v>
+      </c>
+      <c r="K809">
+        <v>0.04</v>
+      </c>
+      <c r="L809">
+        <f>$AC$14</f>
+        <v>0</v>
+      </c>
+      <c r="N809">
+        <f>$AM$104</f>
+        <v>351</v>
+      </c>
+      <c r="P809">
+        <f>$AM$38</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q809">
+        <f t="shared" si="83"/>
+        <v>1.004</v>
+      </c>
+      <c r="S809">
+        <f t="shared" si="72"/>
+        <v>6.5424315887598121</v>
+      </c>
+      <c r="T809">
+        <f t="shared" si="73"/>
+        <v>0.13542833388732811</v>
+      </c>
+      <c r="U809">
+        <f t="shared" si="74"/>
+        <v>1007.5868041217212</v>
+      </c>
+    </row>
+    <row r="810" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F810" t="s">
+        <v>302</v>
+      </c>
+      <c r="H810">
+        <v>30</v>
+      </c>
+      <c r="I810">
+        <v>220</v>
+      </c>
+      <c r="J810">
+        <v>0</v>
+      </c>
+      <c r="K810">
+        <v>0</v>
+      </c>
+      <c r="L810">
+        <f>$AC$14</f>
+        <v>0</v>
+      </c>
+      <c r="N810">
+        <f t="shared" ref="N810:N812" si="90">$AM$104</f>
+        <v>351</v>
+      </c>
+      <c r="P810">
+        <f t="shared" ref="P810:P812" si="91">$AM$38</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q810">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S810">
+        <f t="shared" si="72"/>
+        <v>6.5163661242627606</v>
+      </c>
+      <c r="T810">
+        <f t="shared" si="73"/>
+        <v>0.13488877877223915</v>
+      </c>
+      <c r="U810">
+        <f t="shared" si="74"/>
+        <v>890.26593989677838</v>
+      </c>
+    </row>
+    <row r="811" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F811" t="s">
+        <v>303</v>
+      </c>
+      <c r="H811">
+        <v>31</v>
+      </c>
+      <c r="I811">
+        <v>200</v>
+      </c>
+      <c r="J811">
+        <v>0</v>
+      </c>
+      <c r="K811">
+        <v>0</v>
+      </c>
+      <c r="N811">
+        <f t="shared" si="90"/>
+        <v>351</v>
+      </c>
+      <c r="P811">
+        <f t="shared" si="91"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q811">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S811">
+        <f t="shared" ref="S811:S874" si="92">(1.185 + 0.00454 * N811- 0.0000026 * N811^2 + 0.315 * P811 )^2 * Q811</f>
+        <v>6.5163661242627606</v>
+      </c>
+      <c r="T811">
+        <f t="shared" si="73"/>
+        <v>0.13488877877223915</v>
+      </c>
+      <c r="U811">
+        <f t="shared" si="74"/>
+        <v>836.31042838788278</v>
+      </c>
+    </row>
+    <row r="812" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F812" t="s">
+        <v>304</v>
+      </c>
+      <c r="H812">
+        <v>30</v>
+      </c>
+      <c r="I812">
+        <v>195</v>
+      </c>
+      <c r="J812">
+        <v>0</v>
+      </c>
+      <c r="K812">
+        <v>0</v>
+      </c>
+      <c r="N812">
+        <f>$AM$105</f>
+        <v>364</v>
+      </c>
+      <c r="P812">
+        <f>$AM$39</f>
+        <v>0.11</v>
+      </c>
+      <c r="Q812">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S812">
+        <f t="shared" si="92"/>
+        <v>6.3893704205761583</v>
+      </c>
+      <c r="T812">
+        <f t="shared" si="73"/>
+        <v>0.13225996770592646</v>
+      </c>
+      <c r="U812">
+        <f t="shared" si="74"/>
+        <v>773.72081107966983</v>
+      </c>
+    </row>
+    <row r="813" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F813" t="s">
+        <v>305</v>
+      </c>
+      <c r="H813">
+        <v>31</v>
+      </c>
+      <c r="I813">
+        <v>180</v>
+      </c>
+      <c r="J813">
+        <v>0</v>
+      </c>
+      <c r="K813">
+        <v>0</v>
+      </c>
+      <c r="N813">
+        <f t="shared" ref="N813:N814" si="93">$AM$105</f>
+        <v>364</v>
+      </c>
+      <c r="P813">
+        <f t="shared" ref="P813:P814" si="94">$AM$39</f>
+        <v>0.11</v>
+      </c>
+      <c r="Q813">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S813">
+        <f t="shared" si="92"/>
+        <v>6.3893704205761583</v>
+      </c>
+      <c r="T813">
+        <f t="shared" si="73"/>
+        <v>0.13225996770592646</v>
+      </c>
+      <c r="U813">
+        <f t="shared" si="74"/>
+        <v>738.01061979906967</v>
+      </c>
+    </row>
+    <row r="814" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F814" t="s">
+        <v>306</v>
+      </c>
+      <c r="G814" s="1">
+        <v>28</v>
+      </c>
+      <c r="H814" s="1">
+        <v>28</v>
+      </c>
+      <c r="I814">
+        <v>160</v>
+      </c>
+      <c r="J814">
+        <v>0</v>
+      </c>
+      <c r="K814">
+        <v>0</v>
+      </c>
+      <c r="N814">
+        <f t="shared" si="93"/>
+        <v>364</v>
+      </c>
+      <c r="P814">
+        <f t="shared" si="94"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q814">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S814">
+        <f t="shared" si="92"/>
+        <v>6.3893704205761583</v>
+      </c>
+      <c r="T814">
+        <f t="shared" si="73"/>
+        <v>0.13225996770592646</v>
+      </c>
+      <c r="U814">
+        <f t="shared" si="74"/>
+        <v>592.52465532255064</v>
+      </c>
+    </row>
+    <row r="815" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F815" t="s">
+        <v>307</v>
+      </c>
+      <c r="H815">
+        <v>30</v>
+      </c>
+      <c r="I815">
+        <v>140</v>
+      </c>
+      <c r="J815">
+        <v>0.2</v>
+      </c>
+      <c r="K815">
+        <v>0</v>
+      </c>
+      <c r="N815">
+        <f>$AM$102</f>
+        <v>371</v>
+      </c>
+      <c r="P815">
+        <f>$AM$36</f>
+        <v>0.23</v>
+      </c>
+      <c r="Q815">
+        <f t="shared" si="83"/>
+        <v>1.06</v>
+      </c>
+      <c r="S815">
+        <f t="shared" si="92"/>
+        <v>7.0772597452916148</v>
+      </c>
+      <c r="T815">
+        <f t="shared" si="73"/>
+        <v>0.14649927672753643</v>
+      </c>
+      <c r="U815">
+        <f t="shared" si="74"/>
+        <v>615.29696225565306</v>
+      </c>
+    </row>
+    <row r="816" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F816" t="s">
+        <v>308</v>
+      </c>
+      <c r="H816">
+        <v>31</v>
+      </c>
+      <c r="I816">
+        <v>160</v>
+      </c>
+      <c r="J816">
+        <v>0.2</v>
+      </c>
+      <c r="K816">
+        <v>0.2</v>
+      </c>
+      <c r="N816">
+        <f t="shared" ref="N816:N818" si="95">$AM$102</f>
+        <v>371</v>
+      </c>
+      <c r="P816">
+        <f t="shared" ref="P816:P818" si="96">$AM$36</f>
+        <v>0.23</v>
+      </c>
+      <c r="Q816">
+        <f t="shared" si="83"/>
+        <v>1.08</v>
+      </c>
+      <c r="S816">
+        <f t="shared" si="92"/>
+        <v>7.2107929480329664</v>
+      </c>
+      <c r="T816">
+        <f t="shared" si="73"/>
+        <v>0.14926341402428242</v>
+      </c>
+      <c r="U816">
+        <f t="shared" si="74"/>
+        <v>740.34653356044078</v>
+      </c>
+    </row>
+    <row r="817" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F817" t="s">
+        <v>309</v>
+      </c>
+      <c r="H817">
+        <v>30</v>
+      </c>
+      <c r="I817">
+        <v>180</v>
+      </c>
+      <c r="J817">
+        <v>0.3</v>
+      </c>
+      <c r="K817">
+        <v>0.38</v>
+      </c>
+      <c r="N817">
+        <f t="shared" si="95"/>
+        <v>371</v>
+      </c>
+      <c r="P817">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="Q817">
+        <f t="shared" si="83"/>
+        <v>1.1280000000000001</v>
+      </c>
+      <c r="S817">
+        <f t="shared" si="92"/>
+        <v>7.5312726346122094</v>
+      </c>
+      <c r="T817">
+        <f t="shared" si="73"/>
+        <v>0.15589734353647275</v>
+      </c>
+      <c r="U817">
+        <f t="shared" si="74"/>
+        <v>841.8456550969529</v>
+      </c>
+    </row>
+    <row r="818" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F818" t="s">
+        <v>310</v>
+      </c>
+      <c r="H818">
+        <v>31</v>
+      </c>
+      <c r="I818">
+        <v>200</v>
+      </c>
+      <c r="J818">
+        <v>0.05</v>
+      </c>
+      <c r="K818">
+        <v>0.68</v>
+      </c>
+      <c r="N818">
+        <f>$AM$103</f>
+        <v>310</v>
+      </c>
+      <c r="P818">
+        <f>$AM$37</f>
+        <v>0.47</v>
+      </c>
+      <c r="Q818">
+        <f t="shared" si="83"/>
+        <v>1.0830000000000002</v>
+      </c>
+      <c r="S818">
+        <f t="shared" si="92"/>
+        <v>6.7178907475923015</v>
+      </c>
+      <c r="T818">
+        <f t="shared" si="73"/>
+        <v>0.13906033847516064</v>
+      </c>
+      <c r="U818">
+        <f t="shared" si="74"/>
+        <v>862.174098545996</v>
+      </c>
+    </row>
+    <row r="819" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E819" t="s">
+        <v>141</v>
+      </c>
+      <c r="F819" t="s">
+        <v>299</v>
+      </c>
+      <c r="H819">
+        <v>31</v>
+      </c>
+      <c r="I819">
+        <v>190</v>
+      </c>
+      <c r="J819">
+        <v>0</v>
+      </c>
+      <c r="K819">
+        <v>0</v>
+      </c>
+      <c r="L819">
+        <v>0</v>
+      </c>
+      <c r="N819">
+        <f>$AM$107</f>
+        <v>140</v>
+      </c>
+      <c r="P819">
+        <f>$AM$41</f>
+        <v>0.25</v>
+      </c>
+      <c r="Q819">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R819" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="S819" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="T819">
+        <f t="shared" si="73"/>
+        <v>6.4170000000000005E-2</v>
+      </c>
+      <c r="U819">
+        <f t="shared" si="74"/>
+        <v>377.96129999999999</v>
+      </c>
+    </row>
+    <row r="820" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E820">
+        <v>3</v>
+      </c>
+      <c r="F820" t="s">
+        <v>300</v>
+      </c>
+      <c r="H820">
+        <v>28</v>
+      </c>
+      <c r="I820">
+        <v>195</v>
+      </c>
+      <c r="J820">
+        <v>0</v>
+      </c>
+      <c r="K820">
+        <v>0</v>
+      </c>
+      <c r="L820">
+        <v>0</v>
+      </c>
+      <c r="N820">
+        <f t="shared" ref="N820:N821" si="97">$AM$107</f>
+        <v>140</v>
+      </c>
+      <c r="P820">
+        <f t="shared" ref="P820:P821" si="98">$AM$41</f>
+        <v>0.25</v>
+      </c>
+      <c r="Q820">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R820" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="S820" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="T820">
+        <f t="shared" si="73"/>
+        <v>6.6239999999999993E-2</v>
+      </c>
+      <c r="U820">
+        <f t="shared" si="74"/>
+        <v>361.67039999999997</v>
+      </c>
+    </row>
+    <row r="821" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F821" t="s">
+        <v>301</v>
+      </c>
+      <c r="H821">
+        <v>31</v>
+      </c>
+      <c r="I821">
+        <v>190</v>
+      </c>
+      <c r="J821">
+        <v>0</v>
+      </c>
+      <c r="K821">
+        <v>0</v>
+      </c>
+      <c r="L821">
+        <v>0</v>
+      </c>
+      <c r="N821">
+        <f>$AM$108</f>
+        <v>163</v>
+      </c>
+      <c r="P821">
+        <f>$AM$42</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q821">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R821" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="S821" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="T821">
+        <f t="shared" si="73"/>
+        <v>6.8309999999999996E-2</v>
+      </c>
+      <c r="U821">
+        <f t="shared" si="74"/>
+        <v>402.34589999999997</v>
+      </c>
+    </row>
+    <row r="822" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F822" t="s">
+        <v>302</v>
+      </c>
+      <c r="H822">
+        <v>30</v>
+      </c>
+      <c r="I822">
+        <v>185</v>
+      </c>
+      <c r="J822">
+        <v>0</v>
+      </c>
+      <c r="K822">
+        <v>0</v>
+      </c>
+      <c r="L822">
+        <v>0</v>
+      </c>
+      <c r="N822">
+        <f t="shared" ref="N822:N824" si="99">$AM$108</f>
+        <v>163</v>
+      </c>
+      <c r="P822">
+        <f t="shared" ref="P822:P824" si="100">$AM$42</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q822">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R822" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="S822" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="T822">
+        <f t="shared" si="73"/>
+        <v>7.0379999999999998E-2</v>
+      </c>
+      <c r="U822">
+        <f t="shared" si="74"/>
+        <v>390.60899999999992</v>
+      </c>
+    </row>
+    <row r="823" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F823" t="s">
+        <v>303</v>
+      </c>
+      <c r="H823">
+        <v>31</v>
+      </c>
+      <c r="I823">
+        <v>180</v>
+      </c>
+      <c r="J823">
+        <v>0</v>
+      </c>
+      <c r="K823">
+        <v>0</v>
+      </c>
+      <c r="L823">
+        <v>0</v>
+      </c>
+      <c r="N823">
+        <f t="shared" si="99"/>
+        <v>163</v>
+      </c>
+      <c r="P823">
+        <f t="shared" si="100"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q823">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R823" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="S823" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="T823">
+        <f t="shared" si="73"/>
+        <v>7.2450000000000001E-2</v>
+      </c>
+      <c r="U823">
+        <f t="shared" si="74"/>
+        <v>404.27100000000002</v>
+      </c>
+    </row>
+    <row r="824" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F824" t="s">
+        <v>304</v>
+      </c>
+      <c r="H824">
+        <v>30</v>
+      </c>
+      <c r="I824">
+        <v>179</v>
+      </c>
+      <c r="J824">
+        <v>0</v>
+      </c>
+      <c r="K824">
+        <v>0</v>
+      </c>
+      <c r="L824">
+        <v>0</v>
+      </c>
+      <c r="N824">
+        <f>$AM$109</f>
+        <v>162</v>
+      </c>
+      <c r="P824">
+        <f>$AM$43</f>
+        <v>0.06</v>
+      </c>
+      <c r="Q824">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R824" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="S824" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="T824">
+        <f t="shared" si="73"/>
+        <v>7.2450000000000001E-2</v>
+      </c>
+      <c r="U824">
+        <f t="shared" si="74"/>
+        <v>389.05650000000003</v>
+      </c>
+    </row>
+    <row r="825" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F825" t="s">
+        <v>305</v>
+      </c>
+      <c r="H825">
+        <v>31</v>
+      </c>
+      <c r="I825">
+        <v>170</v>
+      </c>
+      <c r="J825">
+        <v>0</v>
+      </c>
+      <c r="K825">
+        <v>0</v>
+      </c>
+      <c r="L825">
+        <v>0</v>
+      </c>
+      <c r="N825">
+        <f t="shared" ref="N825:N826" si="101">$AM$109</f>
+        <v>162</v>
+      </c>
+      <c r="P825">
+        <f t="shared" ref="P825:P826" si="102">$AM$43</f>
+        <v>0.06</v>
+      </c>
+      <c r="Q825">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R825" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="S825" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="T825">
+        <f t="shared" si="73"/>
+        <v>7.2450000000000001E-2</v>
+      </c>
+      <c r="U825">
+        <f t="shared" si="74"/>
+        <v>381.81150000000002</v>
+      </c>
+    </row>
+    <row r="826" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F826" t="s">
+        <v>306</v>
+      </c>
+      <c r="H826">
+        <v>31</v>
+      </c>
+      <c r="I826">
+        <v>160</v>
+      </c>
+      <c r="J826">
+        <v>0</v>
+      </c>
+      <c r="K826">
+        <v>0</v>
+      </c>
+      <c r="L826">
+        <v>0</v>
+      </c>
+      <c r="N826">
+        <f t="shared" si="101"/>
+        <v>162</v>
+      </c>
+      <c r="P826">
+        <f t="shared" si="102"/>
+        <v>0.06</v>
+      </c>
+      <c r="Q826">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R826" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="S826" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="T826">
+        <f t="shared" si="73"/>
+        <v>7.4520000000000003E-2</v>
+      </c>
+      <c r="U826">
+        <f t="shared" si="74"/>
+        <v>369.61919999999998</v>
+      </c>
+    </row>
+    <row r="827" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F827" t="s">
+        <v>307</v>
+      </c>
+      <c r="H827">
+        <v>30</v>
+      </c>
+      <c r="I827">
+        <v>90</v>
+      </c>
+      <c r="J827">
+        <v>0</v>
+      </c>
+      <c r="K827">
+        <v>0</v>
+      </c>
+      <c r="L827">
+        <v>0</v>
+      </c>
+      <c r="N827">
+        <f>$AM$106</f>
+        <v>174</v>
+      </c>
+      <c r="P827">
+        <f>$AM$40</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q827">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R827" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="S827" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="T827">
+        <f t="shared" si="73"/>
+        <v>7.6590000000000005E-2</v>
+      </c>
+      <c r="U827">
+        <f t="shared" si="74"/>
+        <v>206.79300000000003</v>
+      </c>
+    </row>
+    <row r="828" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F828" t="s">
+        <v>308</v>
+      </c>
+      <c r="H828">
+        <v>31</v>
+      </c>
+      <c r="I828">
+        <v>110</v>
+      </c>
+      <c r="J828">
+        <v>0</v>
+      </c>
+      <c r="K828">
+        <v>0</v>
+      </c>
+      <c r="L828">
+        <v>0</v>
+      </c>
+      <c r="N828">
+        <f t="shared" ref="N828:N830" si="103">$AM$106</f>
+        <v>174</v>
+      </c>
+      <c r="P828">
+        <f t="shared" ref="P828:P830" si="104">$AM$40</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q828">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R828" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="S828" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="T828">
+        <f t="shared" si="73"/>
+        <v>7.6590000000000005E-2</v>
+      </c>
+      <c r="U828">
+        <f t="shared" si="74"/>
+        <v>261.17190000000005</v>
+      </c>
+    </row>
+    <row r="829" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F829" t="s">
+        <v>309</v>
+      </c>
+      <c r="H829">
+        <v>30</v>
+      </c>
+      <c r="I829">
+        <v>140</v>
+      </c>
+      <c r="J829">
+        <v>0</v>
+      </c>
+      <c r="K829">
+        <v>0</v>
+      </c>
+      <c r="L829">
+        <v>0</v>
+      </c>
+      <c r="N829">
+        <f t="shared" si="103"/>
+        <v>174</v>
+      </c>
+      <c r="P829">
+        <f t="shared" si="104"/>
+        <v>0.24</v>
+      </c>
+      <c r="Q829">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R829" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="S829" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="T829">
+        <f t="shared" si="73"/>
+        <v>7.8659999999999994E-2</v>
+      </c>
+      <c r="U829">
+        <f t="shared" si="74"/>
+        <v>330.37199999999996</v>
+      </c>
+    </row>
+    <row r="830" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F830" t="s">
+        <v>310</v>
+      </c>
+      <c r="H830">
+        <v>31</v>
+      </c>
+      <c r="I830">
+        <v>180</v>
+      </c>
+      <c r="J830">
+        <v>0</v>
+      </c>
+      <c r="K830">
+        <v>0</v>
+      </c>
+      <c r="L830">
+        <v>0</v>
+      </c>
+      <c r="N830">
+        <f>$AM$107</f>
+        <v>140</v>
+      </c>
+      <c r="P830">
+        <f>$AM$41</f>
+        <v>0.25</v>
+      </c>
+      <c r="Q830">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="R830" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="S830" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="T830">
+        <f t="shared" si="73"/>
+        <v>7.2450000000000001E-2</v>
+      </c>
+      <c r="U830">
+        <f t="shared" si="74"/>
+        <v>404.27100000000002</v>
+      </c>
+    </row>
+    <row r="831" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E831" t="s">
+        <v>156</v>
+      </c>
+      <c r="F831" t="s">
+        <v>299</v>
+      </c>
+      <c r="H831">
+        <v>31</v>
+      </c>
+      <c r="I831">
+        <v>90</v>
+      </c>
+      <c r="J831">
+        <v>0</v>
+      </c>
+      <c r="K831">
+        <v>0.15</v>
+      </c>
+      <c r="L831">
+        <f>$AC$12</f>
+        <v>1.3</v>
+      </c>
+      <c r="N831">
+        <f>$AM$111</f>
+        <v>405</v>
+      </c>
+      <c r="P831">
+        <f>$AM$45</f>
+        <v>0.31</v>
+      </c>
+      <c r="Q831">
+        <f t="shared" si="83"/>
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="S831">
+        <f t="shared" si="92"/>
+        <v>7.3713412406733729</v>
+      </c>
+      <c r="T831">
+        <f t="shared" si="73"/>
+        <v>0.1525867636819388</v>
+      </c>
+      <c r="U831">
+        <f t="shared" si="74"/>
+        <v>425.71707067260928</v>
+      </c>
+    </row>
+    <row r="832" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E832" t="s">
+        <v>236</v>
+      </c>
+      <c r="F832" t="s">
+        <v>300</v>
+      </c>
+      <c r="H832">
+        <v>28</v>
+      </c>
+      <c r="I832">
+        <v>92</v>
+      </c>
+      <c r="J832">
+        <v>0</v>
+      </c>
+      <c r="K832">
+        <v>0</v>
+      </c>
+      <c r="L832">
+        <f>$AC$13</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N832">
+        <f>$AM$111</f>
+        <v>405</v>
+      </c>
+      <c r="P832">
+        <f>$AM$45</f>
+        <v>0.31</v>
+      </c>
+      <c r="Q832">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S832">
+        <f t="shared" si="92"/>
+        <v>7.2624051632249991</v>
+      </c>
+      <c r="T832">
+        <f t="shared" si="73"/>
+        <v>0.15033178687875748</v>
+      </c>
+      <c r="U832">
+        <f t="shared" si="74"/>
+        <v>387.25468299967929</v>
+      </c>
+    </row>
+    <row r="833" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F833" t="s">
+        <v>301</v>
+      </c>
+      <c r="H833">
+        <v>31</v>
+      </c>
+      <c r="I833">
+        <v>92</v>
+      </c>
+      <c r="J833">
+        <v>0</v>
+      </c>
+      <c r="K833">
+        <v>0</v>
+      </c>
+      <c r="L833">
+        <f>$AC$14</f>
+        <v>0</v>
+      </c>
+      <c r="N833">
+        <f>$AM$112</f>
+        <v>427</v>
+      </c>
+      <c r="P833">
+        <f>$AM$46</f>
+        <v>0.08</v>
+      </c>
+      <c r="Q833">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S833">
+        <f t="shared" si="92"/>
+        <v>7.154151685845159</v>
+      </c>
+      <c r="T833">
+        <f t="shared" si="73"/>
+        <v>0.14809093989699479</v>
+      </c>
+      <c r="U833">
+        <f t="shared" si="74"/>
+        <v>422.35536058622915</v>
+      </c>
+    </row>
+    <row r="834" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F834" t="s">
+        <v>302</v>
+      </c>
+      <c r="H834">
+        <v>30</v>
+      </c>
+      <c r="I834">
+        <v>90</v>
+      </c>
+      <c r="J834">
+        <v>0</v>
+      </c>
+      <c r="K834">
+        <v>0</v>
+      </c>
+      <c r="L834">
+        <f>$AC$14</f>
+        <v>0</v>
+      </c>
+      <c r="N834">
+        <f t="shared" ref="N834:N836" si="105">$AM$112</f>
+        <v>427</v>
+      </c>
+      <c r="P834">
+        <f t="shared" ref="P834:P836" si="106">$AM$46</f>
+        <v>0.08</v>
+      </c>
+      <c r="Q834">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S834">
+        <f t="shared" si="92"/>
+        <v>7.154151685845159</v>
+      </c>
+      <c r="T834">
+        <f t="shared" si="73"/>
+        <v>0.14809093989699479</v>
+      </c>
+      <c r="U834">
+        <f t="shared" si="74"/>
+        <v>399.84553772188593</v>
+      </c>
+    </row>
+    <row r="835" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F835" t="s">
+        <v>303</v>
+      </c>
+      <c r="H835">
+        <v>31</v>
+      </c>
+      <c r="I835">
+        <v>88</v>
+      </c>
+      <c r="J835">
+        <v>0</v>
+      </c>
+      <c r="K835">
+        <v>0</v>
+      </c>
+      <c r="N835">
+        <f t="shared" si="105"/>
+        <v>427</v>
+      </c>
+      <c r="P835">
+        <f t="shared" si="106"/>
+        <v>0.08</v>
+      </c>
+      <c r="Q835">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S835">
+        <f t="shared" si="92"/>
+        <v>7.154151685845159</v>
+      </c>
+      <c r="T835">
+        <f t="shared" si="73"/>
+        <v>0.14809093989699479</v>
+      </c>
+      <c r="U835">
+        <f t="shared" si="74"/>
+        <v>403.99208403900178</v>
+      </c>
+    </row>
+    <row r="836" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F836" t="s">
+        <v>304</v>
+      </c>
+      <c r="H836">
+        <v>30</v>
+      </c>
+      <c r="I836">
+        <v>80</v>
+      </c>
+      <c r="J836">
+        <v>0</v>
+      </c>
+      <c r="K836">
+        <v>0</v>
+      </c>
+      <c r="N836">
+        <f>$AM$113</f>
+        <v>420</v>
+      </c>
+      <c r="P836">
+        <f>$AM$47</f>
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="Q836">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S836">
+        <f t="shared" si="92"/>
+        <v>6.8178954321000003</v>
+      </c>
+      <c r="T836">
+        <f t="shared" ref="T836:T890" si="107">20.7 * S836 * 10^-3</f>
+        <v>0.14113043544447001</v>
+      </c>
+      <c r="U836">
+        <f t="shared" ref="U836:U890" si="108">H836*T836*I836</f>
+        <v>338.713045066728</v>
+      </c>
+    </row>
+    <row r="837" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F837" t="s">
+        <v>305</v>
+      </c>
+      <c r="H837">
+        <v>31</v>
+      </c>
+      <c r="I837">
+        <v>75</v>
+      </c>
+      <c r="J837">
+        <v>0</v>
+      </c>
+      <c r="K837">
+        <v>0</v>
+      </c>
+      <c r="N837">
+        <f t="shared" ref="N837:N838" si="109">$AM$113</f>
+        <v>420</v>
+      </c>
+      <c r="P837">
+        <f t="shared" ref="P837:P838" si="110">$AM$47</f>
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="Q837">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S837">
+        <f t="shared" si="92"/>
+        <v>6.8178954321000003</v>
+      </c>
+      <c r="T837">
+        <f t="shared" si="107"/>
+        <v>0.14113043544447001</v>
+      </c>
+      <c r="U837">
+        <f t="shared" si="108"/>
+        <v>328.12826240839274</v>
+      </c>
+    </row>
+    <row r="838" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F838" t="s">
+        <v>306</v>
+      </c>
+      <c r="H838">
+        <v>31</v>
+      </c>
+      <c r="I838">
+        <v>30</v>
+      </c>
+      <c r="J838">
+        <v>0.05</v>
+      </c>
+      <c r="K838">
+        <v>0</v>
+      </c>
+      <c r="N838">
+        <f t="shared" si="109"/>
+        <v>420</v>
+      </c>
+      <c r="P838">
+        <f t="shared" si="110"/>
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="Q838">
+        <f t="shared" si="83"/>
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="S838">
+        <f t="shared" si="92"/>
+        <v>6.9201638635814993</v>
+      </c>
+      <c r="T838">
+        <f t="shared" si="107"/>
+        <v>0.14324739197613703</v>
+      </c>
+      <c r="U838">
+        <f t="shared" si="108"/>
+        <v>133.22007453780742</v>
+      </c>
+    </row>
+    <row r="839" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F839" t="s">
+        <v>307</v>
+      </c>
+      <c r="H839">
+        <v>30</v>
+      </c>
+      <c r="I839">
+        <v>40</v>
+      </c>
+      <c r="J839">
+        <v>0.4</v>
+      </c>
+      <c r="K839">
+        <v>0.05</v>
+      </c>
+      <c r="N839">
+        <f>$AM$110</f>
+        <v>415</v>
+      </c>
+      <c r="P839">
+        <f>$AM$44</f>
+        <v>-0.05</v>
+      </c>
+      <c r="Q839">
+        <f t="shared" si="83"/>
+        <v>1.125</v>
+      </c>
+      <c r="S839">
+        <f t="shared" si="92"/>
+        <v>7.6375900903781213</v>
+      </c>
+      <c r="T839">
+        <f t="shared" si="107"/>
+        <v>0.15809811487082712</v>
+      </c>
+      <c r="U839">
+        <f t="shared" si="108"/>
+        <v>189.71773784499254</v>
+      </c>
+    </row>
+    <row r="840" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F840" t="s">
+        <v>308</v>
+      </c>
+      <c r="H840">
+        <v>31</v>
+      </c>
+      <c r="I840">
+        <v>55</v>
+      </c>
+      <c r="J840">
+        <v>0.3</v>
+      </c>
+      <c r="K840">
+        <v>0.45</v>
+      </c>
+      <c r="N840">
+        <f t="shared" ref="N840:N842" si="111">$AM$110</f>
+        <v>415</v>
+      </c>
+      <c r="P840">
+        <f t="shared" ref="P840:P842" si="112">$AM$44</f>
+        <v>-0.05</v>
+      </c>
+      <c r="Q840">
+        <f t="shared" si="83"/>
+        <v>1.135</v>
+      </c>
+      <c r="S840">
+        <f t="shared" si="92"/>
+        <v>7.7054797800703714</v>
+      </c>
+      <c r="T840">
+        <f t="shared" si="107"/>
+        <v>0.15950343144745668</v>
+      </c>
+      <c r="U840">
+        <f t="shared" si="108"/>
+        <v>271.95335061791366</v>
+      </c>
+    </row>
+    <row r="841" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F841" t="s">
+        <v>309</v>
+      </c>
+      <c r="H841">
+        <v>30</v>
+      </c>
+      <c r="I841">
+        <v>60</v>
+      </c>
+      <c r="J841">
+        <v>0.2</v>
+      </c>
+      <c r="K841">
+        <v>0.75</v>
+      </c>
+      <c r="N841">
+        <f t="shared" si="111"/>
+        <v>415</v>
+      </c>
+      <c r="P841">
+        <f t="shared" si="112"/>
+        <v>-0.05</v>
+      </c>
+      <c r="Q841">
+        <f t="shared" si="83"/>
+        <v>1.135</v>
+      </c>
+      <c r="S841">
+        <f t="shared" si="92"/>
+        <v>7.7054797800703714</v>
+      </c>
+      <c r="T841">
+        <f t="shared" si="107"/>
+        <v>0.15950343144745668</v>
+      </c>
+      <c r="U841">
+        <f t="shared" si="108"/>
+        <v>287.10617660542204</v>
+      </c>
+    </row>
+    <row r="842" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F842" t="s">
+        <v>310</v>
+      </c>
+      <c r="H842">
+        <v>31</v>
+      </c>
+      <c r="I842">
+        <v>80</v>
+      </c>
+      <c r="J842">
+        <v>0.05</v>
+      </c>
+      <c r="K842">
+        <v>0.91</v>
+      </c>
+      <c r="N842">
+        <f>$AM$111</f>
+        <v>405</v>
+      </c>
+      <c r="P842">
+        <f>$AM$45</f>
+        <v>0.31</v>
+      </c>
+      <c r="Q842">
+        <f t="shared" si="83"/>
+        <v>1.1059999999999999</v>
+      </c>
+      <c r="S842">
+        <f t="shared" si="92"/>
+        <v>8.0322201105268487</v>
+      </c>
+      <c r="T842">
+        <f t="shared" si="107"/>
+        <v>0.16626695628790578</v>
+      </c>
+      <c r="U842">
+        <f t="shared" si="108"/>
+        <v>412.34205159400631</v>
+      </c>
+    </row>
+    <row r="843" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E843" t="s">
+        <v>169</v>
+      </c>
+      <c r="F843" t="s">
+        <v>299</v>
+      </c>
+      <c r="H843">
+        <v>31</v>
+      </c>
+      <c r="I843">
+        <v>70</v>
+      </c>
+      <c r="J843">
+        <v>0</v>
+      </c>
+      <c r="K843">
+        <v>0</v>
+      </c>
+      <c r="L843">
+        <v>0</v>
+      </c>
+      <c r="N843">
+        <f>$AM$115</f>
+        <v>218</v>
+      </c>
+      <c r="P843">
+        <f>$AM$49</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q843">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S843">
+        <f t="shared" si="92"/>
+        <v>4.7400152152377588</v>
+      </c>
+      <c r="T843">
+        <f t="shared" si="107"/>
+        <v>9.8118314955421615E-2</v>
+      </c>
+      <c r="U843">
+        <f t="shared" si="108"/>
+        <v>212.9167434532649</v>
+      </c>
+    </row>
+    <row r="844" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E844" t="s">
+        <v>237</v>
+      </c>
+      <c r="F844" t="s">
+        <v>300</v>
+      </c>
+      <c r="H844">
+        <v>28</v>
+      </c>
+      <c r="I844">
+        <v>70</v>
+      </c>
+      <c r="J844">
+        <v>0</v>
+      </c>
+      <c r="K844">
+        <v>0</v>
+      </c>
+      <c r="L844">
+        <v>0</v>
+      </c>
+      <c r="N844">
+        <f>$AM$115</f>
+        <v>218</v>
+      </c>
+      <c r="P844">
+        <f>$AM$49</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q844">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S844">
+        <f t="shared" si="92"/>
+        <v>4.7400152152377588</v>
+      </c>
+      <c r="T844">
+        <f t="shared" si="107"/>
+        <v>9.8118314955421615E-2</v>
+      </c>
+      <c r="U844">
+        <f t="shared" si="108"/>
+        <v>192.31189731262634</v>
+      </c>
+    </row>
+    <row r="845" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F845" t="s">
+        <v>301</v>
+      </c>
+      <c r="H845">
+        <v>31</v>
+      </c>
+      <c r="I845">
+        <v>60</v>
+      </c>
+      <c r="J845">
+        <v>0</v>
+      </c>
+      <c r="K845">
+        <v>0</v>
+      </c>
+      <c r="L845">
+        <v>0</v>
+      </c>
+      <c r="N845">
+        <f>$AM$116</f>
+        <v>242</v>
+      </c>
+      <c r="P845">
+        <f>$AM$50</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q845">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S845">
+        <f t="shared" si="92"/>
+        <v>4.8709090305849614</v>
+      </c>
+      <c r="T845">
+        <f t="shared" si="107"/>
+        <v>0.10082781693310869</v>
+      </c>
+      <c r="U845">
+        <f t="shared" si="108"/>
+        <v>187.53973949558218</v>
+      </c>
+    </row>
+    <row r="846" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F846" t="s">
+        <v>302</v>
+      </c>
+      <c r="H846">
+        <v>30</v>
+      </c>
+      <c r="I846">
+        <v>50</v>
+      </c>
+      <c r="J846">
+        <v>0</v>
+      </c>
+      <c r="K846">
+        <v>0</v>
+      </c>
+      <c r="L846">
+        <v>0</v>
+      </c>
+      <c r="N846">
+        <f t="shared" ref="N846:N848" si="113">$AM$116</f>
+        <v>242</v>
+      </c>
+      <c r="P846">
+        <f t="shared" ref="P846:P848" si="114">$AM$50</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q846">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S846">
+        <f t="shared" si="92"/>
+        <v>4.8709090305849614</v>
+      </c>
+      <c r="T846">
+        <f t="shared" si="107"/>
+        <v>0.10082781693310869</v>
+      </c>
+      <c r="U846">
+        <f t="shared" si="108"/>
+        <v>151.24172539966304</v>
+      </c>
+    </row>
+    <row r="847" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F847" t="s">
+        <v>303</v>
+      </c>
+      <c r="H847">
+        <v>31</v>
+      </c>
+      <c r="I847">
+        <v>40</v>
+      </c>
+      <c r="J847">
+        <v>0</v>
+      </c>
+      <c r="K847">
+        <v>0</v>
+      </c>
+      <c r="L847">
+        <v>0</v>
+      </c>
+      <c r="N847">
+        <f t="shared" si="113"/>
+        <v>242</v>
+      </c>
+      <c r="P847">
+        <f t="shared" si="114"/>
+        <v>0.24</v>
+      </c>
+      <c r="Q847">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S847">
+        <f t="shared" si="92"/>
+        <v>4.8709090305849614</v>
+      </c>
+      <c r="T847">
+        <f t="shared" si="107"/>
+        <v>0.10082781693310869</v>
+      </c>
+      <c r="U847">
+        <f t="shared" si="108"/>
+        <v>125.02649299705479</v>
+      </c>
+    </row>
+    <row r="848" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F848" t="s">
+        <v>304</v>
+      </c>
+      <c r="H848">
+        <v>30</v>
+      </c>
+      <c r="I848">
+        <v>40</v>
+      </c>
+      <c r="J848">
+        <v>0</v>
+      </c>
+      <c r="K848">
+        <v>0</v>
+      </c>
+      <c r="L848">
+        <v>0</v>
+      </c>
+      <c r="N848">
+        <f>$AM$117</f>
+        <v>261</v>
+      </c>
+      <c r="P848">
+        <f>$AM$51</f>
+        <v>0.16</v>
+      </c>
+      <c r="Q848">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S848">
+        <f t="shared" si="92"/>
+        <v>5.03206019520516</v>
+      </c>
+      <c r="T848">
+        <f t="shared" si="107"/>
+        <v>0.10416364604074682</v>
+      </c>
+      <c r="U848">
+        <f t="shared" si="108"/>
+        <v>124.99637524889619</v>
+      </c>
+    </row>
+    <row r="849" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F849" t="s">
+        <v>305</v>
+      </c>
+      <c r="H849">
+        <v>31</v>
+      </c>
+      <c r="I849">
+        <v>20</v>
+      </c>
+      <c r="J849">
+        <v>0</v>
+      </c>
+      <c r="K849">
+        <v>0</v>
+      </c>
+      <c r="L849">
+        <v>0</v>
+      </c>
+      <c r="N849">
+        <f t="shared" ref="N849:N850" si="115">$AM$117</f>
+        <v>261</v>
+      </c>
+      <c r="P849">
+        <f t="shared" ref="P849:P850" si="116">$AM$51</f>
+        <v>0.16</v>
+      </c>
+      <c r="Q849">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S849">
+        <f t="shared" si="92"/>
+        <v>5.03206019520516</v>
+      </c>
+      <c r="T849">
+        <f t="shared" si="107"/>
+        <v>0.10416364604074682</v>
+      </c>
+      <c r="U849">
+        <f t="shared" si="108"/>
+        <v>64.581460545263027</v>
+      </c>
+    </row>
+    <row r="850" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F850" t="s">
+        <v>306</v>
+      </c>
+      <c r="H850">
+        <v>31</v>
+      </c>
+      <c r="I850">
+        <v>20</v>
+      </c>
+      <c r="J850">
+        <v>0</v>
+      </c>
+      <c r="K850">
+        <v>0</v>
+      </c>
+      <c r="L850">
+        <v>0</v>
+      </c>
+      <c r="N850">
+        <f t="shared" si="115"/>
+        <v>261</v>
+      </c>
+      <c r="P850">
+        <f t="shared" si="116"/>
+        <v>0.16</v>
+      </c>
+      <c r="Q850">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S850">
+        <f t="shared" si="92"/>
+        <v>5.03206019520516</v>
+      </c>
+      <c r="T850">
+        <f t="shared" si="107"/>
+        <v>0.10416364604074682</v>
+      </c>
+      <c r="U850">
+        <f t="shared" si="108"/>
+        <v>64.581460545263027</v>
+      </c>
+    </row>
+    <row r="851" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F851" t="s">
+        <v>307</v>
+      </c>
+      <c r="H851">
+        <v>30</v>
+      </c>
+      <c r="I851">
+        <v>20</v>
+      </c>
+      <c r="J851">
+        <v>0</v>
+      </c>
+      <c r="K851">
+        <v>0</v>
+      </c>
+      <c r="L851">
+        <v>0</v>
+      </c>
+      <c r="N851">
+        <f>$AM$114</f>
+        <v>272</v>
+      </c>
+      <c r="P851">
+        <f>$AM$48</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q851">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="S851">
+        <f t="shared" si="92"/>
+        <v>5.3917843108665613</v>
+      </c>
+      <c r="T851">
+        <f t="shared" si="107"/>
+        <v>0.11160993523493781</v>
+      </c>
+      <c r="U851">
+        <f t="shared" si="108"/>
+        <v>66.96596114096269</v>
+      </c>
+    </row>
+    <row r="852" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F852" t="s">
+        <v>308</v>
+      </c>
+      <c r="H852">
+        <v>31</v>
+      </c>
+      <c r="I852">
+        <v>30</v>
+      </c>
+      <c r="J852">
+        <v>0</v>
+      </c>
+      <c r="K852">
+        <v>0</v>
+      </c>
+      <c r="L852">
+        <v>0</v>
+      </c>
+      <c r="N852">
+        <f t="shared" ref="N852:N854" si="117">$AM$114</f>
+        <v>272</v>
+      </c>
+      <c r="P852">
+        <f t="shared" ref="P852:P854" si="118">$AM$48</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q852">
+        <f t="shared" ref="Q852:Q890" si="119">(J852 * $AD$4 +K852* $AD$5) + (1 -J852 - K852 )</f>
+        <v>1</v>
+      </c>
+      <c r="S852">
+        <f t="shared" si="92"/>
+        <v>5.3917843108665613</v>
+      </c>
+      <c r="T852">
+        <f t="shared" si="107"/>
+        <v>0.11160993523493781</v>
+      </c>
+      <c r="U852">
+        <f t="shared" si="108"/>
+        <v>103.79723976849216</v>
+      </c>
+    </row>
+    <row r="853" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F853" t="s">
+        <v>309</v>
+      </c>
+      <c r="H853">
+        <v>30</v>
+      </c>
+      <c r="I853">
+        <v>50</v>
+      </c>
+      <c r="J853">
+        <v>0</v>
+      </c>
+      <c r="K853">
+        <v>0</v>
+      </c>
+      <c r="L853">
+        <v>0</v>
+      </c>
+      <c r="N853">
+        <f t="shared" si="117"/>
+        <v>272</v>
+      </c>
+      <c r="P853">
+        <f t="shared" si="118"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q853">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S853">
+        <f t="shared" si="92"/>
+        <v>5.3917843108665613</v>
+      </c>
+      <c r="T853">
+        <f t="shared" si="107"/>
+        <v>0.11160993523493781</v>
+      </c>
+      <c r="U853">
+        <f t="shared" si="108"/>
+        <v>167.41490285240673</v>
+      </c>
+    </row>
+    <row r="854" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F854" t="s">
+        <v>310</v>
+      </c>
+      <c r="H854">
+        <v>31</v>
+      </c>
+      <c r="I854">
+        <v>60</v>
+      </c>
+      <c r="J854">
+        <v>0</v>
+      </c>
+      <c r="K854">
+        <v>0</v>
+      </c>
+      <c r="L854">
+        <v>0</v>
+      </c>
+      <c r="N854">
+        <f>$AM$115</f>
+        <v>218</v>
+      </c>
+      <c r="P854">
+        <f>$AM$49</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q854">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S854">
+        <f t="shared" si="92"/>
+        <v>4.7400152152377588</v>
+      </c>
+      <c r="T854">
+        <f t="shared" si="107"/>
+        <v>9.8118314955421615E-2</v>
+      </c>
+      <c r="U854">
+        <f t="shared" si="108"/>
+        <v>182.50006581708419</v>
+      </c>
+    </row>
+    <row r="855" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E855" t="s">
+        <v>171</v>
+      </c>
+      <c r="F855" t="s">
+        <v>299</v>
+      </c>
+      <c r="H855">
+        <v>31</v>
+      </c>
+      <c r="I855">
+        <v>100</v>
+      </c>
+      <c r="J855">
+        <v>0</v>
+      </c>
+      <c r="K855">
+        <v>0</v>
+      </c>
+      <c r="L855">
+        <v>0</v>
+      </c>
+      <c r="N855">
+        <f>$AM$119</f>
+        <v>315</v>
+      </c>
+      <c r="P855">
+        <f>$AM$53</f>
+        <v>0.26</v>
+      </c>
+      <c r="Q855">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S855">
+        <f t="shared" si="92"/>
+        <v>5.9487941702249998</v>
+      </c>
+      <c r="T855">
+        <f t="shared" si="107"/>
+        <v>0.1231400393236575</v>
+      </c>
+      <c r="U855">
+        <f t="shared" si="108"/>
+        <v>381.73412190333823</v>
+      </c>
+    </row>
+    <row r="856" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E856" t="s">
+        <v>238</v>
+      </c>
+      <c r="F856" t="s">
+        <v>300</v>
+      </c>
+      <c r="H856">
+        <v>28</v>
+      </c>
+      <c r="I856">
+        <v>100</v>
+      </c>
+      <c r="J856">
+        <v>0</v>
+      </c>
+      <c r="K856">
+        <v>0</v>
+      </c>
+      <c r="L856">
+        <v>0</v>
+      </c>
+      <c r="N856">
+        <f>$AM$119</f>
+        <v>315</v>
+      </c>
+      <c r="P856">
+        <f>$AM$53</f>
+        <v>0.26</v>
+      </c>
+      <c r="Q856">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S856">
+        <f t="shared" si="92"/>
+        <v>5.9487941702249998</v>
+      </c>
+      <c r="T856">
+        <f t="shared" si="107"/>
+        <v>0.1231400393236575</v>
+      </c>
+      <c r="U856">
+        <f t="shared" si="108"/>
+        <v>344.79211010624101</v>
+      </c>
+    </row>
+    <row r="857" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F857" t="s">
+        <v>301</v>
+      </c>
+      <c r="H857">
+        <v>31</v>
+      </c>
+      <c r="I857">
+        <v>70</v>
+      </c>
+      <c r="J857">
+        <v>0</v>
+      </c>
+      <c r="K857">
+        <v>0</v>
+      </c>
+      <c r="L857">
+        <v>0</v>
+      </c>
+      <c r="N857">
+        <f>$AM$120</f>
+        <v>320</v>
+      </c>
+      <c r="P857">
+        <f>$AM$54</f>
+        <v>0.15</v>
+      </c>
+      <c r="Q857">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S857">
+        <f t="shared" si="92"/>
+        <v>5.8506418160999987</v>
+      </c>
+      <c r="T857">
+        <f t="shared" si="107"/>
+        <v>0.12110828559326997</v>
+      </c>
+      <c r="U857">
+        <f t="shared" si="108"/>
+        <v>262.80497973739585</v>
+      </c>
+    </row>
+    <row r="858" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F858" t="s">
+        <v>302</v>
+      </c>
+      <c r="H858">
+        <v>30</v>
+      </c>
+      <c r="I858">
+        <v>70</v>
+      </c>
+      <c r="J858">
+        <v>0</v>
+      </c>
+      <c r="K858">
+        <v>0</v>
+      </c>
+      <c r="L858">
+        <v>0</v>
+      </c>
+      <c r="N858">
+        <f t="shared" ref="N858:N860" si="120">$AM$120</f>
+        <v>320</v>
+      </c>
+      <c r="P858">
+        <f t="shared" ref="P858:P860" si="121">$AM$54</f>
+        <v>0.15</v>
+      </c>
+      <c r="Q858">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S858">
+        <f t="shared" si="92"/>
+        <v>5.8506418160999987</v>
+      </c>
+      <c r="T858">
+        <f t="shared" si="107"/>
+        <v>0.12110828559326997</v>
+      </c>
+      <c r="U858">
+        <f t="shared" si="108"/>
+        <v>254.32739974586696</v>
+      </c>
+    </row>
+    <row r="859" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F859" t="s">
+        <v>303</v>
+      </c>
+      <c r="H859">
+        <v>31</v>
+      </c>
+      <c r="I859">
+        <v>68</v>
+      </c>
+      <c r="J859">
+        <v>0</v>
+      </c>
+      <c r="K859">
+        <v>0</v>
+      </c>
+      <c r="L859">
+        <v>0</v>
+      </c>
+      <c r="N859">
+        <f t="shared" si="120"/>
+        <v>320</v>
+      </c>
+      <c r="P859">
+        <f t="shared" si="121"/>
+        <v>0.15</v>
+      </c>
+      <c r="Q859">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S859">
+        <f t="shared" si="92"/>
+        <v>5.8506418160999987</v>
+      </c>
+      <c r="T859">
+        <f t="shared" si="107"/>
+        <v>0.12110828559326997</v>
+      </c>
+      <c r="U859">
+        <f t="shared" si="108"/>
+        <v>255.29626603061311</v>
+      </c>
+    </row>
+    <row r="860" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F860" t="s">
+        <v>304</v>
+      </c>
+      <c r="H860">
+        <v>30</v>
+      </c>
+      <c r="I860">
+        <v>40</v>
+      </c>
+      <c r="J860">
+        <v>0</v>
+      </c>
+      <c r="K860">
+        <v>0</v>
+      </c>
+      <c r="L860">
+        <v>0</v>
+      </c>
+      <c r="N860">
+        <f>$AM$121</f>
+        <v>342</v>
+      </c>
+      <c r="P860">
+        <f>$AM$55</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q860">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S860">
+        <f t="shared" si="92"/>
+        <v>6.551417013816959</v>
+      </c>
+      <c r="T860">
+        <f t="shared" si="107"/>
+        <v>0.13561433218601104</v>
+      </c>
+      <c r="U860">
+        <f t="shared" si="108"/>
+        <v>162.73719862321326</v>
+      </c>
+    </row>
+    <row r="861" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F861" t="s">
+        <v>305</v>
+      </c>
+      <c r="H861">
+        <v>31</v>
+      </c>
+      <c r="I861">
+        <v>40</v>
+      </c>
+      <c r="J861">
+        <v>0</v>
+      </c>
+      <c r="K861">
+        <v>0</v>
+      </c>
+      <c r="L861">
+        <v>0</v>
+      </c>
+      <c r="N861">
+        <f t="shared" ref="N861:N862" si="122">$AM$121</f>
+        <v>342</v>
+      </c>
+      <c r="P861">
+        <f t="shared" ref="P861:P862" si="123">$AM$55</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q861">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S861">
+        <f t="shared" si="92"/>
+        <v>6.551417013816959</v>
+      </c>
+      <c r="T861">
+        <f t="shared" si="107"/>
+        <v>0.13561433218601104</v>
+      </c>
+      <c r="U861">
+        <f t="shared" si="108"/>
+        <v>168.16177191065373</v>
+      </c>
+    </row>
+    <row r="862" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F862" t="s">
+        <v>306</v>
+      </c>
+      <c r="H862">
+        <v>31</v>
+      </c>
+      <c r="I862">
+        <v>40</v>
+      </c>
+      <c r="J862">
+        <v>0</v>
+      </c>
+      <c r="K862">
+        <v>0</v>
+      </c>
+      <c r="L862">
+        <v>0</v>
+      </c>
+      <c r="N862">
+        <f t="shared" si="122"/>
+        <v>342</v>
+      </c>
+      <c r="P862">
+        <f t="shared" si="123"/>
+        <v>0.4</v>
+      </c>
+      <c r="Q862">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S862">
+        <f t="shared" si="92"/>
+        <v>6.551417013816959</v>
+      </c>
+      <c r="T862">
+        <f t="shared" si="107"/>
+        <v>0.13561433218601104</v>
+      </c>
+      <c r="U862">
+        <f t="shared" si="108"/>
+        <v>168.16177191065373</v>
+      </c>
+    </row>
+    <row r="863" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F863" t="s">
+        <v>307</v>
+      </c>
+      <c r="H863">
+        <v>30</v>
+      </c>
+      <c r="I863">
+        <v>25</v>
+      </c>
+      <c r="J863">
+        <v>0</v>
+      </c>
+      <c r="K863">
+        <v>0</v>
+      </c>
+      <c r="L863">
+        <v>0</v>
+      </c>
+      <c r="N863">
+        <f>$AM$118</f>
+        <v>392</v>
+      </c>
+      <c r="P863">
+        <f>$AM$52</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Q863">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S863">
+        <f t="shared" si="92"/>
+        <v>7.5333978518529587</v>
+      </c>
+      <c r="T863">
+        <f t="shared" si="107"/>
+        <v>0.15594133553335623</v>
+      </c>
+      <c r="U863">
+        <f t="shared" si="108"/>
+        <v>116.95600165001719</v>
+      </c>
+    </row>
+    <row r="864" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F864" t="s">
+        <v>308</v>
+      </c>
+      <c r="H864">
+        <v>31</v>
+      </c>
+      <c r="I864">
+        <v>60</v>
+      </c>
+      <c r="J864">
+        <v>0</v>
+      </c>
+      <c r="K864">
+        <v>0</v>
+      </c>
+      <c r="L864">
+        <v>0</v>
+      </c>
+      <c r="N864">
+        <f t="shared" ref="N864:N866" si="124">$AM$118</f>
+        <v>392</v>
+      </c>
+      <c r="P864">
+        <f t="shared" ref="P864:P866" si="125">$AM$52</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Q864">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S864">
+        <f t="shared" si="92"/>
+        <v>7.5333978518529587</v>
+      </c>
+      <c r="T864">
+        <f t="shared" si="107"/>
+        <v>0.15594133553335623</v>
+      </c>
+      <c r="U864">
+        <f t="shared" si="108"/>
+        <v>290.05088409204262</v>
+      </c>
+    </row>
+    <row r="865" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F865" t="s">
+        <v>309</v>
+      </c>
+      <c r="H865">
+        <v>30</v>
+      </c>
+      <c r="I865">
+        <v>90</v>
+      </c>
+      <c r="J865">
+        <v>0</v>
+      </c>
+      <c r="K865">
+        <v>0</v>
+      </c>
+      <c r="L865">
+        <v>0</v>
+      </c>
+      <c r="N865">
+        <f t="shared" si="124"/>
+        <v>392</v>
+      </c>
+      <c r="P865">
+        <f t="shared" si="125"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Q865">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S865">
+        <f t="shared" si="92"/>
+        <v>7.5333978518529587</v>
+      </c>
+      <c r="T865">
+        <f t="shared" si="107"/>
+        <v>0.15594133553335623</v>
+      </c>
+      <c r="U865">
+        <f t="shared" si="108"/>
+        <v>421.04160594006186</v>
+      </c>
+    </row>
+    <row r="866" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F866" t="s">
+        <v>310</v>
+      </c>
+      <c r="H866">
+        <v>31</v>
+      </c>
+      <c r="I866">
+        <v>95</v>
+      </c>
+      <c r="J866">
+        <v>0</v>
+      </c>
+      <c r="K866">
+        <v>0</v>
+      </c>
+      <c r="L866">
+        <v>0</v>
+      </c>
+      <c r="N866">
+        <f>$AM$119</f>
+        <v>315</v>
+      </c>
+      <c r="P866">
+        <f>$AM$53</f>
+        <v>0.26</v>
+      </c>
+      <c r="Q866">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S866">
+        <f t="shared" si="92"/>
+        <v>5.9487941702249998</v>
+      </c>
+      <c r="T866">
+        <f t="shared" si="107"/>
+        <v>0.1231400393236575</v>
+      </c>
+      <c r="U866">
+        <f t="shared" si="108"/>
+        <v>362.64741580817133</v>
+      </c>
+    </row>
+    <row r="867" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E867" t="s">
+        <v>164</v>
+      </c>
+      <c r="F867" t="s">
+        <v>299</v>
+      </c>
+      <c r="H867">
+        <v>31</v>
+      </c>
+      <c r="I867">
+        <v>38</v>
+      </c>
+      <c r="J867">
+        <v>0</v>
+      </c>
+      <c r="K867">
+        <v>0</v>
+      </c>
+      <c r="L867">
+        <v>0</v>
+      </c>
+      <c r="N867">
+        <f>$AM$123</f>
+        <v>133</v>
+      </c>
+      <c r="P867">
+        <f>$AM$57</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q867">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S867">
+        <f t="shared" si="92"/>
+        <v>3.1931138214979606</v>
+      </c>
+      <c r="T867">
+        <f t="shared" si="107"/>
+        <v>6.6097456105007779E-2</v>
+      </c>
+      <c r="U867">
+        <f t="shared" si="108"/>
+        <v>77.862803291699166</v>
+      </c>
+    </row>
+    <row r="868" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E868">
+        <v>6</v>
+      </c>
+      <c r="F868" t="s">
+        <v>300</v>
+      </c>
+      <c r="H868">
+        <v>28</v>
+      </c>
+      <c r="I868">
+        <v>38</v>
+      </c>
+      <c r="J868">
+        <v>0</v>
+      </c>
+      <c r="K868">
+        <v>0</v>
+      </c>
+      <c r="L868">
+        <v>0</v>
+      </c>
+      <c r="N868">
+        <f>$AM$123</f>
+        <v>133</v>
+      </c>
+      <c r="P868">
+        <f>$AM$57</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q868">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S868">
+        <f t="shared" si="92"/>
+        <v>3.1931138214979606</v>
+      </c>
+      <c r="T868">
+        <f t="shared" si="107"/>
+        <v>6.6097456105007779E-2</v>
+      </c>
+      <c r="U868">
+        <f t="shared" si="108"/>
+        <v>70.327693295728281</v>
+      </c>
+    </row>
+    <row r="869" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F869" t="s">
+        <v>301</v>
+      </c>
+      <c r="H869">
+        <v>31</v>
+      </c>
+      <c r="I869">
+        <v>35</v>
+      </c>
+      <c r="J869">
+        <v>0</v>
+      </c>
+      <c r="K869">
+        <v>0</v>
+      </c>
+      <c r="L869">
+        <v>0</v>
+      </c>
+      <c r="N869">
+        <f>$AM$124</f>
+        <v>146</v>
+      </c>
+      <c r="P869">
+        <f>$AM$58</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q869">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S869">
+        <f t="shared" si="92"/>
+        <v>3.3612396901185604</v>
+      </c>
+      <c r="T869">
+        <f t="shared" si="107"/>
+        <v>6.9577661585454198E-2</v>
+      </c>
+      <c r="U869">
+        <f t="shared" si="108"/>
+        <v>75.491762820217801</v>
+      </c>
+    </row>
+    <row r="870" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F870" t="s">
+        <v>302</v>
+      </c>
+      <c r="H870">
+        <v>30</v>
+      </c>
+      <c r="I870">
+        <v>34</v>
+      </c>
+      <c r="J870">
+        <v>0</v>
+      </c>
+      <c r="K870">
+        <v>0</v>
+      </c>
+      <c r="L870">
+        <v>0</v>
+      </c>
+      <c r="N870">
+        <f t="shared" ref="N870:N871" si="126">$AM$124</f>
+        <v>146</v>
+      </c>
+      <c r="P870">
+        <f t="shared" ref="P870:P871" si="127">$AM$58</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q870">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S870">
+        <f t="shared" si="92"/>
+        <v>3.3612396901185604</v>
+      </c>
+      <c r="T870">
+        <f t="shared" si="107"/>
+        <v>6.9577661585454198E-2</v>
+      </c>
+      <c r="U870">
+        <f t="shared" si="108"/>
+        <v>70.969214817163277</v>
+      </c>
+    </row>
+    <row r="871" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F871" t="s">
+        <v>303</v>
+      </c>
+      <c r="H871">
+        <v>31</v>
+      </c>
+      <c r="I871">
+        <v>33</v>
+      </c>
+      <c r="J871">
+        <v>0</v>
+      </c>
+      <c r="K871">
+        <v>0</v>
+      </c>
+      <c r="L871">
+        <v>0</v>
+      </c>
+      <c r="N871">
+        <f t="shared" si="126"/>
+        <v>146</v>
+      </c>
+      <c r="P871">
+        <f t="shared" si="127"/>
+        <v>0.13</v>
+      </c>
+      <c r="Q871">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S871">
+        <f t="shared" si="92"/>
+        <v>3.3612396901185604</v>
+      </c>
+      <c r="T871">
+        <f t="shared" si="107"/>
+        <v>6.9577661585454198E-2</v>
+      </c>
+      <c r="U871">
+        <f t="shared" si="108"/>
+        <v>71.177947801919643</v>
+      </c>
+    </row>
+    <row r="872" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F872" t="s">
+        <v>304</v>
+      </c>
+      <c r="H872">
+        <v>30</v>
+      </c>
+      <c r="I872">
+        <v>20</v>
+      </c>
+      <c r="J872">
+        <v>0</v>
+      </c>
+      <c r="K872">
+        <v>0</v>
+      </c>
+      <c r="L872">
+        <v>0</v>
+      </c>
+      <c r="N872">
+        <f>$AM$125</f>
+        <v>157</v>
+      </c>
+      <c r="P872">
+        <f>$AM$59</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q872">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S872">
+        <f t="shared" si="92"/>
+        <v>3.5142848777347604</v>
+      </c>
+      <c r="T872">
+        <f t="shared" si="107"/>
+        <v>7.2745696969109527E-2</v>
+      </c>
+      <c r="U872">
+        <f t="shared" si="108"/>
+        <v>43.64741818146571</v>
+      </c>
+    </row>
+    <row r="873" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F873" t="s">
+        <v>305</v>
+      </c>
+      <c r="H873">
+        <v>31</v>
+      </c>
+      <c r="I873">
+        <v>18</v>
+      </c>
+      <c r="J873">
+        <v>0</v>
+      </c>
+      <c r="K873">
+        <v>0</v>
+      </c>
+      <c r="L873">
+        <v>0</v>
+      </c>
+      <c r="N873">
+        <f t="shared" ref="N873:N874" si="128">$AM$125</f>
+        <v>157</v>
+      </c>
+      <c r="P873">
+        <f t="shared" ref="P873:P874" si="129">$AM$59</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q873">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S873">
+        <f t="shared" si="92"/>
+        <v>3.5142848777347604</v>
+      </c>
+      <c r="T873">
+        <f t="shared" si="107"/>
+        <v>7.2745696969109527E-2</v>
+      </c>
+      <c r="U873">
+        <f t="shared" si="108"/>
+        <v>40.59209890876312</v>
+      </c>
+    </row>
+    <row r="874" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F874" t="s">
+        <v>306</v>
+      </c>
+      <c r="H874">
+        <v>31</v>
+      </c>
+      <c r="I874">
+        <v>18</v>
+      </c>
+      <c r="J874">
+        <v>0</v>
+      </c>
+      <c r="K874">
+        <v>0</v>
+      </c>
+      <c r="L874">
+        <v>0</v>
+      </c>
+      <c r="N874">
+        <f t="shared" si="128"/>
+        <v>157</v>
+      </c>
+      <c r="P874">
+        <f t="shared" si="129"/>
+        <v>0.13</v>
+      </c>
+      <c r="Q874">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S874">
+        <f t="shared" si="92"/>
+        <v>3.5142848777347604</v>
+      </c>
+      <c r="T874">
+        <f t="shared" si="107"/>
+        <v>7.2745696969109527E-2</v>
+      </c>
+      <c r="U874">
+        <f t="shared" si="108"/>
+        <v>40.59209890876312</v>
+      </c>
+    </row>
+    <row r="875" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F875" t="s">
+        <v>307</v>
+      </c>
+      <c r="H875">
+        <v>30</v>
+      </c>
+      <c r="I875">
+        <v>20</v>
+      </c>
+      <c r="J875">
+        <v>0</v>
+      </c>
+      <c r="K875">
+        <v>0</v>
+      </c>
+      <c r="L875">
+        <v>0</v>
+      </c>
+      <c r="N875">
+        <f>$AM$122</f>
+        <v>170</v>
+      </c>
+      <c r="P875">
+        <f>$AM$56</f>
+        <v>0.34</v>
+      </c>
+      <c r="Q875">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S875">
+        <f t="shared" ref="S875:S890" si="130">(1.185 + 0.00454 * N875- 0.0000026 * N875^2 + 0.315 * P875 )^2 * Q875</f>
+        <v>3.9551663375999992</v>
+      </c>
+      <c r="T875">
+        <f t="shared" si="107"/>
+        <v>8.1871943188319973E-2</v>
+      </c>
+      <c r="U875">
+        <f t="shared" si="108"/>
+        <v>49.123165912991986</v>
+      </c>
+    </row>
+    <row r="876" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F876" t="s">
+        <v>308</v>
+      </c>
+      <c r="H876">
+        <v>31</v>
+      </c>
+      <c r="I876">
+        <v>38</v>
+      </c>
+      <c r="J876">
+        <v>0</v>
+      </c>
+      <c r="K876">
+        <v>0</v>
+      </c>
+      <c r="L876">
+        <v>0</v>
+      </c>
+      <c r="N876">
+        <f t="shared" ref="N876:N878" si="131">$AM$122</f>
+        <v>170</v>
+      </c>
+      <c r="P876">
+        <f t="shared" ref="P876:P878" si="132">$AM$56</f>
+        <v>0.34</v>
+      </c>
+      <c r="Q876">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S876">
+        <f t="shared" si="130"/>
+        <v>3.9551663375999992</v>
+      </c>
+      <c r="T876">
+        <f t="shared" si="107"/>
+        <v>8.1871943188319973E-2</v>
+      </c>
+      <c r="U876">
+        <f t="shared" si="108"/>
+        <v>96.445149075840931</v>
+      </c>
+    </row>
+    <row r="877" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F877" t="s">
+        <v>309</v>
+      </c>
+      <c r="H877">
+        <v>30</v>
+      </c>
+      <c r="I877">
+        <v>40</v>
+      </c>
+      <c r="J877">
+        <v>0</v>
+      </c>
+      <c r="K877">
+        <v>0</v>
+      </c>
+      <c r="L877">
+        <v>0</v>
+      </c>
+      <c r="N877">
+        <f t="shared" si="131"/>
+        <v>170</v>
+      </c>
+      <c r="P877">
+        <f t="shared" si="132"/>
+        <v>0.34</v>
+      </c>
+      <c r="Q877">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S877">
+        <f t="shared" si="130"/>
+        <v>3.9551663375999992</v>
+      </c>
+      <c r="T877">
+        <f t="shared" si="107"/>
+        <v>8.1871943188319973E-2</v>
+      </c>
+      <c r="U877">
+        <f t="shared" si="108"/>
+        <v>98.246331825983972</v>
+      </c>
+    </row>
+    <row r="878" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="F878" t="s">
+        <v>310</v>
+      </c>
+      <c r="H878">
+        <v>31</v>
+      </c>
+      <c r="I878">
+        <v>40</v>
+      </c>
+      <c r="J878">
+        <v>0</v>
+      </c>
+      <c r="K878">
+        <v>0</v>
+      </c>
+      <c r="L878">
+        <v>0</v>
+      </c>
+      <c r="N878">
+        <f>$AM$123</f>
+        <v>133</v>
+      </c>
+      <c r="P878">
+        <f>$AM$57</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q878">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S878">
+        <f t="shared" si="130"/>
+        <v>3.1931138214979606</v>
+      </c>
+      <c r="T878">
+        <f t="shared" si="107"/>
+        <v>6.6097456105007779E-2</v>
+      </c>
+      <c r="U878">
+        <f t="shared" si="108"/>
+        <v>81.960845570209656</v>
+      </c>
+    </row>
+    <row r="879" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E879" t="s">
+        <v>176</v>
+      </c>
+      <c r="F879" t="s">
+        <v>299</v>
+      </c>
+      <c r="H879">
+        <v>31</v>
+      </c>
+      <c r="I879">
+        <v>40</v>
+      </c>
+      <c r="J879">
+        <v>0</v>
+      </c>
+      <c r="K879">
+        <v>0</v>
+      </c>
+      <c r="L879">
+        <v>0</v>
+      </c>
+      <c r="N879">
+        <f>$AM$127</f>
+        <v>445</v>
+      </c>
+      <c r="P879">
+        <f>$AM$61</f>
+        <v>0.43</v>
+      </c>
+      <c r="Q879">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S879">
+        <f t="shared" si="130"/>
+        <v>7.9856260332249995</v>
+      </c>
+      <c r="T879">
+        <f t="shared" si="107"/>
+        <v>0.16530245888775749</v>
+      </c>
+      <c r="U879">
+        <f t="shared" si="108"/>
+        <v>204.97504902081928</v>
+      </c>
+    </row>
+    <row r="880" spans="5:21" x14ac:dyDescent="0.2">
+      <c r="E880" t="s">
+        <v>239</v>
+      </c>
+      <c r="F880" t="s">
+        <v>300</v>
+      </c>
+      <c r="H880">
+        <v>28</v>
+      </c>
+      <c r="I880">
+        <v>38</v>
+      </c>
+      <c r="J880">
+        <v>0</v>
+      </c>
+      <c r="K880">
+        <v>0</v>
+      </c>
+      <c r="L880">
+        <v>0</v>
+      </c>
+      <c r="N880">
+        <f>$AM$127</f>
+        <v>445</v>
+      </c>
+      <c r="P880">
+        <f>$AM$61</f>
+        <v>0.43</v>
+      </c>
+      <c r="Q880">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S880">
+        <f t="shared" si="130"/>
+        <v>7.9856260332249995</v>
+      </c>
+      <c r="T880">
+        <f t="shared" si="107"/>
+        <v>0.16530245888775749</v>
+      </c>
+      <c r="U880">
+        <f t="shared" si="108"/>
+        <v>175.88181625657398</v>
+      </c>
+    </row>
+    <row r="881" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F881" t="s">
+        <v>301</v>
+      </c>
+      <c r="H881">
+        <v>31</v>
+      </c>
+      <c r="I881">
+        <v>25</v>
+      </c>
+      <c r="J881">
+        <v>0</v>
+      </c>
+      <c r="K881">
+        <v>0</v>
+      </c>
+      <c r="L881">
+        <v>0</v>
+      </c>
+      <c r="N881">
+        <f>$AM$128</f>
+        <v>471</v>
+      </c>
+      <c r="P881">
+        <f>$AM$62</f>
+        <v>0.21</v>
+      </c>
+      <c r="Q881">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S881">
+        <f t="shared" si="130"/>
+        <v>7.9113004163715583</v>
+      </c>
+      <c r="T881">
+        <f t="shared" si="107"/>
+        <v>0.16376391861889125</v>
+      </c>
+      <c r="U881">
+        <f t="shared" si="108"/>
+        <v>126.91703692964072</v>
+      </c>
+    </row>
+    <row r="882" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F882" t="s">
+        <v>302</v>
+      </c>
+      <c r="H882">
+        <v>30</v>
+      </c>
+      <c r="I882">
+        <v>20</v>
+      </c>
+      <c r="J882">
+        <v>0</v>
+      </c>
+      <c r="K882">
+        <v>0</v>
+      </c>
+      <c r="L882">
+        <v>0</v>
+      </c>
+      <c r="N882">
+        <f t="shared" ref="N882:N884" si="133">$AM$128</f>
+        <v>471</v>
+      </c>
+      <c r="P882">
+        <f t="shared" ref="P882:P884" si="134">$AM$62</f>
+        <v>0.21</v>
+      </c>
+      <c r="Q882">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S882">
+        <f t="shared" si="130"/>
+        <v>7.9113004163715583</v>
+      </c>
+      <c r="T882">
+        <f t="shared" si="107"/>
+        <v>0.16376391861889125</v>
+      </c>
+      <c r="U882">
+        <f t="shared" si="108"/>
+        <v>98.258351171334766</v>
+      </c>
+    </row>
+    <row r="883" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F883" t="s">
+        <v>303</v>
+      </c>
+      <c r="H883">
+        <v>31</v>
+      </c>
+      <c r="I883">
+        <v>20</v>
+      </c>
+      <c r="J883">
+        <v>0</v>
+      </c>
+      <c r="K883">
+        <v>0</v>
+      </c>
+      <c r="L883">
+        <v>0</v>
+      </c>
+      <c r="N883">
+        <f t="shared" si="133"/>
+        <v>471</v>
+      </c>
+      <c r="P883">
+        <f t="shared" si="134"/>
+        <v>0.21</v>
+      </c>
+      <c r="Q883">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S883">
+        <f t="shared" si="130"/>
+        <v>7.9113004163715583</v>
+      </c>
+      <c r="T883">
+        <f t="shared" si="107"/>
+        <v>0.16376391861889125</v>
+      </c>
+      <c r="U883">
+        <f t="shared" si="108"/>
+        <v>101.53362954371258</v>
+      </c>
+    </row>
+    <row r="884" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F884" t="s">
+        <v>304</v>
+      </c>
+      <c r="H884">
+        <v>30</v>
+      </c>
+      <c r="I884">
+        <v>0</v>
+      </c>
+      <c r="J884">
+        <v>0</v>
+      </c>
+      <c r="K884">
+        <v>0</v>
+      </c>
+      <c r="L884">
+        <v>0</v>
+      </c>
+      <c r="N884">
+        <f>$AM$129</f>
+        <v>484</v>
+      </c>
+      <c r="P884">
+        <f>$AM$63</f>
+        <v>0.33</v>
+      </c>
+      <c r="Q884">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S884">
+        <f t="shared" si="130"/>
+        <v>8.278535337331359</v>
+      </c>
+      <c r="T884">
+        <f t="shared" si="107"/>
+        <v>0.17136568148275913</v>
+      </c>
+      <c r="U884">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F885" t="s">
+        <v>305</v>
+      </c>
+      <c r="H885">
+        <v>31</v>
+      </c>
+      <c r="I885">
+        <v>0</v>
+      </c>
+      <c r="J885">
+        <v>0</v>
+      </c>
+      <c r="K885">
+        <v>0</v>
+      </c>
+      <c r="L885">
+        <v>0</v>
+      </c>
+      <c r="N885">
+        <f t="shared" ref="N885:N886" si="135">$AM$129</f>
+        <v>484</v>
+      </c>
+      <c r="P885">
+        <f t="shared" ref="P885:P886" si="136">$AM$63</f>
+        <v>0.33</v>
+      </c>
+      <c r="Q885">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S885">
+        <f t="shared" si="130"/>
+        <v>8.278535337331359</v>
+      </c>
+      <c r="T885">
+        <f t="shared" si="107"/>
+        <v>0.17136568148275913</v>
+      </c>
+      <c r="U885">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F886" t="s">
+        <v>306</v>
+      </c>
+      <c r="H886">
+        <v>31</v>
+      </c>
+      <c r="I886">
+        <v>25</v>
+      </c>
+      <c r="J886">
+        <v>0</v>
+      </c>
+      <c r="K886">
+        <v>0</v>
+      </c>
+      <c r="L886">
+        <v>0</v>
+      </c>
+      <c r="N886">
+        <f t="shared" si="135"/>
+        <v>484</v>
+      </c>
+      <c r="P886">
+        <f t="shared" si="136"/>
+        <v>0.33</v>
+      </c>
+      <c r="Q886">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S886">
+        <f t="shared" si="130"/>
+        <v>8.278535337331359</v>
+      </c>
+      <c r="T886">
+        <f t="shared" si="107"/>
+        <v>0.17136568148275913</v>
+      </c>
+      <c r="U886">
+        <f t="shared" si="108"/>
+        <v>132.80840314913834</v>
+      </c>
+    </row>
+    <row r="887" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F887" t="s">
+        <v>307</v>
+      </c>
+      <c r="H887">
+        <v>30</v>
+      </c>
+      <c r="I887">
+        <v>30</v>
+      </c>
+      <c r="J887">
+        <v>0</v>
+      </c>
+      <c r="K887">
+        <v>0</v>
+      </c>
+      <c r="L887">
+        <v>0</v>
+      </c>
+      <c r="N887">
+        <f>$AM$126</f>
+        <v>531</v>
+      </c>
+      <c r="P887">
+        <f>$AM$60</f>
+        <v>0.52</v>
+      </c>
+      <c r="Q887">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S887">
+        <f t="shared" si="130"/>
+        <v>9.1593475476339599</v>
+      </c>
+      <c r="T887">
+        <f t="shared" si="107"/>
+        <v>0.18959849423602296</v>
+      </c>
+      <c r="U887">
+        <f t="shared" si="108"/>
+        <v>170.63864481242067</v>
+      </c>
+    </row>
+    <row r="888" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F888" t="s">
+        <v>308</v>
+      </c>
+      <c r="H888">
+        <v>31</v>
+      </c>
+      <c r="I888">
+        <v>35</v>
+      </c>
+      <c r="J888">
+        <v>0</v>
+      </c>
+      <c r="K888">
+        <v>0</v>
+      </c>
+      <c r="L888">
+        <v>0</v>
+      </c>
+      <c r="N888">
+        <f t="shared" ref="N888:N890" si="137">$AM$126</f>
+        <v>531</v>
+      </c>
+      <c r="P888">
+        <f t="shared" ref="P888:P890" si="138">$AM$60</f>
+        <v>0.52</v>
+      </c>
+      <c r="Q888">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S888">
+        <f t="shared" si="130"/>
+        <v>9.1593475476339599</v>
+      </c>
+      <c r="T888">
+        <f t="shared" si="107"/>
+        <v>0.18959849423602296</v>
+      </c>
+      <c r="U888">
+        <f t="shared" si="108"/>
+        <v>205.71436624608492</v>
+      </c>
+    </row>
+    <row r="889" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F889" t="s">
+        <v>309</v>
+      </c>
+      <c r="H889">
+        <v>30</v>
+      </c>
+      <c r="I889">
+        <v>40</v>
+      </c>
+      <c r="J889">
+        <v>0</v>
+      </c>
+      <c r="K889">
+        <v>0</v>
+      </c>
+      <c r="L889">
+        <v>0</v>
+      </c>
+      <c r="N889">
+        <f t="shared" si="137"/>
+        <v>531</v>
+      </c>
+      <c r="P889">
+        <f t="shared" si="138"/>
+        <v>0.52</v>
+      </c>
+      <c r="Q889">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S889">
+        <f t="shared" si="130"/>
+        <v>9.1593475476339599</v>
+      </c>
+      <c r="T889">
+        <f t="shared" si="107"/>
+        <v>0.18959849423602296</v>
+      </c>
+      <c r="U889">
+        <f t="shared" si="108"/>
+        <v>227.51819308322754</v>
+      </c>
+    </row>
+    <row r="890" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="F890" t="s">
+        <v>310</v>
+      </c>
+      <c r="H890">
+        <v>31</v>
+      </c>
+      <c r="I890">
+        <v>42</v>
+      </c>
+      <c r="J890">
+        <v>0</v>
+      </c>
+      <c r="K890">
+        <v>0</v>
+      </c>
+      <c r="L890">
+        <v>0</v>
+      </c>
+      <c r="N890">
+        <f>$AM$127</f>
+        <v>445</v>
+      </c>
+      <c r="P890">
+        <f>$AM$61</f>
+        <v>0.43</v>
+      </c>
+      <c r="Q890">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="S890">
+        <f t="shared" si="130"/>
+        <v>7.9856260332249995</v>
+      </c>
+      <c r="T890">
+        <f t="shared" si="107"/>
+        <v>0.16530245888775749</v>
+      </c>
+      <c r="U890">
+        <f t="shared" si="108"/>
+        <v>215.22380147186024</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="V2:V10 T11 S2:T10 N2:N10 L2:L10 P2:Q10 H2:J9 H10:I10" numberStoredAsText="1"/>

--- a/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/3.2-beef-enteric/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{A9CDA150-C7B8-344A-B152-B20469EC9742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{9D25F5B6-DC18-CB45-9AA9-BD7472F19CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51220" yWindow="14300" windowWidth="28800" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="313">
   <si>
     <t>EFPRP</t>
   </si>
@@ -1018,6 +1018,12 @@
   </si>
   <si>
     <t>December</t>
+  </si>
+  <si>
+    <t>QLD - Moderate/High - no calving</t>
+  </si>
+  <si>
+    <t>No calving</t>
   </si>
 </sst>
 </file>
@@ -55532,9 +55538,14 @@
         <v>262</v>
       </c>
     </row>
+    <row r="610" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A610" t="s">
+        <v>312</v>
+      </c>
+    </row>
     <row r="611" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="B611" t="s">
         <v>232</v>
@@ -55592,7 +55603,7 @@
       </c>
       <c r="V611">
         <f>SUM(U611:U650)/1000</f>
-        <v>42.546995304582374</v>
+        <v>41.513791886009763</v>
       </c>
     </row>
     <row r="612" spans="1:22" x14ac:dyDescent="0.2">
@@ -56086,10 +56097,10 @@
         <v>150</v>
       </c>
       <c r="J623">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K623">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L623">
         <f>$AC$12</f>
@@ -56103,19 +56114,19 @@
       </c>
       <c r="Q623">
         <f>(J623 * $AD$4 +K623* $AD$5) + (1 -J623 - K623 )</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="S623">
         <f t="shared" si="59"/>
-        <v>8.2359239277242935</v>
+        <v>6.7785382121187601</v>
       </c>
       <c r="T623">
         <f t="shared" si="60"/>
-        <v>0.17048362530389286</v>
+        <v>0.14031574099085833</v>
       </c>
       <c r="U623">
         <f>H623*T623*I623</f>
-        <v>2333.4946213470334</v>
+        <v>1920.5717048123736</v>
       </c>
     </row>
     <row r="624" spans="1:22" x14ac:dyDescent="0.2">
@@ -56135,7 +56146,7 @@
         <v>0</v>
       </c>
       <c r="K624">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="L624">
         <f>$AC$13</f>
@@ -56149,19 +56160,19 @@
       </c>
       <c r="Q624">
         <f t="shared" ref="Q624:Q636" si="61">(J624 * $AD$4 +K624* $AD$5) + (1 -J624 - K624 )</f>
-        <v>1.0710000000000002</v>
+        <v>1</v>
       </c>
       <c r="S624">
         <f t="shared" si="59"/>
-        <v>6.919489694563473</v>
+        <v>6.4607746914691617</v>
       </c>
       <c r="T624">
         <f t="shared" si="60"/>
-        <v>0.14323343667746388</v>
+        <v>0.13373803611341165</v>
       </c>
       <c r="U624">
         <f>H624*T624*I624</f>
-        <v>3267.5127742046448</v>
+        <v>3050.8989488372031</v>
       </c>
     </row>
     <row r="625" spans="5:21" x14ac:dyDescent="0.2">
@@ -56218,7 +56229,7 @@
         <v>200</v>
       </c>
       <c r="J626">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K626">
         <v>0</v>
@@ -56235,19 +56246,19 @@
       </c>
       <c r="Q626">
         <f t="shared" si="61"/>
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="S626">
         <f t="shared" si="59"/>
-        <v>6.2411086991808444</v>
+        <v>6.0593288341561591</v>
       </c>
       <c r="T626">
         <f t="shared" si="60"/>
-        <v>0.12919095007304346</v>
+        <v>0.12542810686703249</v>
       </c>
       <c r="U626">
         <f>H626*T626*I626</f>
-        <v>2357.7348388330433</v>
+        <v>2289.0629503233426</v>
       </c>
     </row>
     <row r="627" spans="5:21" x14ac:dyDescent="0.2">
@@ -56438,10 +56449,10 @@
         <v>50</v>
       </c>
       <c r="J631">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K631">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L631">
         <f>$AC$12</f>
@@ -56455,19 +56466,19 @@
       </c>
       <c r="Q631">
         <f t="shared" si="61"/>
-        <v>1.2750000000000001</v>
+        <v>1</v>
       </c>
       <c r="S631">
         <f t="shared" si="59"/>
-        <v>9.1459363232214983</v>
+        <v>7.1732833907619584</v>
       </c>
       <c r="T631">
         <f t="shared" si="60"/>
-        <v>0.18932088189068499</v>
+        <v>0.14848696618877252</v>
       </c>
       <c r="U631">
         <f>H631*T631*I631</f>
-        <v>863.77652362625031</v>
+        <v>677.47178323627463</v>
       </c>
     </row>
     <row r="632" spans="5:21" x14ac:dyDescent="0.2">
@@ -56487,7 +56498,7 @@
         <v>0</v>
       </c>
       <c r="K632">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L632">
         <f>$AC$13</f>
@@ -56501,19 +56512,19 @@
       </c>
       <c r="Q632">
         <f t="shared" si="61"/>
-        <v>1.0900000000000001</v>
+        <v>1</v>
       </c>
       <c r="S632">
         <f t="shared" si="59"/>
-        <v>9.5337261050566653</v>
+        <v>8.7465377110611602</v>
       </c>
       <c r="T632">
         <f t="shared" si="60"/>
-        <v>0.19734813037467297</v>
+        <v>0.18105333061896603</v>
       </c>
       <c r="U632">
         <f>H632*T632*I632</f>
-        <v>1800.8016896688907</v>
+        <v>1652.111641898065</v>
       </c>
     </row>
     <row r="633" spans="5:21" x14ac:dyDescent="0.2">
